--- a/Consolidado_contratistas_plantabal.xlsx
+++ b/Consolidado_contratistas_plantabal.xlsx
@@ -282,7 +282,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="15">
+  <dxfs count="18">
     <dxf>
       <font>
         <name val="Arial"/>
@@ -479,6 +479,39 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color rgb="009C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00FFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color rgb="009C5700"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00FFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color rgb="00276221"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00C6EFCE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -835,10 +868,10 @@
     <col width="18" customWidth="1" min="2" max="3"/>
     <col width="30" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="7"/>
-    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="11" customWidth="1" min="7" max="7"/>
     <col width="15" customWidth="1" min="8" max="8"/>
     <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="11" customWidth="1" min="10" max="10"/>
     <col width="16" customWidth="1" min="11" max="11"/>
     <col width="14" customWidth="1" min="12" max="12"/>
     <col width="15" customWidth="1" min="13" max="15"/>
@@ -2635,60 +2668,76 @@
     <mergeCell ref="A1:B1"/>
   </mergeCells>
   <conditionalFormatting sqref="F6:F55">
-    <cfRule type="expression" priority="6" dxfId="2">
-      <formula>AND(F6&lt;&gt;"",ISNUMBER(F6),F6&lt;TODAY())</formula>
+    <cfRule type="expression" priority="1" dxfId="15">
+      <formula>AND(F6&lt;&gt;"",ISNUMBER(F6),F6+365&lt;TODAY())</formula>
     </cfRule>
-    <cfRule type="expression" priority="7" dxfId="1">
-      <formula>AND(F6&lt;&gt;"",ISNUMBER(F6),F6&gt;=TODAY(),F6&lt;=TODAY()+30)</formula>
+    <cfRule type="expression" priority="2" dxfId="16">
+      <formula>AND(F6&lt;&gt;"",ISNUMBER(F6),F6+365&gt;=TODAY(),F6+365&lt;=TODAY()+30)</formula>
     </cfRule>
-    <cfRule type="expression" priority="8" dxfId="0">
-      <formula>AND(F6&lt;&gt;"",ISNUMBER(F6),F6&gt;TODAY()+30)</formula>
+    <cfRule type="expression" priority="3" dxfId="17">
+      <formula>AND(F6&lt;&gt;"",ISNUMBER(F6),F6+365&gt;TODAY()+30)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G6:G55">
-    <cfRule type="expression" priority="30" dxfId="2">
-      <formula>AND(G6&lt;&gt;"",ISNUMBER(G6),G6&lt;DATE(YEAR(TODAY()),MONTH(TODAY())-1,1))</formula>
+    <cfRule type="expression" priority="4" dxfId="17">
+      <formula>G6="✔ Vigente"</formula>
     </cfRule>
-    <cfRule type="expression" priority="31" dxfId="0">
-      <formula>AND(G6&lt;&gt;"",ISNUMBER(G6),G6&gt;=DATE(YEAR(TODAY()),MONTH(TODAY())-1,1))</formula>
+    <cfRule type="expression" priority="5" dxfId="15">
+      <formula>G6="✘ Vencido"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H6:H55">
-    <cfRule type="expression" priority="9" dxfId="2">
-      <formula>AND(H6&lt;&gt;"",ISNUMBER(H6),H6&lt;TODAY())</formula>
+    <cfRule type="expression" priority="6" dxfId="15">
+      <formula>AND(H6&lt;&gt;"",ISNUMBER(H6),H6&lt;DATE(YEAR(TODAY()),MONTH(TODAY())-1,1))</formula>
     </cfRule>
-    <cfRule type="expression" priority="10" dxfId="1">
-      <formula>AND(H6&lt;&gt;"",ISNUMBER(H6),H6&gt;=TODAY(),H6&lt;=TODAY()+30)</formula>
-    </cfRule>
-    <cfRule type="expression" priority="11" dxfId="0">
-      <formula>AND(H6&lt;&gt;"",ISNUMBER(H6),H6&gt;TODAY()+30)</formula>
+    <cfRule type="expression" priority="7" dxfId="17">
+      <formula>AND(H6&lt;&gt;"",ISNUMBER(H6),H6&gt;=DATE(YEAR(TODAY()),MONTH(TODAY())-1,1))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I6:I55">
-    <cfRule type="cellIs" priority="4" operator="equal" dxfId="4">
-      <formula>"APTO"</formula>
+    <cfRule type="expression" priority="8" dxfId="15">
+      <formula>AND(I6&lt;&gt;"",ISNUMBER(I6),I6+365&lt;TODAY())</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="5" operator="equal" dxfId="3">
-      <formula>"NO APTO"</formula>
+    <cfRule type="expression" priority="9" dxfId="16">
+      <formula>AND(I6&lt;&gt;"",ISNUMBER(I6),I6+365&gt;=TODAY(),I6+365&lt;=TODAY()+30)</formula>
+    </cfRule>
+    <cfRule type="expression" priority="10" dxfId="17">
+      <formula>AND(I6&lt;&gt;"",ISNUMBER(I6),I6+365&gt;TODAY()+30)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J6:J55">
-    <cfRule type="cellIs" priority="2" operator="equal" dxfId="4">
-      <formula>"✔ ACCESO PERMITIDO"</formula>
+    <cfRule type="expression" priority="11" dxfId="17">
+      <formula>J6="✔ Vigente"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="3" operator="equal" dxfId="3">
-      <formula>"✘ SIN ACCESO"</formula>
+    <cfRule type="expression" priority="12" dxfId="15">
+      <formula>J6="✘ Vencido"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K6:P55">
-    <cfRule type="expression" priority="12" dxfId="2">
-      <formula>AND(K6&lt;&gt;"",ISNUMBER(K6),K6&lt;TODAY())</formula>
+  <conditionalFormatting sqref="K6:K55">
+    <cfRule type="expression" priority="13" dxfId="17">
+      <formula>UPPER(K6)="APTO"</formula>
     </cfRule>
-    <cfRule type="expression" priority="13" dxfId="1">
-      <formula>AND(K6&lt;&gt;"",ISNUMBER(K6),K6&gt;=TODAY(),K6&lt;=TODAY()+30)</formula>
+    <cfRule type="expression" priority="14" dxfId="15">
+      <formula>UPPER(K6)="NO APTO"</formula>
     </cfRule>
-    <cfRule type="expression" priority="14" dxfId="0">
-      <formula>AND(K6&lt;&gt;"",ISNUMBER(K6),K6&gt;TODAY()+30)</formula>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L6:L55">
+    <cfRule type="expression" priority="15" dxfId="17">
+      <formula>L6="✔ ACCESO PERMITIDO"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="16" dxfId="15">
+      <formula>L6="✘ SIN ACCESO"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M6:R55">
+    <cfRule type="expression" priority="17" dxfId="15">
+      <formula>AND(M6&lt;&gt;"",ISNUMBER(M6),M6&lt;TODAY())</formula>
+    </cfRule>
+    <cfRule type="expression" priority="18" dxfId="16">
+      <formula>AND(M6&lt;&gt;"",ISNUMBER(M6),M6&gt;=TODAY(),M6&lt;=TODAY()+30)</formula>
+    </cfRule>
+    <cfRule type="expression" priority="19" dxfId="17">
+      <formula>AND(M6&lt;&gt;"",ISNUMBER(M6),M6&gt;TODAY()+30)</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">

--- a/Consolidado_contratistas_plantabal.xlsx
+++ b/Consolidado_contratistas_plantabal.xlsx
@@ -485,33 +485,33 @@
     <dxf>
       <font>
         <b val="1"/>
-        <color rgb="009C0006"/>
+        <color rgb="FF9C0006"/>
       </font>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="00FFC7CE"/>
+          <fgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <font>
         <b val="1"/>
-        <color rgb="009C5700"/>
+        <color rgb="FF9C5700"/>
       </font>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="00FFEB9C"/>
+          <fgColor rgb="FFFFEB9C"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <font>
         <b val="1"/>
-        <color rgb="00276221"/>
+        <color rgb="FF276221"/>
       </font>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="00C6EFCE"/>
+          <fgColor rgb="FFC6EFCE"/>
         </patternFill>
       </fill>
     </dxf>

--- a/Consolidado_contratistas_plantabal.xlsx
+++ b/Consolidado_contratistas_plantabal.xlsx
@@ -943,7 +943,7 @@
       <c r="F5" s="8" t="inlineStr">
         <is>
           <t>Inducción de seguridad
-(Fecha recepción)</t>
+(Fecha vencimiento)</t>
         </is>
       </c>
       <c r="G5" s="22" t="inlineStr">
@@ -961,7 +961,7 @@
       <c r="I5" s="8" t="inlineStr">
         <is>
           <t>Cert. Médico Laboral
-(Fecha emisión)</t>
+(Fecha vencimiento)</t>
         </is>
       </c>
       <c r="J5" s="22" t="inlineStr">
@@ -1055,7 +1055,7 @@
         <v>46478</v>
       </c>
       <c r="G6" s="13">
-        <f>IF(F6="","",IF(F6+365&gt;=TODAY(),"✔ Vigente","✘ Vencido"))</f>
+        <f>IF(F6="","",IF(F6&gt;=TODAY(),"✔ Vigente","✘ Vencido"))</f>
         <v/>
       </c>
       <c r="H6" s="12" t="n">
@@ -1065,7 +1065,7 @@
         <v>46478</v>
       </c>
       <c r="J6" s="13">
-        <f>IF(I6="","",IF(I6+365&gt;=TODAY(),"✔ Vigente","✘ Vencido"))</f>
+        <f>IF(I6="","",IF(I6&gt;=TODAY(),"✔ Vigente","✘ Vencido"))</f>
         <v/>
       </c>
       <c r="K6" s="13" t="inlineStr">
@@ -1074,7 +1074,7 @@
         </is>
       </c>
       <c r="L6" s="14">
-        <f>IF(AND(F6&lt;&gt;"",ISNUMBER(F6),F6+365&gt;=TODAY(),H6&lt;&gt;"",ISNUMBER(H6),H6&gt;=DATE(YEAR(TODAY()),MONTH(TODAY())-1,1),I6&lt;&gt;"",ISNUMBER(I6),I6+365&gt;=TODAY(),K6="APTO"),"✔ ACCESO PERMITIDO","✘ SIN ACCESO")</f>
+        <f>IF(AND(F6&lt;&gt;"",ISNUMBER(F6),F6&gt;=TODAY(),H6&lt;&gt;"",ISNUMBER(H6),H6&gt;=DATE(YEAR(TODAY()),MONTH(TODAY())-1,1),I6&lt;&gt;"",ISNUMBER(I6),I6&gt;=TODAY(),K6="APTO"),"✔ ACCESO PERMITIDO","✘ SIN ACCESO")</f>
         <v/>
       </c>
       <c r="M6" s="12" t="n">
@@ -1099,18 +1099,18 @@
       <c r="E7" s="11" t="n"/>
       <c r="F7" s="12" t="n"/>
       <c r="G7" s="13">
-        <f>IF(F7="","",IF(F7+365&gt;=TODAY(),"✔ Vigente","✘ Vencido"))</f>
+        <f>IF(F7="","",IF(F7&gt;=TODAY(),"✔ Vigente","✘ Vencido"))</f>
         <v/>
       </c>
       <c r="H7" s="12" t="n"/>
       <c r="I7" s="12" t="n"/>
       <c r="J7" s="13">
-        <f>IF(I7="","",IF(I7+365&gt;=TODAY(),"✔ Vigente","✘ Vencido"))</f>
+        <f>IF(I7="","",IF(I7&gt;=TODAY(),"✔ Vigente","✘ Vencido"))</f>
         <v/>
       </c>
       <c r="K7" s="13" t="n"/>
       <c r="L7" s="16">
-        <f>IF(AND(F7&lt;&gt;"",ISNUMBER(F7),F7+365&gt;=TODAY(),H7&lt;&gt;"",ISNUMBER(H7),H7&gt;=DATE(YEAR(TODAY()),MONTH(TODAY())-1,1),I7&lt;&gt;"",ISNUMBER(I7),I7+365&gt;=TODAY(),K7="APTO"),"✔ ACCESO PERMITIDO","✘ SIN ACCESO")</f>
+        <f>IF(AND(F7&lt;&gt;"",ISNUMBER(F7),F7&gt;=TODAY(),H7&lt;&gt;"",ISNUMBER(H7),H7&gt;=DATE(YEAR(TODAY()),MONTH(TODAY())-1,1),I7&lt;&gt;"",ISNUMBER(I7),I7&gt;=TODAY(),K7="APTO"),"✔ ACCESO PERMITIDO","✘ SIN ACCESO")</f>
         <v/>
       </c>
       <c r="M7" s="12" t="n"/>
@@ -1131,18 +1131,18 @@
       <c r="E8" s="11" t="n"/>
       <c r="F8" s="12" t="n"/>
       <c r="G8" s="13">
-        <f>IF(F8="","",IF(F8+365&gt;=TODAY(),"✔ Vigente","✘ Vencido"))</f>
+        <f>IF(F8="","",IF(F8&gt;=TODAY(),"✔ Vigente","✘ Vencido"))</f>
         <v/>
       </c>
       <c r="H8" s="12" t="n"/>
       <c r="I8" s="12" t="n"/>
       <c r="J8" s="13">
-        <f>IF(I8="","",IF(I8+365&gt;=TODAY(),"✔ Vigente","✘ Vencido"))</f>
+        <f>IF(I8="","",IF(I8&gt;=TODAY(),"✔ Vigente","✘ Vencido"))</f>
         <v/>
       </c>
       <c r="K8" s="13" t="n"/>
       <c r="L8" s="14">
-        <f>IF(AND(F8&lt;&gt;"",ISNUMBER(F8),F8+365&gt;=TODAY(),H8&lt;&gt;"",ISNUMBER(H8),H8&gt;=DATE(YEAR(TODAY()),MONTH(TODAY())-1,1),I8&lt;&gt;"",ISNUMBER(I8),I8+365&gt;=TODAY(),K8="APTO"),"✔ ACCESO PERMITIDO","✘ SIN ACCESO")</f>
+        <f>IF(AND(F8&lt;&gt;"",ISNUMBER(F8),F8&gt;=TODAY(),H8&lt;&gt;"",ISNUMBER(H8),H8&gt;=DATE(YEAR(TODAY()),MONTH(TODAY())-1,1),I8&lt;&gt;"",ISNUMBER(I8),I8&gt;=TODAY(),K8="APTO"),"✔ ACCESO PERMITIDO","✘ SIN ACCESO")</f>
         <v/>
       </c>
       <c r="M8" s="12" t="n"/>
@@ -1163,18 +1163,18 @@
       <c r="E9" s="11" t="n"/>
       <c r="F9" s="12" t="n"/>
       <c r="G9" s="13">
-        <f>IF(F9="","",IF(F9+365&gt;=TODAY(),"✔ Vigente","✘ Vencido"))</f>
+        <f>IF(F9="","",IF(F9&gt;=TODAY(),"✔ Vigente","✘ Vencido"))</f>
         <v/>
       </c>
       <c r="H9" s="12" t="n"/>
       <c r="I9" s="12" t="n"/>
       <c r="J9" s="13">
-        <f>IF(I9="","",IF(I9+365&gt;=TODAY(),"✔ Vigente","✘ Vencido"))</f>
+        <f>IF(I9="","",IF(I9&gt;=TODAY(),"✔ Vigente","✘ Vencido"))</f>
         <v/>
       </c>
       <c r="K9" s="13" t="n"/>
       <c r="L9" s="16">
-        <f>IF(AND(F9&lt;&gt;"",ISNUMBER(F9),F9+365&gt;=TODAY(),H9&lt;&gt;"",ISNUMBER(H9),H9&gt;=DATE(YEAR(TODAY()),MONTH(TODAY())-1,1),I9&lt;&gt;"",ISNUMBER(I9),I9+365&gt;=TODAY(),K9="APTO"),"✔ ACCESO PERMITIDO","✘ SIN ACCESO")</f>
+        <f>IF(AND(F9&lt;&gt;"",ISNUMBER(F9),F9&gt;=TODAY(),H9&lt;&gt;"",ISNUMBER(H9),H9&gt;=DATE(YEAR(TODAY()),MONTH(TODAY())-1,1),I9&lt;&gt;"",ISNUMBER(I9),I9&gt;=TODAY(),K9="APTO"),"✔ ACCESO PERMITIDO","✘ SIN ACCESO")</f>
         <v/>
       </c>
       <c r="M9" s="12" t="n"/>
@@ -1195,18 +1195,18 @@
       <c r="E10" s="11" t="n"/>
       <c r="F10" s="12" t="n"/>
       <c r="G10" s="13">
-        <f>IF(F10="","",IF(F10+365&gt;=TODAY(),"✔ Vigente","✘ Vencido"))</f>
+        <f>IF(F10="","",IF(F10&gt;=TODAY(),"✔ Vigente","✘ Vencido"))</f>
         <v/>
       </c>
       <c r="H10" s="12" t="n"/>
       <c r="I10" s="12" t="n"/>
       <c r="J10" s="13">
-        <f>IF(I10="","",IF(I10+365&gt;=TODAY(),"✔ Vigente","✘ Vencido"))</f>
+        <f>IF(I10="","",IF(I10&gt;=TODAY(),"✔ Vigente","✘ Vencido"))</f>
         <v/>
       </c>
       <c r="K10" s="13" t="n"/>
       <c r="L10" s="14">
-        <f>IF(AND(F10&lt;&gt;"",ISNUMBER(F10),F10+365&gt;=TODAY(),H10&lt;&gt;"",ISNUMBER(H10),H10&gt;=DATE(YEAR(TODAY()),MONTH(TODAY())-1,1),I10&lt;&gt;"",ISNUMBER(I10),I10+365&gt;=TODAY(),K10="APTO"),"✔ ACCESO PERMITIDO","✘ SIN ACCESO")</f>
+        <f>IF(AND(F10&lt;&gt;"",ISNUMBER(F10),F10&gt;=TODAY(),H10&lt;&gt;"",ISNUMBER(H10),H10&gt;=DATE(YEAR(TODAY()),MONTH(TODAY())-1,1),I10&lt;&gt;"",ISNUMBER(I10),I10&gt;=TODAY(),K10="APTO"),"✔ ACCESO PERMITIDO","✘ SIN ACCESO")</f>
         <v/>
       </c>
       <c r="M10" s="12" t="n"/>
@@ -1227,18 +1227,18 @@
       <c r="E11" s="11" t="n"/>
       <c r="F11" s="12" t="n"/>
       <c r="G11" s="13">
-        <f>IF(F11="","",IF(F11+365&gt;=TODAY(),"✔ Vigente","✘ Vencido"))</f>
+        <f>IF(F11="","",IF(F11&gt;=TODAY(),"✔ Vigente","✘ Vencido"))</f>
         <v/>
       </c>
       <c r="H11" s="12" t="n"/>
       <c r="I11" s="12" t="n"/>
       <c r="J11" s="13">
-        <f>IF(I11="","",IF(I11+365&gt;=TODAY(),"✔ Vigente","✘ Vencido"))</f>
+        <f>IF(I11="","",IF(I11&gt;=TODAY(),"✔ Vigente","✘ Vencido"))</f>
         <v/>
       </c>
       <c r="K11" s="13" t="n"/>
       <c r="L11" s="16">
-        <f>IF(AND(F11&lt;&gt;"",ISNUMBER(F11),F11+365&gt;=TODAY(),H11&lt;&gt;"",ISNUMBER(H11),H11&gt;=DATE(YEAR(TODAY()),MONTH(TODAY())-1,1),I11&lt;&gt;"",ISNUMBER(I11),I11+365&gt;=TODAY(),K11="APTO"),"✔ ACCESO PERMITIDO","✘ SIN ACCESO")</f>
+        <f>IF(AND(F11&lt;&gt;"",ISNUMBER(F11),F11&gt;=TODAY(),H11&lt;&gt;"",ISNUMBER(H11),H11&gt;=DATE(YEAR(TODAY()),MONTH(TODAY())-1,1),I11&lt;&gt;"",ISNUMBER(I11),I11&gt;=TODAY(),K11="APTO"),"✔ ACCESO PERMITIDO","✘ SIN ACCESO")</f>
         <v/>
       </c>
       <c r="M11" s="12" t="n"/>
@@ -1259,18 +1259,18 @@
       <c r="E12" s="11" t="n"/>
       <c r="F12" s="12" t="n"/>
       <c r="G12" s="13">
-        <f>IF(F12="","",IF(F12+365&gt;=TODAY(),"✔ Vigente","✘ Vencido"))</f>
+        <f>IF(F12="","",IF(F12&gt;=TODAY(),"✔ Vigente","✘ Vencido"))</f>
         <v/>
       </c>
       <c r="H12" s="12" t="n"/>
       <c r="I12" s="12" t="n"/>
       <c r="J12" s="13">
-        <f>IF(I12="","",IF(I12+365&gt;=TODAY(),"✔ Vigente","✘ Vencido"))</f>
+        <f>IF(I12="","",IF(I12&gt;=TODAY(),"✔ Vigente","✘ Vencido"))</f>
         <v/>
       </c>
       <c r="K12" s="13" t="n"/>
       <c r="L12" s="14">
-        <f>IF(AND(F12&lt;&gt;"",ISNUMBER(F12),F12+365&gt;=TODAY(),H12&lt;&gt;"",ISNUMBER(H12),H12&gt;=DATE(YEAR(TODAY()),MONTH(TODAY())-1,1),I12&lt;&gt;"",ISNUMBER(I12),I12+365&gt;=TODAY(),K12="APTO"),"✔ ACCESO PERMITIDO","✘ SIN ACCESO")</f>
+        <f>IF(AND(F12&lt;&gt;"",ISNUMBER(F12),F12&gt;=TODAY(),H12&lt;&gt;"",ISNUMBER(H12),H12&gt;=DATE(YEAR(TODAY()),MONTH(TODAY())-1,1),I12&lt;&gt;"",ISNUMBER(I12),I12&gt;=TODAY(),K12="APTO"),"✔ ACCESO PERMITIDO","✘ SIN ACCESO")</f>
         <v/>
       </c>
       <c r="M12" s="12" t="n"/>
@@ -1291,18 +1291,18 @@
       <c r="E13" s="11" t="n"/>
       <c r="F13" s="12" t="n"/>
       <c r="G13" s="13">
-        <f>IF(F13="","",IF(F13+365&gt;=TODAY(),"✔ Vigente","✘ Vencido"))</f>
+        <f>IF(F13="","",IF(F13&gt;=TODAY(),"✔ Vigente","✘ Vencido"))</f>
         <v/>
       </c>
       <c r="H13" s="12" t="n"/>
       <c r="I13" s="12" t="n"/>
       <c r="J13" s="13">
-        <f>IF(I13="","",IF(I13+365&gt;=TODAY(),"✔ Vigente","✘ Vencido"))</f>
+        <f>IF(I13="","",IF(I13&gt;=TODAY(),"✔ Vigente","✘ Vencido"))</f>
         <v/>
       </c>
       <c r="K13" s="13" t="n"/>
       <c r="L13" s="16">
-        <f>IF(AND(F13&lt;&gt;"",ISNUMBER(F13),F13+365&gt;=TODAY(),H13&lt;&gt;"",ISNUMBER(H13),H13&gt;=DATE(YEAR(TODAY()),MONTH(TODAY())-1,1),I13&lt;&gt;"",ISNUMBER(I13),I13+365&gt;=TODAY(),K13="APTO"),"✔ ACCESO PERMITIDO","✘ SIN ACCESO")</f>
+        <f>IF(AND(F13&lt;&gt;"",ISNUMBER(F13),F13&gt;=TODAY(),H13&lt;&gt;"",ISNUMBER(H13),H13&gt;=DATE(YEAR(TODAY()),MONTH(TODAY())-1,1),I13&lt;&gt;"",ISNUMBER(I13),I13&gt;=TODAY(),K13="APTO"),"✔ ACCESO PERMITIDO","✘ SIN ACCESO")</f>
         <v/>
       </c>
       <c r="M13" s="12" t="n"/>
@@ -1323,18 +1323,18 @@
       <c r="E14" s="11" t="n"/>
       <c r="F14" s="12" t="n"/>
       <c r="G14" s="13">
-        <f>IF(F14="","",IF(F14+365&gt;=TODAY(),"✔ Vigente","✘ Vencido"))</f>
+        <f>IF(F14="","",IF(F14&gt;=TODAY(),"✔ Vigente","✘ Vencido"))</f>
         <v/>
       </c>
       <c r="H14" s="12" t="n"/>
       <c r="I14" s="12" t="n"/>
       <c r="J14" s="13">
-        <f>IF(I14="","",IF(I14+365&gt;=TODAY(),"✔ Vigente","✘ Vencido"))</f>
+        <f>IF(I14="","",IF(I14&gt;=TODAY(),"✔ Vigente","✘ Vencido"))</f>
         <v/>
       </c>
       <c r="K14" s="13" t="n"/>
       <c r="L14" s="14">
-        <f>IF(AND(F14&lt;&gt;"",ISNUMBER(F14),F14+365&gt;=TODAY(),H14&lt;&gt;"",ISNUMBER(H14),H14&gt;=DATE(YEAR(TODAY()),MONTH(TODAY())-1,1),I14&lt;&gt;"",ISNUMBER(I14),I14+365&gt;=TODAY(),K14="APTO"),"✔ ACCESO PERMITIDO","✘ SIN ACCESO")</f>
+        <f>IF(AND(F14&lt;&gt;"",ISNUMBER(F14),F14&gt;=TODAY(),H14&lt;&gt;"",ISNUMBER(H14),H14&gt;=DATE(YEAR(TODAY()),MONTH(TODAY())-1,1),I14&lt;&gt;"",ISNUMBER(I14),I14&gt;=TODAY(),K14="APTO"),"✔ ACCESO PERMITIDO","✘ SIN ACCESO")</f>
         <v/>
       </c>
       <c r="M14" s="12" t="n"/>
@@ -1355,18 +1355,18 @@
       <c r="E15" s="11" t="n"/>
       <c r="F15" s="12" t="n"/>
       <c r="G15" s="13">
-        <f>IF(F15="","",IF(F15+365&gt;=TODAY(),"✔ Vigente","✘ Vencido"))</f>
+        <f>IF(F15="","",IF(F15&gt;=TODAY(),"✔ Vigente","✘ Vencido"))</f>
         <v/>
       </c>
       <c r="H15" s="12" t="n"/>
       <c r="I15" s="12" t="n"/>
       <c r="J15" s="13">
-        <f>IF(I15="","",IF(I15+365&gt;=TODAY(),"✔ Vigente","✘ Vencido"))</f>
+        <f>IF(I15="","",IF(I15&gt;=TODAY(),"✔ Vigente","✘ Vencido"))</f>
         <v/>
       </c>
       <c r="K15" s="13" t="n"/>
       <c r="L15" s="16">
-        <f>IF(AND(F15&lt;&gt;"",ISNUMBER(F15),F15+365&gt;=TODAY(),H15&lt;&gt;"",ISNUMBER(H15),H15&gt;=DATE(YEAR(TODAY()),MONTH(TODAY())-1,1),I15&lt;&gt;"",ISNUMBER(I15),I15+365&gt;=TODAY(),K15="APTO"),"✔ ACCESO PERMITIDO","✘ SIN ACCESO")</f>
+        <f>IF(AND(F15&lt;&gt;"",ISNUMBER(F15),F15&gt;=TODAY(),H15&lt;&gt;"",ISNUMBER(H15),H15&gt;=DATE(YEAR(TODAY()),MONTH(TODAY())-1,1),I15&lt;&gt;"",ISNUMBER(I15),I15&gt;=TODAY(),K15="APTO"),"✔ ACCESO PERMITIDO","✘ SIN ACCESO")</f>
         <v/>
       </c>
       <c r="M15" s="12" t="n"/>
@@ -1387,18 +1387,18 @@
       <c r="E16" s="11" t="n"/>
       <c r="F16" s="12" t="n"/>
       <c r="G16" s="13">
-        <f>IF(F16="","",IF(F16+365&gt;=TODAY(),"✔ Vigente","✘ Vencido"))</f>
+        <f>IF(F16="","",IF(F16&gt;=TODAY(),"✔ Vigente","✘ Vencido"))</f>
         <v/>
       </c>
       <c r="H16" s="12" t="n"/>
       <c r="I16" s="12" t="n"/>
       <c r="J16" s="13">
-        <f>IF(I16="","",IF(I16+365&gt;=TODAY(),"✔ Vigente","✘ Vencido"))</f>
+        <f>IF(I16="","",IF(I16&gt;=TODAY(),"✔ Vigente","✘ Vencido"))</f>
         <v/>
       </c>
       <c r="K16" s="13" t="n"/>
       <c r="L16" s="14">
-        <f>IF(AND(F16&lt;&gt;"",ISNUMBER(F16),F16+365&gt;=TODAY(),H16&lt;&gt;"",ISNUMBER(H16),H16&gt;=DATE(YEAR(TODAY()),MONTH(TODAY())-1,1),I16&lt;&gt;"",ISNUMBER(I16),I16+365&gt;=TODAY(),K16="APTO"),"✔ ACCESO PERMITIDO","✘ SIN ACCESO")</f>
+        <f>IF(AND(F16&lt;&gt;"",ISNUMBER(F16),F16&gt;=TODAY(),H16&lt;&gt;"",ISNUMBER(H16),H16&gt;=DATE(YEAR(TODAY()),MONTH(TODAY())-1,1),I16&lt;&gt;"",ISNUMBER(I16),I16&gt;=TODAY(),K16="APTO"),"✔ ACCESO PERMITIDO","✘ SIN ACCESO")</f>
         <v/>
       </c>
       <c r="M16" s="12" t="n"/>
@@ -1419,18 +1419,18 @@
       <c r="E17" s="11" t="n"/>
       <c r="F17" s="12" t="n"/>
       <c r="G17" s="13">
-        <f>IF(F17="","",IF(F17+365&gt;=TODAY(),"✔ Vigente","✘ Vencido"))</f>
+        <f>IF(F17="","",IF(F17&gt;=TODAY(),"✔ Vigente","✘ Vencido"))</f>
         <v/>
       </c>
       <c r="H17" s="12" t="n"/>
       <c r="I17" s="12" t="n"/>
       <c r="J17" s="13">
-        <f>IF(I17="","",IF(I17+365&gt;=TODAY(),"✔ Vigente","✘ Vencido"))</f>
+        <f>IF(I17="","",IF(I17&gt;=TODAY(),"✔ Vigente","✘ Vencido"))</f>
         <v/>
       </c>
       <c r="K17" s="13" t="n"/>
       <c r="L17" s="16">
-        <f>IF(AND(F17&lt;&gt;"",ISNUMBER(F17),F17+365&gt;=TODAY(),H17&lt;&gt;"",ISNUMBER(H17),H17&gt;=DATE(YEAR(TODAY()),MONTH(TODAY())-1,1),I17&lt;&gt;"",ISNUMBER(I17),I17+365&gt;=TODAY(),K17="APTO"),"✔ ACCESO PERMITIDO","✘ SIN ACCESO")</f>
+        <f>IF(AND(F17&lt;&gt;"",ISNUMBER(F17),F17&gt;=TODAY(),H17&lt;&gt;"",ISNUMBER(H17),H17&gt;=DATE(YEAR(TODAY()),MONTH(TODAY())-1,1),I17&lt;&gt;"",ISNUMBER(I17),I17&gt;=TODAY(),K17="APTO"),"✔ ACCESO PERMITIDO","✘ SIN ACCESO")</f>
         <v/>
       </c>
       <c r="M17" s="12" t="n"/>
@@ -1451,18 +1451,18 @@
       <c r="E18" s="11" t="n"/>
       <c r="F18" s="12" t="n"/>
       <c r="G18" s="13">
-        <f>IF(F18="","",IF(F18+365&gt;=TODAY(),"✔ Vigente","✘ Vencido"))</f>
+        <f>IF(F18="","",IF(F18&gt;=TODAY(),"✔ Vigente","✘ Vencido"))</f>
         <v/>
       </c>
       <c r="H18" s="12" t="n"/>
       <c r="I18" s="12" t="n"/>
       <c r="J18" s="13">
-        <f>IF(I18="","",IF(I18+365&gt;=TODAY(),"✔ Vigente","✘ Vencido"))</f>
+        <f>IF(I18="","",IF(I18&gt;=TODAY(),"✔ Vigente","✘ Vencido"))</f>
         <v/>
       </c>
       <c r="K18" s="13" t="n"/>
       <c r="L18" s="14">
-        <f>IF(AND(F18&lt;&gt;"",ISNUMBER(F18),F18+365&gt;=TODAY(),H18&lt;&gt;"",ISNUMBER(H18),H18&gt;=DATE(YEAR(TODAY()),MONTH(TODAY())-1,1),I18&lt;&gt;"",ISNUMBER(I18),I18+365&gt;=TODAY(),K18="APTO"),"✔ ACCESO PERMITIDO","✘ SIN ACCESO")</f>
+        <f>IF(AND(F18&lt;&gt;"",ISNUMBER(F18),F18&gt;=TODAY(),H18&lt;&gt;"",ISNUMBER(H18),H18&gt;=DATE(YEAR(TODAY()),MONTH(TODAY())-1,1),I18&lt;&gt;"",ISNUMBER(I18),I18&gt;=TODAY(),K18="APTO"),"✔ ACCESO PERMITIDO","✘ SIN ACCESO")</f>
         <v/>
       </c>
       <c r="M18" s="12" t="n"/>
@@ -1483,18 +1483,18 @@
       <c r="E19" s="11" t="n"/>
       <c r="F19" s="12" t="n"/>
       <c r="G19" s="13">
-        <f>IF(F19="","",IF(F19+365&gt;=TODAY(),"✔ Vigente","✘ Vencido"))</f>
+        <f>IF(F19="","",IF(F19&gt;=TODAY(),"✔ Vigente","✘ Vencido"))</f>
         <v/>
       </c>
       <c r="H19" s="12" t="n"/>
       <c r="I19" s="12" t="n"/>
       <c r="J19" s="13">
-        <f>IF(I19="","",IF(I19+365&gt;=TODAY(),"✔ Vigente","✘ Vencido"))</f>
+        <f>IF(I19="","",IF(I19&gt;=TODAY(),"✔ Vigente","✘ Vencido"))</f>
         <v/>
       </c>
       <c r="K19" s="13" t="n"/>
       <c r="L19" s="16">
-        <f>IF(AND(F19&lt;&gt;"",ISNUMBER(F19),F19+365&gt;=TODAY(),H19&lt;&gt;"",ISNUMBER(H19),H19&gt;=DATE(YEAR(TODAY()),MONTH(TODAY())-1,1),I19&lt;&gt;"",ISNUMBER(I19),I19+365&gt;=TODAY(),K19="APTO"),"✔ ACCESO PERMITIDO","✘ SIN ACCESO")</f>
+        <f>IF(AND(F19&lt;&gt;"",ISNUMBER(F19),F19&gt;=TODAY(),H19&lt;&gt;"",ISNUMBER(H19),H19&gt;=DATE(YEAR(TODAY()),MONTH(TODAY())-1,1),I19&lt;&gt;"",ISNUMBER(I19),I19&gt;=TODAY(),K19="APTO"),"✔ ACCESO PERMITIDO","✘ SIN ACCESO")</f>
         <v/>
       </c>
       <c r="M19" s="12" t="n"/>
@@ -1515,18 +1515,18 @@
       <c r="E20" s="11" t="n"/>
       <c r="F20" s="12" t="n"/>
       <c r="G20" s="13">
-        <f>IF(F20="","",IF(F20+365&gt;=TODAY(),"✔ Vigente","✘ Vencido"))</f>
+        <f>IF(F20="","",IF(F20&gt;=TODAY(),"✔ Vigente","✘ Vencido"))</f>
         <v/>
       </c>
       <c r="H20" s="12" t="n"/>
       <c r="I20" s="12" t="n"/>
       <c r="J20" s="13">
-        <f>IF(I20="","",IF(I20+365&gt;=TODAY(),"✔ Vigente","✘ Vencido"))</f>
+        <f>IF(I20="","",IF(I20&gt;=TODAY(),"✔ Vigente","✘ Vencido"))</f>
         <v/>
       </c>
       <c r="K20" s="13" t="n"/>
       <c r="L20" s="14">
-        <f>IF(AND(F20&lt;&gt;"",ISNUMBER(F20),F20+365&gt;=TODAY(),H20&lt;&gt;"",ISNUMBER(H20),H20&gt;=DATE(YEAR(TODAY()),MONTH(TODAY())-1,1),I20&lt;&gt;"",ISNUMBER(I20),I20+365&gt;=TODAY(),K20="APTO"),"✔ ACCESO PERMITIDO","✘ SIN ACCESO")</f>
+        <f>IF(AND(F20&lt;&gt;"",ISNUMBER(F20),F20&gt;=TODAY(),H20&lt;&gt;"",ISNUMBER(H20),H20&gt;=DATE(YEAR(TODAY()),MONTH(TODAY())-1,1),I20&lt;&gt;"",ISNUMBER(I20),I20&gt;=TODAY(),K20="APTO"),"✔ ACCESO PERMITIDO","✘ SIN ACCESO")</f>
         <v/>
       </c>
       <c r="M20" s="12" t="n"/>
@@ -1547,18 +1547,18 @@
       <c r="E21" s="11" t="n"/>
       <c r="F21" s="12" t="n"/>
       <c r="G21" s="13">
-        <f>IF(F21="","",IF(F21+365&gt;=TODAY(),"✔ Vigente","✘ Vencido"))</f>
+        <f>IF(F21="","",IF(F21&gt;=TODAY(),"✔ Vigente","✘ Vencido"))</f>
         <v/>
       </c>
       <c r="H21" s="12" t="n"/>
       <c r="I21" s="12" t="n"/>
       <c r="J21" s="13">
-        <f>IF(I21="","",IF(I21+365&gt;=TODAY(),"✔ Vigente","✘ Vencido"))</f>
+        <f>IF(I21="","",IF(I21&gt;=TODAY(),"✔ Vigente","✘ Vencido"))</f>
         <v/>
       </c>
       <c r="K21" s="13" t="n"/>
       <c r="L21" s="16">
-        <f>IF(AND(F21&lt;&gt;"",ISNUMBER(F21),F21+365&gt;=TODAY(),H21&lt;&gt;"",ISNUMBER(H21),H21&gt;=DATE(YEAR(TODAY()),MONTH(TODAY())-1,1),I21&lt;&gt;"",ISNUMBER(I21),I21+365&gt;=TODAY(),K21="APTO"),"✔ ACCESO PERMITIDO","✘ SIN ACCESO")</f>
+        <f>IF(AND(F21&lt;&gt;"",ISNUMBER(F21),F21&gt;=TODAY(),H21&lt;&gt;"",ISNUMBER(H21),H21&gt;=DATE(YEAR(TODAY()),MONTH(TODAY())-1,1),I21&lt;&gt;"",ISNUMBER(I21),I21&gt;=TODAY(),K21="APTO"),"✔ ACCESO PERMITIDO","✘ SIN ACCESO")</f>
         <v/>
       </c>
       <c r="M21" s="12" t="n"/>
@@ -1579,18 +1579,18 @@
       <c r="E22" s="11" t="n"/>
       <c r="F22" s="12" t="n"/>
       <c r="G22" s="13">
-        <f>IF(F22="","",IF(F22+365&gt;=TODAY(),"✔ Vigente","✘ Vencido"))</f>
+        <f>IF(F22="","",IF(F22&gt;=TODAY(),"✔ Vigente","✘ Vencido"))</f>
         <v/>
       </c>
       <c r="H22" s="12" t="n"/>
       <c r="I22" s="12" t="n"/>
       <c r="J22" s="13">
-        <f>IF(I22="","",IF(I22+365&gt;=TODAY(),"✔ Vigente","✘ Vencido"))</f>
+        <f>IF(I22="","",IF(I22&gt;=TODAY(),"✔ Vigente","✘ Vencido"))</f>
         <v/>
       </c>
       <c r="K22" s="13" t="n"/>
       <c r="L22" s="14">
-        <f>IF(AND(F22&lt;&gt;"",ISNUMBER(F22),F22+365&gt;=TODAY(),H22&lt;&gt;"",ISNUMBER(H22),H22&gt;=DATE(YEAR(TODAY()),MONTH(TODAY())-1,1),I22&lt;&gt;"",ISNUMBER(I22),I22+365&gt;=TODAY(),K22="APTO"),"✔ ACCESO PERMITIDO","✘ SIN ACCESO")</f>
+        <f>IF(AND(F22&lt;&gt;"",ISNUMBER(F22),F22&gt;=TODAY(),H22&lt;&gt;"",ISNUMBER(H22),H22&gt;=DATE(YEAR(TODAY()),MONTH(TODAY())-1,1),I22&lt;&gt;"",ISNUMBER(I22),I22&gt;=TODAY(),K22="APTO"),"✔ ACCESO PERMITIDO","✘ SIN ACCESO")</f>
         <v/>
       </c>
       <c r="M22" s="12" t="n"/>
@@ -1611,18 +1611,18 @@
       <c r="E23" s="11" t="n"/>
       <c r="F23" s="12" t="n"/>
       <c r="G23" s="13">
-        <f>IF(F23="","",IF(F23+365&gt;=TODAY(),"✔ Vigente","✘ Vencido"))</f>
+        <f>IF(F23="","",IF(F23&gt;=TODAY(),"✔ Vigente","✘ Vencido"))</f>
         <v/>
       </c>
       <c r="H23" s="12" t="n"/>
       <c r="I23" s="12" t="n"/>
       <c r="J23" s="13">
-        <f>IF(I23="","",IF(I23+365&gt;=TODAY(),"✔ Vigente","✘ Vencido"))</f>
+        <f>IF(I23="","",IF(I23&gt;=TODAY(),"✔ Vigente","✘ Vencido"))</f>
         <v/>
       </c>
       <c r="K23" s="13" t="n"/>
       <c r="L23" s="16">
-        <f>IF(AND(F23&lt;&gt;"",ISNUMBER(F23),F23+365&gt;=TODAY(),H23&lt;&gt;"",ISNUMBER(H23),H23&gt;=DATE(YEAR(TODAY()),MONTH(TODAY())-1,1),I23&lt;&gt;"",ISNUMBER(I23),I23+365&gt;=TODAY(),K23="APTO"),"✔ ACCESO PERMITIDO","✘ SIN ACCESO")</f>
+        <f>IF(AND(F23&lt;&gt;"",ISNUMBER(F23),F23&gt;=TODAY(),H23&lt;&gt;"",ISNUMBER(H23),H23&gt;=DATE(YEAR(TODAY()),MONTH(TODAY())-1,1),I23&lt;&gt;"",ISNUMBER(I23),I23&gt;=TODAY(),K23="APTO"),"✔ ACCESO PERMITIDO","✘ SIN ACCESO")</f>
         <v/>
       </c>
       <c r="M23" s="12" t="n"/>
@@ -1643,18 +1643,18 @@
       <c r="E24" s="11" t="n"/>
       <c r="F24" s="12" t="n"/>
       <c r="G24" s="13">
-        <f>IF(F24="","",IF(F24+365&gt;=TODAY(),"✔ Vigente","✘ Vencido"))</f>
+        <f>IF(F24="","",IF(F24&gt;=TODAY(),"✔ Vigente","✘ Vencido"))</f>
         <v/>
       </c>
       <c r="H24" s="12" t="n"/>
       <c r="I24" s="12" t="n"/>
       <c r="J24" s="13">
-        <f>IF(I24="","",IF(I24+365&gt;=TODAY(),"✔ Vigente","✘ Vencido"))</f>
+        <f>IF(I24="","",IF(I24&gt;=TODAY(),"✔ Vigente","✘ Vencido"))</f>
         <v/>
       </c>
       <c r="K24" s="13" t="n"/>
       <c r="L24" s="14">
-        <f>IF(AND(F24&lt;&gt;"",ISNUMBER(F24),F24+365&gt;=TODAY(),H24&lt;&gt;"",ISNUMBER(H24),H24&gt;=DATE(YEAR(TODAY()),MONTH(TODAY())-1,1),I24&lt;&gt;"",ISNUMBER(I24),I24+365&gt;=TODAY(),K24="APTO"),"✔ ACCESO PERMITIDO","✘ SIN ACCESO")</f>
+        <f>IF(AND(F24&lt;&gt;"",ISNUMBER(F24),F24&gt;=TODAY(),H24&lt;&gt;"",ISNUMBER(H24),H24&gt;=DATE(YEAR(TODAY()),MONTH(TODAY())-1,1),I24&lt;&gt;"",ISNUMBER(I24),I24&gt;=TODAY(),K24="APTO"),"✔ ACCESO PERMITIDO","✘ SIN ACCESO")</f>
         <v/>
       </c>
       <c r="M24" s="12" t="n"/>
@@ -1675,18 +1675,18 @@
       <c r="E25" s="11" t="n"/>
       <c r="F25" s="12" t="n"/>
       <c r="G25" s="13">
-        <f>IF(F25="","",IF(F25+365&gt;=TODAY(),"✔ Vigente","✘ Vencido"))</f>
+        <f>IF(F25="","",IF(F25&gt;=TODAY(),"✔ Vigente","✘ Vencido"))</f>
         <v/>
       </c>
       <c r="H25" s="12" t="n"/>
       <c r="I25" s="12" t="n"/>
       <c r="J25" s="13">
-        <f>IF(I25="","",IF(I25+365&gt;=TODAY(),"✔ Vigente","✘ Vencido"))</f>
+        <f>IF(I25="","",IF(I25&gt;=TODAY(),"✔ Vigente","✘ Vencido"))</f>
         <v/>
       </c>
       <c r="K25" s="13" t="n"/>
       <c r="L25" s="16">
-        <f>IF(AND(F25&lt;&gt;"",ISNUMBER(F25),F25+365&gt;=TODAY(),H25&lt;&gt;"",ISNUMBER(H25),H25&gt;=DATE(YEAR(TODAY()),MONTH(TODAY())-1,1),I25&lt;&gt;"",ISNUMBER(I25),I25+365&gt;=TODAY(),K25="APTO"),"✔ ACCESO PERMITIDO","✘ SIN ACCESO")</f>
+        <f>IF(AND(F25&lt;&gt;"",ISNUMBER(F25),F25&gt;=TODAY(),H25&lt;&gt;"",ISNUMBER(H25),H25&gt;=DATE(YEAR(TODAY()),MONTH(TODAY())-1,1),I25&lt;&gt;"",ISNUMBER(I25),I25&gt;=TODAY(),K25="APTO"),"✔ ACCESO PERMITIDO","✘ SIN ACCESO")</f>
         <v/>
       </c>
       <c r="M25" s="12" t="n"/>
@@ -1707,18 +1707,18 @@
       <c r="E26" s="11" t="n"/>
       <c r="F26" s="12" t="n"/>
       <c r="G26" s="13">
-        <f>IF(F26="","",IF(F26+365&gt;=TODAY(),"✔ Vigente","✘ Vencido"))</f>
+        <f>IF(F26="","",IF(F26&gt;=TODAY(),"✔ Vigente","✘ Vencido"))</f>
         <v/>
       </c>
       <c r="H26" s="12" t="n"/>
       <c r="I26" s="12" t="n"/>
       <c r="J26" s="13">
-        <f>IF(I26="","",IF(I26+365&gt;=TODAY(),"✔ Vigente","✘ Vencido"))</f>
+        <f>IF(I26="","",IF(I26&gt;=TODAY(),"✔ Vigente","✘ Vencido"))</f>
         <v/>
       </c>
       <c r="K26" s="13" t="n"/>
       <c r="L26" s="14">
-        <f>IF(AND(F26&lt;&gt;"",ISNUMBER(F26),F26+365&gt;=TODAY(),H26&lt;&gt;"",ISNUMBER(H26),H26&gt;=DATE(YEAR(TODAY()),MONTH(TODAY())-1,1),I26&lt;&gt;"",ISNUMBER(I26),I26+365&gt;=TODAY(),K26="APTO"),"✔ ACCESO PERMITIDO","✘ SIN ACCESO")</f>
+        <f>IF(AND(F26&lt;&gt;"",ISNUMBER(F26),F26&gt;=TODAY(),H26&lt;&gt;"",ISNUMBER(H26),H26&gt;=DATE(YEAR(TODAY()),MONTH(TODAY())-1,1),I26&lt;&gt;"",ISNUMBER(I26),I26&gt;=TODAY(),K26="APTO"),"✔ ACCESO PERMITIDO","✘ SIN ACCESO")</f>
         <v/>
       </c>
       <c r="M26" s="12" t="n"/>
@@ -1739,18 +1739,18 @@
       <c r="E27" s="11" t="n"/>
       <c r="F27" s="12" t="n"/>
       <c r="G27" s="13">
-        <f>IF(F27="","",IF(F27+365&gt;=TODAY(),"✔ Vigente","✘ Vencido"))</f>
+        <f>IF(F27="","",IF(F27&gt;=TODAY(),"✔ Vigente","✘ Vencido"))</f>
         <v/>
       </c>
       <c r="H27" s="12" t="n"/>
       <c r="I27" s="12" t="n"/>
       <c r="J27" s="13">
-        <f>IF(I27="","",IF(I27+365&gt;=TODAY(),"✔ Vigente","✘ Vencido"))</f>
+        <f>IF(I27="","",IF(I27&gt;=TODAY(),"✔ Vigente","✘ Vencido"))</f>
         <v/>
       </c>
       <c r="K27" s="13" t="n"/>
       <c r="L27" s="16">
-        <f>IF(AND(F27&lt;&gt;"",ISNUMBER(F27),F27+365&gt;=TODAY(),H27&lt;&gt;"",ISNUMBER(H27),H27&gt;=DATE(YEAR(TODAY()),MONTH(TODAY())-1,1),I27&lt;&gt;"",ISNUMBER(I27),I27+365&gt;=TODAY(),K27="APTO"),"✔ ACCESO PERMITIDO","✘ SIN ACCESO")</f>
+        <f>IF(AND(F27&lt;&gt;"",ISNUMBER(F27),F27&gt;=TODAY(),H27&lt;&gt;"",ISNUMBER(H27),H27&gt;=DATE(YEAR(TODAY()),MONTH(TODAY())-1,1),I27&lt;&gt;"",ISNUMBER(I27),I27&gt;=TODAY(),K27="APTO"),"✔ ACCESO PERMITIDO","✘ SIN ACCESO")</f>
         <v/>
       </c>
       <c r="M27" s="12" t="n"/>
@@ -1771,18 +1771,18 @@
       <c r="E28" s="11" t="n"/>
       <c r="F28" s="12" t="n"/>
       <c r="G28" s="13">
-        <f>IF(F28="","",IF(F28+365&gt;=TODAY(),"✔ Vigente","✘ Vencido"))</f>
+        <f>IF(F28="","",IF(F28&gt;=TODAY(),"✔ Vigente","✘ Vencido"))</f>
         <v/>
       </c>
       <c r="H28" s="12" t="n"/>
       <c r="I28" s="12" t="n"/>
       <c r="J28" s="13">
-        <f>IF(I28="","",IF(I28+365&gt;=TODAY(),"✔ Vigente","✘ Vencido"))</f>
+        <f>IF(I28="","",IF(I28&gt;=TODAY(),"✔ Vigente","✘ Vencido"))</f>
         <v/>
       </c>
       <c r="K28" s="13" t="n"/>
       <c r="L28" s="14">
-        <f>IF(AND(F28&lt;&gt;"",ISNUMBER(F28),F28+365&gt;=TODAY(),H28&lt;&gt;"",ISNUMBER(H28),H28&gt;=DATE(YEAR(TODAY()),MONTH(TODAY())-1,1),I28&lt;&gt;"",ISNUMBER(I28),I28+365&gt;=TODAY(),K28="APTO"),"✔ ACCESO PERMITIDO","✘ SIN ACCESO")</f>
+        <f>IF(AND(F28&lt;&gt;"",ISNUMBER(F28),F28&gt;=TODAY(),H28&lt;&gt;"",ISNUMBER(H28),H28&gt;=DATE(YEAR(TODAY()),MONTH(TODAY())-1,1),I28&lt;&gt;"",ISNUMBER(I28),I28&gt;=TODAY(),K28="APTO"),"✔ ACCESO PERMITIDO","✘ SIN ACCESO")</f>
         <v/>
       </c>
       <c r="M28" s="12" t="n"/>
@@ -1803,18 +1803,18 @@
       <c r="E29" s="11" t="n"/>
       <c r="F29" s="12" t="n"/>
       <c r="G29" s="13">
-        <f>IF(F29="","",IF(F29+365&gt;=TODAY(),"✔ Vigente","✘ Vencido"))</f>
+        <f>IF(F29="","",IF(F29&gt;=TODAY(),"✔ Vigente","✘ Vencido"))</f>
         <v/>
       </c>
       <c r="H29" s="12" t="n"/>
       <c r="I29" s="12" t="n"/>
       <c r="J29" s="13">
-        <f>IF(I29="","",IF(I29+365&gt;=TODAY(),"✔ Vigente","✘ Vencido"))</f>
+        <f>IF(I29="","",IF(I29&gt;=TODAY(),"✔ Vigente","✘ Vencido"))</f>
         <v/>
       </c>
       <c r="K29" s="13" t="n"/>
       <c r="L29" s="16">
-        <f>IF(AND(F29&lt;&gt;"",ISNUMBER(F29),F29+365&gt;=TODAY(),H29&lt;&gt;"",ISNUMBER(H29),H29&gt;=DATE(YEAR(TODAY()),MONTH(TODAY())-1,1),I29&lt;&gt;"",ISNUMBER(I29),I29+365&gt;=TODAY(),K29="APTO"),"✔ ACCESO PERMITIDO","✘ SIN ACCESO")</f>
+        <f>IF(AND(F29&lt;&gt;"",ISNUMBER(F29),F29&gt;=TODAY(),H29&lt;&gt;"",ISNUMBER(H29),H29&gt;=DATE(YEAR(TODAY()),MONTH(TODAY())-1,1),I29&lt;&gt;"",ISNUMBER(I29),I29&gt;=TODAY(),K29="APTO"),"✔ ACCESO PERMITIDO","✘ SIN ACCESO")</f>
         <v/>
       </c>
       <c r="M29" s="12" t="n"/>
@@ -1835,18 +1835,18 @@
       <c r="E30" s="11" t="n"/>
       <c r="F30" s="12" t="n"/>
       <c r="G30" s="13">
-        <f>IF(F30="","",IF(F30+365&gt;=TODAY(),"✔ Vigente","✘ Vencido"))</f>
+        <f>IF(F30="","",IF(F30&gt;=TODAY(),"✔ Vigente","✘ Vencido"))</f>
         <v/>
       </c>
       <c r="H30" s="12" t="n"/>
       <c r="I30" s="12" t="n"/>
       <c r="J30" s="13">
-        <f>IF(I30="","",IF(I30+365&gt;=TODAY(),"✔ Vigente","✘ Vencido"))</f>
+        <f>IF(I30="","",IF(I30&gt;=TODAY(),"✔ Vigente","✘ Vencido"))</f>
         <v/>
       </c>
       <c r="K30" s="13" t="n"/>
       <c r="L30" s="14">
-        <f>IF(AND(F30&lt;&gt;"",ISNUMBER(F30),F30+365&gt;=TODAY(),H30&lt;&gt;"",ISNUMBER(H30),H30&gt;=DATE(YEAR(TODAY()),MONTH(TODAY())-1,1),I30&lt;&gt;"",ISNUMBER(I30),I30+365&gt;=TODAY(),K30="APTO"),"✔ ACCESO PERMITIDO","✘ SIN ACCESO")</f>
+        <f>IF(AND(F30&lt;&gt;"",ISNUMBER(F30),F30&gt;=TODAY(),H30&lt;&gt;"",ISNUMBER(H30),H30&gt;=DATE(YEAR(TODAY()),MONTH(TODAY())-1,1),I30&lt;&gt;"",ISNUMBER(I30),I30&gt;=TODAY(),K30="APTO"),"✔ ACCESO PERMITIDO","✘ SIN ACCESO")</f>
         <v/>
       </c>
       <c r="M30" s="12" t="n"/>
@@ -1867,18 +1867,18 @@
       <c r="E31" s="11" t="n"/>
       <c r="F31" s="12" t="n"/>
       <c r="G31" s="13">
-        <f>IF(F31="","",IF(F31+365&gt;=TODAY(),"✔ Vigente","✘ Vencido"))</f>
+        <f>IF(F31="","",IF(F31&gt;=TODAY(),"✔ Vigente","✘ Vencido"))</f>
         <v/>
       </c>
       <c r="H31" s="12" t="n"/>
       <c r="I31" s="12" t="n"/>
       <c r="J31" s="13">
-        <f>IF(I31="","",IF(I31+365&gt;=TODAY(),"✔ Vigente","✘ Vencido"))</f>
+        <f>IF(I31="","",IF(I31&gt;=TODAY(),"✔ Vigente","✘ Vencido"))</f>
         <v/>
       </c>
       <c r="K31" s="13" t="n"/>
       <c r="L31" s="16">
-        <f>IF(AND(F31&lt;&gt;"",ISNUMBER(F31),F31+365&gt;=TODAY(),H31&lt;&gt;"",ISNUMBER(H31),H31&gt;=DATE(YEAR(TODAY()),MONTH(TODAY())-1,1),I31&lt;&gt;"",ISNUMBER(I31),I31+365&gt;=TODAY(),K31="APTO"),"✔ ACCESO PERMITIDO","✘ SIN ACCESO")</f>
+        <f>IF(AND(F31&lt;&gt;"",ISNUMBER(F31),F31&gt;=TODAY(),H31&lt;&gt;"",ISNUMBER(H31),H31&gt;=DATE(YEAR(TODAY()),MONTH(TODAY())-1,1),I31&lt;&gt;"",ISNUMBER(I31),I31&gt;=TODAY(),K31="APTO"),"✔ ACCESO PERMITIDO","✘ SIN ACCESO")</f>
         <v/>
       </c>
       <c r="M31" s="12" t="n"/>
@@ -1899,18 +1899,18 @@
       <c r="E32" s="11" t="n"/>
       <c r="F32" s="12" t="n"/>
       <c r="G32" s="13">
-        <f>IF(F32="","",IF(F32+365&gt;=TODAY(),"✔ Vigente","✘ Vencido"))</f>
+        <f>IF(F32="","",IF(F32&gt;=TODAY(),"✔ Vigente","✘ Vencido"))</f>
         <v/>
       </c>
       <c r="H32" s="12" t="n"/>
       <c r="I32" s="12" t="n"/>
       <c r="J32" s="13">
-        <f>IF(I32="","",IF(I32+365&gt;=TODAY(),"✔ Vigente","✘ Vencido"))</f>
+        <f>IF(I32="","",IF(I32&gt;=TODAY(),"✔ Vigente","✘ Vencido"))</f>
         <v/>
       </c>
       <c r="K32" s="13" t="n"/>
       <c r="L32" s="14">
-        <f>IF(AND(F32&lt;&gt;"",ISNUMBER(F32),F32+365&gt;=TODAY(),H32&lt;&gt;"",ISNUMBER(H32),H32&gt;=DATE(YEAR(TODAY()),MONTH(TODAY())-1,1),I32&lt;&gt;"",ISNUMBER(I32),I32+365&gt;=TODAY(),K32="APTO"),"✔ ACCESO PERMITIDO","✘ SIN ACCESO")</f>
+        <f>IF(AND(F32&lt;&gt;"",ISNUMBER(F32),F32&gt;=TODAY(),H32&lt;&gt;"",ISNUMBER(H32),H32&gt;=DATE(YEAR(TODAY()),MONTH(TODAY())-1,1),I32&lt;&gt;"",ISNUMBER(I32),I32&gt;=TODAY(),K32="APTO"),"✔ ACCESO PERMITIDO","✘ SIN ACCESO")</f>
         <v/>
       </c>
       <c r="M32" s="12" t="n"/>
@@ -1931,18 +1931,18 @@
       <c r="E33" s="11" t="n"/>
       <c r="F33" s="12" t="n"/>
       <c r="G33" s="13">
-        <f>IF(F33="","",IF(F33+365&gt;=TODAY(),"✔ Vigente","✘ Vencido"))</f>
+        <f>IF(F33="","",IF(F33&gt;=TODAY(),"✔ Vigente","✘ Vencido"))</f>
         <v/>
       </c>
       <c r="H33" s="12" t="n"/>
       <c r="I33" s="12" t="n"/>
       <c r="J33" s="13">
-        <f>IF(I33="","",IF(I33+365&gt;=TODAY(),"✔ Vigente","✘ Vencido"))</f>
+        <f>IF(I33="","",IF(I33&gt;=TODAY(),"✔ Vigente","✘ Vencido"))</f>
         <v/>
       </c>
       <c r="K33" s="13" t="n"/>
       <c r="L33" s="16">
-        <f>IF(AND(F33&lt;&gt;"",ISNUMBER(F33),F33+365&gt;=TODAY(),H33&lt;&gt;"",ISNUMBER(H33),H33&gt;=DATE(YEAR(TODAY()),MONTH(TODAY())-1,1),I33&lt;&gt;"",ISNUMBER(I33),I33+365&gt;=TODAY(),K33="APTO"),"✔ ACCESO PERMITIDO","✘ SIN ACCESO")</f>
+        <f>IF(AND(F33&lt;&gt;"",ISNUMBER(F33),F33&gt;=TODAY(),H33&lt;&gt;"",ISNUMBER(H33),H33&gt;=DATE(YEAR(TODAY()),MONTH(TODAY())-1,1),I33&lt;&gt;"",ISNUMBER(I33),I33&gt;=TODAY(),K33="APTO"),"✔ ACCESO PERMITIDO","✘ SIN ACCESO")</f>
         <v/>
       </c>
       <c r="M33" s="12" t="n"/>
@@ -1963,18 +1963,18 @@
       <c r="E34" s="11" t="n"/>
       <c r="F34" s="12" t="n"/>
       <c r="G34" s="13">
-        <f>IF(F34="","",IF(F34+365&gt;=TODAY(),"✔ Vigente","✘ Vencido"))</f>
+        <f>IF(F34="","",IF(F34&gt;=TODAY(),"✔ Vigente","✘ Vencido"))</f>
         <v/>
       </c>
       <c r="H34" s="12" t="n"/>
       <c r="I34" s="12" t="n"/>
       <c r="J34" s="13">
-        <f>IF(I34="","",IF(I34+365&gt;=TODAY(),"✔ Vigente","✘ Vencido"))</f>
+        <f>IF(I34="","",IF(I34&gt;=TODAY(),"✔ Vigente","✘ Vencido"))</f>
         <v/>
       </c>
       <c r="K34" s="13" t="n"/>
       <c r="L34" s="14">
-        <f>IF(AND(F34&lt;&gt;"",ISNUMBER(F34),F34+365&gt;=TODAY(),H34&lt;&gt;"",ISNUMBER(H34),H34&gt;=DATE(YEAR(TODAY()),MONTH(TODAY())-1,1),I34&lt;&gt;"",ISNUMBER(I34),I34+365&gt;=TODAY(),K34="APTO"),"✔ ACCESO PERMITIDO","✘ SIN ACCESO")</f>
+        <f>IF(AND(F34&lt;&gt;"",ISNUMBER(F34),F34&gt;=TODAY(),H34&lt;&gt;"",ISNUMBER(H34),H34&gt;=DATE(YEAR(TODAY()),MONTH(TODAY())-1,1),I34&lt;&gt;"",ISNUMBER(I34),I34&gt;=TODAY(),K34="APTO"),"✔ ACCESO PERMITIDO","✘ SIN ACCESO")</f>
         <v/>
       </c>
       <c r="M34" s="12" t="n"/>
@@ -1995,18 +1995,18 @@
       <c r="E35" s="11" t="n"/>
       <c r="F35" s="12" t="n"/>
       <c r="G35" s="13">
-        <f>IF(F35="","",IF(F35+365&gt;=TODAY(),"✔ Vigente","✘ Vencido"))</f>
+        <f>IF(F35="","",IF(F35&gt;=TODAY(),"✔ Vigente","✘ Vencido"))</f>
         <v/>
       </c>
       <c r="H35" s="12" t="n"/>
       <c r="I35" s="12" t="n"/>
       <c r="J35" s="13">
-        <f>IF(I35="","",IF(I35+365&gt;=TODAY(),"✔ Vigente","✘ Vencido"))</f>
+        <f>IF(I35="","",IF(I35&gt;=TODAY(),"✔ Vigente","✘ Vencido"))</f>
         <v/>
       </c>
       <c r="K35" s="13" t="n"/>
       <c r="L35" s="16">
-        <f>IF(AND(F35&lt;&gt;"",ISNUMBER(F35),F35+365&gt;=TODAY(),H35&lt;&gt;"",ISNUMBER(H35),H35&gt;=DATE(YEAR(TODAY()),MONTH(TODAY())-1,1),I35&lt;&gt;"",ISNUMBER(I35),I35+365&gt;=TODAY(),K35="APTO"),"✔ ACCESO PERMITIDO","✘ SIN ACCESO")</f>
+        <f>IF(AND(F35&lt;&gt;"",ISNUMBER(F35),F35&gt;=TODAY(),H35&lt;&gt;"",ISNUMBER(H35),H35&gt;=DATE(YEAR(TODAY()),MONTH(TODAY())-1,1),I35&lt;&gt;"",ISNUMBER(I35),I35&gt;=TODAY(),K35="APTO"),"✔ ACCESO PERMITIDO","✘ SIN ACCESO")</f>
         <v/>
       </c>
       <c r="M35" s="12" t="n"/>
@@ -2027,18 +2027,18 @@
       <c r="E36" s="11" t="n"/>
       <c r="F36" s="12" t="n"/>
       <c r="G36" s="13">
-        <f>IF(F36="","",IF(F36+365&gt;=TODAY(),"✔ Vigente","✘ Vencido"))</f>
+        <f>IF(F36="","",IF(F36&gt;=TODAY(),"✔ Vigente","✘ Vencido"))</f>
         <v/>
       </c>
       <c r="H36" s="12" t="n"/>
       <c r="I36" s="12" t="n"/>
       <c r="J36" s="13">
-        <f>IF(I36="","",IF(I36+365&gt;=TODAY(),"✔ Vigente","✘ Vencido"))</f>
+        <f>IF(I36="","",IF(I36&gt;=TODAY(),"✔ Vigente","✘ Vencido"))</f>
         <v/>
       </c>
       <c r="K36" s="13" t="n"/>
       <c r="L36" s="14">
-        <f>IF(AND(F36&lt;&gt;"",ISNUMBER(F36),F36+365&gt;=TODAY(),H36&lt;&gt;"",ISNUMBER(H36),H36&gt;=DATE(YEAR(TODAY()),MONTH(TODAY())-1,1),I36&lt;&gt;"",ISNUMBER(I36),I36+365&gt;=TODAY(),K36="APTO"),"✔ ACCESO PERMITIDO","✘ SIN ACCESO")</f>
+        <f>IF(AND(F36&lt;&gt;"",ISNUMBER(F36),F36&gt;=TODAY(),H36&lt;&gt;"",ISNUMBER(H36),H36&gt;=DATE(YEAR(TODAY()),MONTH(TODAY())-1,1),I36&lt;&gt;"",ISNUMBER(I36),I36&gt;=TODAY(),K36="APTO"),"✔ ACCESO PERMITIDO","✘ SIN ACCESO")</f>
         <v/>
       </c>
       <c r="M36" s="12" t="n"/>
@@ -2059,18 +2059,18 @@
       <c r="E37" s="11" t="n"/>
       <c r="F37" s="12" t="n"/>
       <c r="G37" s="13">
-        <f>IF(F37="","",IF(F37+365&gt;=TODAY(),"✔ Vigente","✘ Vencido"))</f>
+        <f>IF(F37="","",IF(F37&gt;=TODAY(),"✔ Vigente","✘ Vencido"))</f>
         <v/>
       </c>
       <c r="H37" s="12" t="n"/>
       <c r="I37" s="12" t="n"/>
       <c r="J37" s="13">
-        <f>IF(I37="","",IF(I37+365&gt;=TODAY(),"✔ Vigente","✘ Vencido"))</f>
+        <f>IF(I37="","",IF(I37&gt;=TODAY(),"✔ Vigente","✘ Vencido"))</f>
         <v/>
       </c>
       <c r="K37" s="13" t="n"/>
       <c r="L37" s="16">
-        <f>IF(AND(F37&lt;&gt;"",ISNUMBER(F37),F37+365&gt;=TODAY(),H37&lt;&gt;"",ISNUMBER(H37),H37&gt;=DATE(YEAR(TODAY()),MONTH(TODAY())-1,1),I37&lt;&gt;"",ISNUMBER(I37),I37+365&gt;=TODAY(),K37="APTO"),"✔ ACCESO PERMITIDO","✘ SIN ACCESO")</f>
+        <f>IF(AND(F37&lt;&gt;"",ISNUMBER(F37),F37&gt;=TODAY(),H37&lt;&gt;"",ISNUMBER(H37),H37&gt;=DATE(YEAR(TODAY()),MONTH(TODAY())-1,1),I37&lt;&gt;"",ISNUMBER(I37),I37&gt;=TODAY(),K37="APTO"),"✔ ACCESO PERMITIDO","✘ SIN ACCESO")</f>
         <v/>
       </c>
       <c r="M37" s="12" t="n"/>
@@ -2091,18 +2091,18 @@
       <c r="E38" s="11" t="n"/>
       <c r="F38" s="12" t="n"/>
       <c r="G38" s="13">
-        <f>IF(F38="","",IF(F38+365&gt;=TODAY(),"✔ Vigente","✘ Vencido"))</f>
+        <f>IF(F38="","",IF(F38&gt;=TODAY(),"✔ Vigente","✘ Vencido"))</f>
         <v/>
       </c>
       <c r="H38" s="12" t="n"/>
       <c r="I38" s="12" t="n"/>
       <c r="J38" s="13">
-        <f>IF(I38="","",IF(I38+365&gt;=TODAY(),"✔ Vigente","✘ Vencido"))</f>
+        <f>IF(I38="","",IF(I38&gt;=TODAY(),"✔ Vigente","✘ Vencido"))</f>
         <v/>
       </c>
       <c r="K38" s="13" t="n"/>
       <c r="L38" s="14">
-        <f>IF(AND(F38&lt;&gt;"",ISNUMBER(F38),F38+365&gt;=TODAY(),H38&lt;&gt;"",ISNUMBER(H38),H38&gt;=DATE(YEAR(TODAY()),MONTH(TODAY())-1,1),I38&lt;&gt;"",ISNUMBER(I38),I38+365&gt;=TODAY(),K38="APTO"),"✔ ACCESO PERMITIDO","✘ SIN ACCESO")</f>
+        <f>IF(AND(F38&lt;&gt;"",ISNUMBER(F38),F38&gt;=TODAY(),H38&lt;&gt;"",ISNUMBER(H38),H38&gt;=DATE(YEAR(TODAY()),MONTH(TODAY())-1,1),I38&lt;&gt;"",ISNUMBER(I38),I38&gt;=TODAY(),K38="APTO"),"✔ ACCESO PERMITIDO","✘ SIN ACCESO")</f>
         <v/>
       </c>
       <c r="M38" s="12" t="n"/>
@@ -2123,18 +2123,18 @@
       <c r="E39" s="11" t="n"/>
       <c r="F39" s="12" t="n"/>
       <c r="G39" s="13">
-        <f>IF(F39="","",IF(F39+365&gt;=TODAY(),"✔ Vigente","✘ Vencido"))</f>
+        <f>IF(F39="","",IF(F39&gt;=TODAY(),"✔ Vigente","✘ Vencido"))</f>
         <v/>
       </c>
       <c r="H39" s="12" t="n"/>
       <c r="I39" s="12" t="n"/>
       <c r="J39" s="13">
-        <f>IF(I39="","",IF(I39+365&gt;=TODAY(),"✔ Vigente","✘ Vencido"))</f>
+        <f>IF(I39="","",IF(I39&gt;=TODAY(),"✔ Vigente","✘ Vencido"))</f>
         <v/>
       </c>
       <c r="K39" s="13" t="n"/>
       <c r="L39" s="16">
-        <f>IF(AND(F39&lt;&gt;"",ISNUMBER(F39),F39+365&gt;=TODAY(),H39&lt;&gt;"",ISNUMBER(H39),H39&gt;=DATE(YEAR(TODAY()),MONTH(TODAY())-1,1),I39&lt;&gt;"",ISNUMBER(I39),I39+365&gt;=TODAY(),K39="APTO"),"✔ ACCESO PERMITIDO","✘ SIN ACCESO")</f>
+        <f>IF(AND(F39&lt;&gt;"",ISNUMBER(F39),F39&gt;=TODAY(),H39&lt;&gt;"",ISNUMBER(H39),H39&gt;=DATE(YEAR(TODAY()),MONTH(TODAY())-1,1),I39&lt;&gt;"",ISNUMBER(I39),I39&gt;=TODAY(),K39="APTO"),"✔ ACCESO PERMITIDO","✘ SIN ACCESO")</f>
         <v/>
       </c>
       <c r="M39" s="12" t="n"/>
@@ -2155,18 +2155,18 @@
       <c r="E40" s="11" t="n"/>
       <c r="F40" s="12" t="n"/>
       <c r="G40" s="13">
-        <f>IF(F40="","",IF(F40+365&gt;=TODAY(),"✔ Vigente","✘ Vencido"))</f>
+        <f>IF(F40="","",IF(F40&gt;=TODAY(),"✔ Vigente","✘ Vencido"))</f>
         <v/>
       </c>
       <c r="H40" s="12" t="n"/>
       <c r="I40" s="12" t="n"/>
       <c r="J40" s="13">
-        <f>IF(I40="","",IF(I40+365&gt;=TODAY(),"✔ Vigente","✘ Vencido"))</f>
+        <f>IF(I40="","",IF(I40&gt;=TODAY(),"✔ Vigente","✘ Vencido"))</f>
         <v/>
       </c>
       <c r="K40" s="13" t="n"/>
       <c r="L40" s="14">
-        <f>IF(AND(F40&lt;&gt;"",ISNUMBER(F40),F40+365&gt;=TODAY(),H40&lt;&gt;"",ISNUMBER(H40),H40&gt;=DATE(YEAR(TODAY()),MONTH(TODAY())-1,1),I40&lt;&gt;"",ISNUMBER(I40),I40+365&gt;=TODAY(),K40="APTO"),"✔ ACCESO PERMITIDO","✘ SIN ACCESO")</f>
+        <f>IF(AND(F40&lt;&gt;"",ISNUMBER(F40),F40&gt;=TODAY(),H40&lt;&gt;"",ISNUMBER(H40),H40&gt;=DATE(YEAR(TODAY()),MONTH(TODAY())-1,1),I40&lt;&gt;"",ISNUMBER(I40),I40&gt;=TODAY(),K40="APTO"),"✔ ACCESO PERMITIDO","✘ SIN ACCESO")</f>
         <v/>
       </c>
       <c r="M40" s="12" t="n"/>
@@ -2187,18 +2187,18 @@
       <c r="E41" s="11" t="n"/>
       <c r="F41" s="12" t="n"/>
       <c r="G41" s="13">
-        <f>IF(F41="","",IF(F41+365&gt;=TODAY(),"✔ Vigente","✘ Vencido"))</f>
+        <f>IF(F41="","",IF(F41&gt;=TODAY(),"✔ Vigente","✘ Vencido"))</f>
         <v/>
       </c>
       <c r="H41" s="12" t="n"/>
       <c r="I41" s="12" t="n"/>
       <c r="J41" s="13">
-        <f>IF(I41="","",IF(I41+365&gt;=TODAY(),"✔ Vigente","✘ Vencido"))</f>
+        <f>IF(I41="","",IF(I41&gt;=TODAY(),"✔ Vigente","✘ Vencido"))</f>
         <v/>
       </c>
       <c r="K41" s="13" t="n"/>
       <c r="L41" s="16">
-        <f>IF(AND(F41&lt;&gt;"",ISNUMBER(F41),F41+365&gt;=TODAY(),H41&lt;&gt;"",ISNUMBER(H41),H41&gt;=DATE(YEAR(TODAY()),MONTH(TODAY())-1,1),I41&lt;&gt;"",ISNUMBER(I41),I41+365&gt;=TODAY(),K41="APTO"),"✔ ACCESO PERMITIDO","✘ SIN ACCESO")</f>
+        <f>IF(AND(F41&lt;&gt;"",ISNUMBER(F41),F41&gt;=TODAY(),H41&lt;&gt;"",ISNUMBER(H41),H41&gt;=DATE(YEAR(TODAY()),MONTH(TODAY())-1,1),I41&lt;&gt;"",ISNUMBER(I41),I41&gt;=TODAY(),K41="APTO"),"✔ ACCESO PERMITIDO","✘ SIN ACCESO")</f>
         <v/>
       </c>
       <c r="M41" s="12" t="n"/>
@@ -2219,18 +2219,18 @@
       <c r="E42" s="11" t="n"/>
       <c r="F42" s="12" t="n"/>
       <c r="G42" s="13">
-        <f>IF(F42="","",IF(F42+365&gt;=TODAY(),"✔ Vigente","✘ Vencido"))</f>
+        <f>IF(F42="","",IF(F42&gt;=TODAY(),"✔ Vigente","✘ Vencido"))</f>
         <v/>
       </c>
       <c r="H42" s="12" t="n"/>
       <c r="I42" s="12" t="n"/>
       <c r="J42" s="13">
-        <f>IF(I42="","",IF(I42+365&gt;=TODAY(),"✔ Vigente","✘ Vencido"))</f>
+        <f>IF(I42="","",IF(I42&gt;=TODAY(),"✔ Vigente","✘ Vencido"))</f>
         <v/>
       </c>
       <c r="K42" s="13" t="n"/>
       <c r="L42" s="14">
-        <f>IF(AND(F42&lt;&gt;"",ISNUMBER(F42),F42+365&gt;=TODAY(),H42&lt;&gt;"",ISNUMBER(H42),H42&gt;=DATE(YEAR(TODAY()),MONTH(TODAY())-1,1),I42&lt;&gt;"",ISNUMBER(I42),I42+365&gt;=TODAY(),K42="APTO"),"✔ ACCESO PERMITIDO","✘ SIN ACCESO")</f>
+        <f>IF(AND(F42&lt;&gt;"",ISNUMBER(F42),F42&gt;=TODAY(),H42&lt;&gt;"",ISNUMBER(H42),H42&gt;=DATE(YEAR(TODAY()),MONTH(TODAY())-1,1),I42&lt;&gt;"",ISNUMBER(I42),I42&gt;=TODAY(),K42="APTO"),"✔ ACCESO PERMITIDO","✘ SIN ACCESO")</f>
         <v/>
       </c>
       <c r="M42" s="12" t="n"/>
@@ -2251,18 +2251,18 @@
       <c r="E43" s="11" t="n"/>
       <c r="F43" s="12" t="n"/>
       <c r="G43" s="13">
-        <f>IF(F43="","",IF(F43+365&gt;=TODAY(),"✔ Vigente","✘ Vencido"))</f>
+        <f>IF(F43="","",IF(F43&gt;=TODAY(),"✔ Vigente","✘ Vencido"))</f>
         <v/>
       </c>
       <c r="H43" s="12" t="n"/>
       <c r="I43" s="12" t="n"/>
       <c r="J43" s="13">
-        <f>IF(I43="","",IF(I43+365&gt;=TODAY(),"✔ Vigente","✘ Vencido"))</f>
+        <f>IF(I43="","",IF(I43&gt;=TODAY(),"✔ Vigente","✘ Vencido"))</f>
         <v/>
       </c>
       <c r="K43" s="13" t="n"/>
       <c r="L43" s="16">
-        <f>IF(AND(F43&lt;&gt;"",ISNUMBER(F43),F43+365&gt;=TODAY(),H43&lt;&gt;"",ISNUMBER(H43),H43&gt;=DATE(YEAR(TODAY()),MONTH(TODAY())-1,1),I43&lt;&gt;"",ISNUMBER(I43),I43+365&gt;=TODAY(),K43="APTO"),"✔ ACCESO PERMITIDO","✘ SIN ACCESO")</f>
+        <f>IF(AND(F43&lt;&gt;"",ISNUMBER(F43),F43&gt;=TODAY(),H43&lt;&gt;"",ISNUMBER(H43),H43&gt;=DATE(YEAR(TODAY()),MONTH(TODAY())-1,1),I43&lt;&gt;"",ISNUMBER(I43),I43&gt;=TODAY(),K43="APTO"),"✔ ACCESO PERMITIDO","✘ SIN ACCESO")</f>
         <v/>
       </c>
       <c r="M43" s="12" t="n"/>
@@ -2283,18 +2283,18 @@
       <c r="E44" s="11" t="n"/>
       <c r="F44" s="12" t="n"/>
       <c r="G44" s="13">
-        <f>IF(F44="","",IF(F44+365&gt;=TODAY(),"✔ Vigente","✘ Vencido"))</f>
+        <f>IF(F44="","",IF(F44&gt;=TODAY(),"✔ Vigente","✘ Vencido"))</f>
         <v/>
       </c>
       <c r="H44" s="12" t="n"/>
       <c r="I44" s="12" t="n"/>
       <c r="J44" s="13">
-        <f>IF(I44="","",IF(I44+365&gt;=TODAY(),"✔ Vigente","✘ Vencido"))</f>
+        <f>IF(I44="","",IF(I44&gt;=TODAY(),"✔ Vigente","✘ Vencido"))</f>
         <v/>
       </c>
       <c r="K44" s="13" t="n"/>
       <c r="L44" s="14">
-        <f>IF(AND(F44&lt;&gt;"",ISNUMBER(F44),F44+365&gt;=TODAY(),H44&lt;&gt;"",ISNUMBER(H44),H44&gt;=DATE(YEAR(TODAY()),MONTH(TODAY())-1,1),I44&lt;&gt;"",ISNUMBER(I44),I44+365&gt;=TODAY(),K44="APTO"),"✔ ACCESO PERMITIDO","✘ SIN ACCESO")</f>
+        <f>IF(AND(F44&lt;&gt;"",ISNUMBER(F44),F44&gt;=TODAY(),H44&lt;&gt;"",ISNUMBER(H44),H44&gt;=DATE(YEAR(TODAY()),MONTH(TODAY())-1,1),I44&lt;&gt;"",ISNUMBER(I44),I44&gt;=TODAY(),K44="APTO"),"✔ ACCESO PERMITIDO","✘ SIN ACCESO")</f>
         <v/>
       </c>
       <c r="M44" s="12" t="n"/>
@@ -2315,18 +2315,18 @@
       <c r="E45" s="11" t="n"/>
       <c r="F45" s="12" t="n"/>
       <c r="G45" s="13">
-        <f>IF(F45="","",IF(F45+365&gt;=TODAY(),"✔ Vigente","✘ Vencido"))</f>
+        <f>IF(F45="","",IF(F45&gt;=TODAY(),"✔ Vigente","✘ Vencido"))</f>
         <v/>
       </c>
       <c r="H45" s="12" t="n"/>
       <c r="I45" s="12" t="n"/>
       <c r="J45" s="13">
-        <f>IF(I45="","",IF(I45+365&gt;=TODAY(),"✔ Vigente","✘ Vencido"))</f>
+        <f>IF(I45="","",IF(I45&gt;=TODAY(),"✔ Vigente","✘ Vencido"))</f>
         <v/>
       </c>
       <c r="K45" s="13" t="n"/>
       <c r="L45" s="16">
-        <f>IF(AND(F45&lt;&gt;"",ISNUMBER(F45),F45+365&gt;=TODAY(),H45&lt;&gt;"",ISNUMBER(H45),H45&gt;=DATE(YEAR(TODAY()),MONTH(TODAY())-1,1),I45&lt;&gt;"",ISNUMBER(I45),I45+365&gt;=TODAY(),K45="APTO"),"✔ ACCESO PERMITIDO","✘ SIN ACCESO")</f>
+        <f>IF(AND(F45&lt;&gt;"",ISNUMBER(F45),F45&gt;=TODAY(),H45&lt;&gt;"",ISNUMBER(H45),H45&gt;=DATE(YEAR(TODAY()),MONTH(TODAY())-1,1),I45&lt;&gt;"",ISNUMBER(I45),I45&gt;=TODAY(),K45="APTO"),"✔ ACCESO PERMITIDO","✘ SIN ACCESO")</f>
         <v/>
       </c>
       <c r="M45" s="12" t="n"/>
@@ -2347,18 +2347,18 @@
       <c r="E46" s="11" t="n"/>
       <c r="F46" s="12" t="n"/>
       <c r="G46" s="13">
-        <f>IF(F46="","",IF(F46+365&gt;=TODAY(),"✔ Vigente","✘ Vencido"))</f>
+        <f>IF(F46="","",IF(F46&gt;=TODAY(),"✔ Vigente","✘ Vencido"))</f>
         <v/>
       </c>
       <c r="H46" s="12" t="n"/>
       <c r="I46" s="12" t="n"/>
       <c r="J46" s="13">
-        <f>IF(I46="","",IF(I46+365&gt;=TODAY(),"✔ Vigente","✘ Vencido"))</f>
+        <f>IF(I46="","",IF(I46&gt;=TODAY(),"✔ Vigente","✘ Vencido"))</f>
         <v/>
       </c>
       <c r="K46" s="13" t="n"/>
       <c r="L46" s="14">
-        <f>IF(AND(F46&lt;&gt;"",ISNUMBER(F46),F46+365&gt;=TODAY(),H46&lt;&gt;"",ISNUMBER(H46),H46&gt;=DATE(YEAR(TODAY()),MONTH(TODAY())-1,1),I46&lt;&gt;"",ISNUMBER(I46),I46+365&gt;=TODAY(),K46="APTO"),"✔ ACCESO PERMITIDO","✘ SIN ACCESO")</f>
+        <f>IF(AND(F46&lt;&gt;"",ISNUMBER(F46),F46&gt;=TODAY(),H46&lt;&gt;"",ISNUMBER(H46),H46&gt;=DATE(YEAR(TODAY()),MONTH(TODAY())-1,1),I46&lt;&gt;"",ISNUMBER(I46),I46&gt;=TODAY(),K46="APTO"),"✔ ACCESO PERMITIDO","✘ SIN ACCESO")</f>
         <v/>
       </c>
       <c r="M46" s="12" t="n"/>
@@ -2379,18 +2379,18 @@
       <c r="E47" s="11" t="n"/>
       <c r="F47" s="12" t="n"/>
       <c r="G47" s="13">
-        <f>IF(F47="","",IF(F47+365&gt;=TODAY(),"✔ Vigente","✘ Vencido"))</f>
+        <f>IF(F47="","",IF(F47&gt;=TODAY(),"✔ Vigente","✘ Vencido"))</f>
         <v/>
       </c>
       <c r="H47" s="12" t="n"/>
       <c r="I47" s="12" t="n"/>
       <c r="J47" s="13">
-        <f>IF(I47="","",IF(I47+365&gt;=TODAY(),"✔ Vigente","✘ Vencido"))</f>
+        <f>IF(I47="","",IF(I47&gt;=TODAY(),"✔ Vigente","✘ Vencido"))</f>
         <v/>
       </c>
       <c r="K47" s="13" t="n"/>
       <c r="L47" s="16">
-        <f>IF(AND(F47&lt;&gt;"",ISNUMBER(F47),F47+365&gt;=TODAY(),H47&lt;&gt;"",ISNUMBER(H47),H47&gt;=DATE(YEAR(TODAY()),MONTH(TODAY())-1,1),I47&lt;&gt;"",ISNUMBER(I47),I47+365&gt;=TODAY(),K47="APTO"),"✔ ACCESO PERMITIDO","✘ SIN ACCESO")</f>
+        <f>IF(AND(F47&lt;&gt;"",ISNUMBER(F47),F47&gt;=TODAY(),H47&lt;&gt;"",ISNUMBER(H47),H47&gt;=DATE(YEAR(TODAY()),MONTH(TODAY())-1,1),I47&lt;&gt;"",ISNUMBER(I47),I47&gt;=TODAY(),K47="APTO"),"✔ ACCESO PERMITIDO","✘ SIN ACCESO")</f>
         <v/>
       </c>
       <c r="M47" s="12" t="n"/>
@@ -2411,18 +2411,18 @@
       <c r="E48" s="11" t="n"/>
       <c r="F48" s="12" t="n"/>
       <c r="G48" s="13">
-        <f>IF(F48="","",IF(F48+365&gt;=TODAY(),"✔ Vigente","✘ Vencido"))</f>
+        <f>IF(F48="","",IF(F48&gt;=TODAY(),"✔ Vigente","✘ Vencido"))</f>
         <v/>
       </c>
       <c r="H48" s="12" t="n"/>
       <c r="I48" s="12" t="n"/>
       <c r="J48" s="13">
-        <f>IF(I48="","",IF(I48+365&gt;=TODAY(),"✔ Vigente","✘ Vencido"))</f>
+        <f>IF(I48="","",IF(I48&gt;=TODAY(),"✔ Vigente","✘ Vencido"))</f>
         <v/>
       </c>
       <c r="K48" s="13" t="n"/>
       <c r="L48" s="14">
-        <f>IF(AND(F48&lt;&gt;"",ISNUMBER(F48),F48+365&gt;=TODAY(),H48&lt;&gt;"",ISNUMBER(H48),H48&gt;=DATE(YEAR(TODAY()),MONTH(TODAY())-1,1),I48&lt;&gt;"",ISNUMBER(I48),I48+365&gt;=TODAY(),K48="APTO"),"✔ ACCESO PERMITIDO","✘ SIN ACCESO")</f>
+        <f>IF(AND(F48&lt;&gt;"",ISNUMBER(F48),F48&gt;=TODAY(),H48&lt;&gt;"",ISNUMBER(H48),H48&gt;=DATE(YEAR(TODAY()),MONTH(TODAY())-1,1),I48&lt;&gt;"",ISNUMBER(I48),I48&gt;=TODAY(),K48="APTO"),"✔ ACCESO PERMITIDO","✘ SIN ACCESO")</f>
         <v/>
       </c>
       <c r="M48" s="12" t="n"/>
@@ -2443,18 +2443,18 @@
       <c r="E49" s="11" t="n"/>
       <c r="F49" s="12" t="n"/>
       <c r="G49" s="13">
-        <f>IF(F49="","",IF(F49+365&gt;=TODAY(),"✔ Vigente","✘ Vencido"))</f>
+        <f>IF(F49="","",IF(F49&gt;=TODAY(),"✔ Vigente","✘ Vencido"))</f>
         <v/>
       </c>
       <c r="H49" s="12" t="n"/>
       <c r="I49" s="12" t="n"/>
       <c r="J49" s="13">
-        <f>IF(I49="","",IF(I49+365&gt;=TODAY(),"✔ Vigente","✘ Vencido"))</f>
+        <f>IF(I49="","",IF(I49&gt;=TODAY(),"✔ Vigente","✘ Vencido"))</f>
         <v/>
       </c>
       <c r="K49" s="13" t="n"/>
       <c r="L49" s="16">
-        <f>IF(AND(F49&lt;&gt;"",ISNUMBER(F49),F49+365&gt;=TODAY(),H49&lt;&gt;"",ISNUMBER(H49),H49&gt;=DATE(YEAR(TODAY()),MONTH(TODAY())-1,1),I49&lt;&gt;"",ISNUMBER(I49),I49+365&gt;=TODAY(),K49="APTO"),"✔ ACCESO PERMITIDO","✘ SIN ACCESO")</f>
+        <f>IF(AND(F49&lt;&gt;"",ISNUMBER(F49),F49&gt;=TODAY(),H49&lt;&gt;"",ISNUMBER(H49),H49&gt;=DATE(YEAR(TODAY()),MONTH(TODAY())-1,1),I49&lt;&gt;"",ISNUMBER(I49),I49&gt;=TODAY(),K49="APTO"),"✔ ACCESO PERMITIDO","✘ SIN ACCESO")</f>
         <v/>
       </c>
       <c r="M49" s="12" t="n"/>
@@ -2475,18 +2475,18 @@
       <c r="E50" s="11" t="n"/>
       <c r="F50" s="12" t="n"/>
       <c r="G50" s="13">
-        <f>IF(F50="","",IF(F50+365&gt;=TODAY(),"✔ Vigente","✘ Vencido"))</f>
+        <f>IF(F50="","",IF(F50&gt;=TODAY(),"✔ Vigente","✘ Vencido"))</f>
         <v/>
       </c>
       <c r="H50" s="12" t="n"/>
       <c r="I50" s="12" t="n"/>
       <c r="J50" s="13">
-        <f>IF(I50="","",IF(I50+365&gt;=TODAY(),"✔ Vigente","✘ Vencido"))</f>
+        <f>IF(I50="","",IF(I50&gt;=TODAY(),"✔ Vigente","✘ Vencido"))</f>
         <v/>
       </c>
       <c r="K50" s="13" t="n"/>
       <c r="L50" s="14">
-        <f>IF(AND(F50&lt;&gt;"",ISNUMBER(F50),F50+365&gt;=TODAY(),H50&lt;&gt;"",ISNUMBER(H50),H50&gt;=DATE(YEAR(TODAY()),MONTH(TODAY())-1,1),I50&lt;&gt;"",ISNUMBER(I50),I50+365&gt;=TODAY(),K50="APTO"),"✔ ACCESO PERMITIDO","✘ SIN ACCESO")</f>
+        <f>IF(AND(F50&lt;&gt;"",ISNUMBER(F50),F50&gt;=TODAY(),H50&lt;&gt;"",ISNUMBER(H50),H50&gt;=DATE(YEAR(TODAY()),MONTH(TODAY())-1,1),I50&lt;&gt;"",ISNUMBER(I50),I50&gt;=TODAY(),K50="APTO"),"✔ ACCESO PERMITIDO","✘ SIN ACCESO")</f>
         <v/>
       </c>
       <c r="M50" s="12" t="n"/>
@@ -2507,18 +2507,18 @@
       <c r="E51" s="11" t="n"/>
       <c r="F51" s="12" t="n"/>
       <c r="G51" s="13">
-        <f>IF(F51="","",IF(F51+365&gt;=TODAY(),"✔ Vigente","✘ Vencido"))</f>
+        <f>IF(F51="","",IF(F51&gt;=TODAY(),"✔ Vigente","✘ Vencido"))</f>
         <v/>
       </c>
       <c r="H51" s="12" t="n"/>
       <c r="I51" s="12" t="n"/>
       <c r="J51" s="13">
-        <f>IF(I51="","",IF(I51+365&gt;=TODAY(),"✔ Vigente","✘ Vencido"))</f>
+        <f>IF(I51="","",IF(I51&gt;=TODAY(),"✔ Vigente","✘ Vencido"))</f>
         <v/>
       </c>
       <c r="K51" s="13" t="n"/>
       <c r="L51" s="16">
-        <f>IF(AND(F51&lt;&gt;"",ISNUMBER(F51),F51+365&gt;=TODAY(),H51&lt;&gt;"",ISNUMBER(H51),H51&gt;=DATE(YEAR(TODAY()),MONTH(TODAY())-1,1),I51&lt;&gt;"",ISNUMBER(I51),I51+365&gt;=TODAY(),K51="APTO"),"✔ ACCESO PERMITIDO","✘ SIN ACCESO")</f>
+        <f>IF(AND(F51&lt;&gt;"",ISNUMBER(F51),F51&gt;=TODAY(),H51&lt;&gt;"",ISNUMBER(H51),H51&gt;=DATE(YEAR(TODAY()),MONTH(TODAY())-1,1),I51&lt;&gt;"",ISNUMBER(I51),I51&gt;=TODAY(),K51="APTO"),"✔ ACCESO PERMITIDO","✘ SIN ACCESO")</f>
         <v/>
       </c>
       <c r="M51" s="12" t="n"/>
@@ -2539,18 +2539,18 @@
       <c r="E52" s="11" t="n"/>
       <c r="F52" s="12" t="n"/>
       <c r="G52" s="13">
-        <f>IF(F52="","",IF(F52+365&gt;=TODAY(),"✔ Vigente","✘ Vencido"))</f>
+        <f>IF(F52="","",IF(F52&gt;=TODAY(),"✔ Vigente","✘ Vencido"))</f>
         <v/>
       </c>
       <c r="H52" s="12" t="n"/>
       <c r="I52" s="12" t="n"/>
       <c r="J52" s="13">
-        <f>IF(I52="","",IF(I52+365&gt;=TODAY(),"✔ Vigente","✘ Vencido"))</f>
+        <f>IF(I52="","",IF(I52&gt;=TODAY(),"✔ Vigente","✘ Vencido"))</f>
         <v/>
       </c>
       <c r="K52" s="13" t="n"/>
       <c r="L52" s="14">
-        <f>IF(AND(F52&lt;&gt;"",ISNUMBER(F52),F52+365&gt;=TODAY(),H52&lt;&gt;"",ISNUMBER(H52),H52&gt;=DATE(YEAR(TODAY()),MONTH(TODAY())-1,1),I52&lt;&gt;"",ISNUMBER(I52),I52+365&gt;=TODAY(),K52="APTO"),"✔ ACCESO PERMITIDO","✘ SIN ACCESO")</f>
+        <f>IF(AND(F52&lt;&gt;"",ISNUMBER(F52),F52&gt;=TODAY(),H52&lt;&gt;"",ISNUMBER(H52),H52&gt;=DATE(YEAR(TODAY()),MONTH(TODAY())-1,1),I52&lt;&gt;"",ISNUMBER(I52),I52&gt;=TODAY(),K52="APTO"),"✔ ACCESO PERMITIDO","✘ SIN ACCESO")</f>
         <v/>
       </c>
       <c r="M52" s="12" t="n"/>
@@ -2571,18 +2571,18 @@
       <c r="E53" s="11" t="n"/>
       <c r="F53" s="12" t="n"/>
       <c r="G53" s="13">
-        <f>IF(F53="","",IF(F53+365&gt;=TODAY(),"✔ Vigente","✘ Vencido"))</f>
+        <f>IF(F53="","",IF(F53&gt;=TODAY(),"✔ Vigente","✘ Vencido"))</f>
         <v/>
       </c>
       <c r="H53" s="12" t="n"/>
       <c r="I53" s="12" t="n"/>
       <c r="J53" s="13">
-        <f>IF(I53="","",IF(I53+365&gt;=TODAY(),"✔ Vigente","✘ Vencido"))</f>
+        <f>IF(I53="","",IF(I53&gt;=TODAY(),"✔ Vigente","✘ Vencido"))</f>
         <v/>
       </c>
       <c r="K53" s="13" t="n"/>
       <c r="L53" s="16">
-        <f>IF(AND(F53&lt;&gt;"",ISNUMBER(F53),F53+365&gt;=TODAY(),H53&lt;&gt;"",ISNUMBER(H53),H53&gt;=DATE(YEAR(TODAY()),MONTH(TODAY())-1,1),I53&lt;&gt;"",ISNUMBER(I53),I53+365&gt;=TODAY(),K53="APTO"),"✔ ACCESO PERMITIDO","✘ SIN ACCESO")</f>
+        <f>IF(AND(F53&lt;&gt;"",ISNUMBER(F53),F53&gt;=TODAY(),H53&lt;&gt;"",ISNUMBER(H53),H53&gt;=DATE(YEAR(TODAY()),MONTH(TODAY())-1,1),I53&lt;&gt;"",ISNUMBER(I53),I53&gt;=TODAY(),K53="APTO"),"✔ ACCESO PERMITIDO","✘ SIN ACCESO")</f>
         <v/>
       </c>
       <c r="M53" s="12" t="n"/>
@@ -2603,18 +2603,18 @@
       <c r="E54" s="11" t="n"/>
       <c r="F54" s="12" t="n"/>
       <c r="G54" s="13">
-        <f>IF(F54="","",IF(F54+365&gt;=TODAY(),"✔ Vigente","✘ Vencido"))</f>
+        <f>IF(F54="","",IF(F54&gt;=TODAY(),"✔ Vigente","✘ Vencido"))</f>
         <v/>
       </c>
       <c r="H54" s="12" t="n"/>
       <c r="I54" s="12" t="n"/>
       <c r="J54" s="13">
-        <f>IF(I54="","",IF(I54+365&gt;=TODAY(),"✔ Vigente","✘ Vencido"))</f>
+        <f>IF(I54="","",IF(I54&gt;=TODAY(),"✔ Vigente","✘ Vencido"))</f>
         <v/>
       </c>
       <c r="K54" s="13" t="n"/>
       <c r="L54" s="14">
-        <f>IF(AND(F54&lt;&gt;"",ISNUMBER(F54),F54+365&gt;=TODAY(),H54&lt;&gt;"",ISNUMBER(H54),H54&gt;=DATE(YEAR(TODAY()),MONTH(TODAY())-1,1),I54&lt;&gt;"",ISNUMBER(I54),I54+365&gt;=TODAY(),K54="APTO"),"✔ ACCESO PERMITIDO","✘ SIN ACCESO")</f>
+        <f>IF(AND(F54&lt;&gt;"",ISNUMBER(F54),F54&gt;=TODAY(),H54&lt;&gt;"",ISNUMBER(H54),H54&gt;=DATE(YEAR(TODAY()),MONTH(TODAY())-1,1),I54&lt;&gt;"",ISNUMBER(I54),I54&gt;=TODAY(),K54="APTO"),"✔ ACCESO PERMITIDO","✘ SIN ACCESO")</f>
         <v/>
       </c>
       <c r="M54" s="12" t="n"/>
@@ -2635,18 +2635,18 @@
       <c r="E55" s="11" t="n"/>
       <c r="F55" s="12" t="n"/>
       <c r="G55" s="13">
-        <f>IF(F55="","",IF(F55+365&gt;=TODAY(),"✔ Vigente","✘ Vencido"))</f>
+        <f>IF(F55="","",IF(F55&gt;=TODAY(),"✔ Vigente","✘ Vencido"))</f>
         <v/>
       </c>
       <c r="H55" s="12" t="n"/>
       <c r="I55" s="12" t="n"/>
       <c r="J55" s="13">
-        <f>IF(I55="","",IF(I55+365&gt;=TODAY(),"✔ Vigente","✘ Vencido"))</f>
+        <f>IF(I55="","",IF(I55&gt;=TODAY(),"✔ Vigente","✘ Vencido"))</f>
         <v/>
       </c>
       <c r="K55" s="13" t="n"/>
       <c r="L55" s="16">
-        <f>IF(AND(F55&lt;&gt;"",ISNUMBER(F55),F55+365&gt;=TODAY(),H55&lt;&gt;"",ISNUMBER(H55),H55&gt;=DATE(YEAR(TODAY()),MONTH(TODAY())-1,1),I55&lt;&gt;"",ISNUMBER(I55),I55+365&gt;=TODAY(),K55="APTO"),"✔ ACCESO PERMITIDO","✘ SIN ACCESO")</f>
+        <f>IF(AND(F55&lt;&gt;"",ISNUMBER(F55),F55&gt;=TODAY(),H55&lt;&gt;"",ISNUMBER(H55),H55&gt;=DATE(YEAR(TODAY()),MONTH(TODAY())-1,1),I55&lt;&gt;"",ISNUMBER(I55),I55&gt;=TODAY(),K55="APTO"),"✔ ACCESO PERMITIDO","✘ SIN ACCESO")</f>
         <v/>
       </c>
       <c r="M55" s="12" t="n"/>
@@ -2669,13 +2669,13 @@
   </mergeCells>
   <conditionalFormatting sqref="F6:F55">
     <cfRule type="expression" priority="1" dxfId="15">
-      <formula>AND(F6&lt;&gt;"",ISNUMBER(F6),F6+365&lt;TODAY())</formula>
+      <formula>AND(F6&lt;&gt;"",ISNUMBER(F6),F6&lt;TODAY())</formula>
     </cfRule>
     <cfRule type="expression" priority="2" dxfId="16">
-      <formula>AND(F6&lt;&gt;"",ISNUMBER(F6),F6+365&gt;=TODAY(),F6+365&lt;=TODAY()+30)</formula>
+      <formula>AND(F6&lt;&gt;"",ISNUMBER(F6),F6&gt;=TODAY(),F6&lt;=TODAY()+30)</formula>
     </cfRule>
     <cfRule type="expression" priority="3" dxfId="17">
-      <formula>AND(F6&lt;&gt;"",ISNUMBER(F6),F6+365&gt;TODAY()+30)</formula>
+      <formula>AND(F6&lt;&gt;"",ISNUMBER(F6),F6&gt;TODAY()+30)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G6:G55">
@@ -2696,13 +2696,13 @@
   </conditionalFormatting>
   <conditionalFormatting sqref="I6:I55">
     <cfRule type="expression" priority="8" dxfId="15">
-      <formula>AND(I6&lt;&gt;"",ISNUMBER(I6),I6+365&lt;TODAY())</formula>
+      <formula>AND(I6&lt;&gt;"",ISNUMBER(I6),I6&lt;TODAY())</formula>
     </cfRule>
     <cfRule type="expression" priority="9" dxfId="16">
-      <formula>AND(I6&lt;&gt;"",ISNUMBER(I6),I6+365&gt;=TODAY(),I6+365&lt;=TODAY()+30)</formula>
+      <formula>AND(I6&lt;&gt;"",ISNUMBER(I6),I6&gt;=TODAY(),I6&lt;=TODAY()+30)</formula>
     </cfRule>
     <cfRule type="expression" priority="10" dxfId="17">
-      <formula>AND(I6&lt;&gt;"",ISNUMBER(I6),I6+365&gt;TODAY()+30)</formula>
+      <formula>AND(I6&lt;&gt;"",ISNUMBER(I6),I6&gt;TODAY()+30)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J6:J55">

--- a/Consolidado_contratistas_plantabal.xlsx
+++ b/Consolidado_contratistas_plantabal.xlsx
@@ -1074,7 +1074,7 @@
         </is>
       </c>
       <c r="L6" s="14">
-        <f>IF(AND(F6&lt;&gt;"",ISNUMBER(F6),F6&gt;=TODAY(),H6&lt;&gt;"",ISNUMBER(H6),H6&gt;=DATE(YEAR(TODAY()),MONTH(TODAY())-1,1),I6&lt;&gt;"",ISNUMBER(I6),I6&gt;=TODAY(),K6="APTO"),"✔ ACCESO PERMITIDO","✘ SIN ACCESO")</f>
+        <f>IF(AND(G6="✔ Vigente",H6&lt;&gt;"",ISNUMBER(H6),H6&gt;=DATE(YEAR(TODAY()),MONTH(TODAY())-1,1),J6="✔ Vigente",UPPER(K6)="APTO"),"✔ ACCESO PERMITIDO","✘ SIN ACCESO")</f>
         <v/>
       </c>
       <c r="M6" s="12" t="n">
@@ -1110,7 +1110,7 @@
       </c>
       <c r="K7" s="13" t="n"/>
       <c r="L7" s="16">
-        <f>IF(AND(F7&lt;&gt;"",ISNUMBER(F7),F7&gt;=TODAY(),H7&lt;&gt;"",ISNUMBER(H7),H7&gt;=DATE(YEAR(TODAY()),MONTH(TODAY())-1,1),I7&lt;&gt;"",ISNUMBER(I7),I7&gt;=TODAY(),K7="APTO"),"✔ ACCESO PERMITIDO","✘ SIN ACCESO")</f>
+        <f>IF(AND(G7="✔ Vigente",H7&lt;&gt;"",ISNUMBER(H7),H7&gt;=DATE(YEAR(TODAY()),MONTH(TODAY())-1,1),J7="✔ Vigente",UPPER(K7)="APTO"),"✔ ACCESO PERMITIDO","✘ SIN ACCESO")</f>
         <v/>
       </c>
       <c r="M7" s="12" t="n"/>
@@ -1142,7 +1142,7 @@
       </c>
       <c r="K8" s="13" t="n"/>
       <c r="L8" s="14">
-        <f>IF(AND(F8&lt;&gt;"",ISNUMBER(F8),F8&gt;=TODAY(),H8&lt;&gt;"",ISNUMBER(H8),H8&gt;=DATE(YEAR(TODAY()),MONTH(TODAY())-1,1),I8&lt;&gt;"",ISNUMBER(I8),I8&gt;=TODAY(),K8="APTO"),"✔ ACCESO PERMITIDO","✘ SIN ACCESO")</f>
+        <f>IF(AND(G8="✔ Vigente",H8&lt;&gt;"",ISNUMBER(H8),H8&gt;=DATE(YEAR(TODAY()),MONTH(TODAY())-1,1),J8="✔ Vigente",UPPER(K8)="APTO"),"✔ ACCESO PERMITIDO","✘ SIN ACCESO")</f>
         <v/>
       </c>
       <c r="M8" s="12" t="n"/>
@@ -1174,7 +1174,7 @@
       </c>
       <c r="K9" s="13" t="n"/>
       <c r="L9" s="16">
-        <f>IF(AND(F9&lt;&gt;"",ISNUMBER(F9),F9&gt;=TODAY(),H9&lt;&gt;"",ISNUMBER(H9),H9&gt;=DATE(YEAR(TODAY()),MONTH(TODAY())-1,1),I9&lt;&gt;"",ISNUMBER(I9),I9&gt;=TODAY(),K9="APTO"),"✔ ACCESO PERMITIDO","✘ SIN ACCESO")</f>
+        <f>IF(AND(G9="✔ Vigente",H9&lt;&gt;"",ISNUMBER(H9),H9&gt;=DATE(YEAR(TODAY()),MONTH(TODAY())-1,1),J9="✔ Vigente",UPPER(K9)="APTO"),"✔ ACCESO PERMITIDO","✘ SIN ACCESO")</f>
         <v/>
       </c>
       <c r="M9" s="12" t="n"/>
@@ -1206,7 +1206,7 @@
       </c>
       <c r="K10" s="13" t="n"/>
       <c r="L10" s="14">
-        <f>IF(AND(F10&lt;&gt;"",ISNUMBER(F10),F10&gt;=TODAY(),H10&lt;&gt;"",ISNUMBER(H10),H10&gt;=DATE(YEAR(TODAY()),MONTH(TODAY())-1,1),I10&lt;&gt;"",ISNUMBER(I10),I10&gt;=TODAY(),K10="APTO"),"✔ ACCESO PERMITIDO","✘ SIN ACCESO")</f>
+        <f>IF(AND(G10="✔ Vigente",H10&lt;&gt;"",ISNUMBER(H10),H10&gt;=DATE(YEAR(TODAY()),MONTH(TODAY())-1,1),J10="✔ Vigente",UPPER(K10)="APTO"),"✔ ACCESO PERMITIDO","✘ SIN ACCESO")</f>
         <v/>
       </c>
       <c r="M10" s="12" t="n"/>
@@ -1238,7 +1238,7 @@
       </c>
       <c r="K11" s="13" t="n"/>
       <c r="L11" s="16">
-        <f>IF(AND(F11&lt;&gt;"",ISNUMBER(F11),F11&gt;=TODAY(),H11&lt;&gt;"",ISNUMBER(H11),H11&gt;=DATE(YEAR(TODAY()),MONTH(TODAY())-1,1),I11&lt;&gt;"",ISNUMBER(I11),I11&gt;=TODAY(),K11="APTO"),"✔ ACCESO PERMITIDO","✘ SIN ACCESO")</f>
+        <f>IF(AND(G11="✔ Vigente",H11&lt;&gt;"",ISNUMBER(H11),H11&gt;=DATE(YEAR(TODAY()),MONTH(TODAY())-1,1),J11="✔ Vigente",UPPER(K11)="APTO"),"✔ ACCESO PERMITIDO","✘ SIN ACCESO")</f>
         <v/>
       </c>
       <c r="M11" s="12" t="n"/>
@@ -1270,7 +1270,7 @@
       </c>
       <c r="K12" s="13" t="n"/>
       <c r="L12" s="14">
-        <f>IF(AND(F12&lt;&gt;"",ISNUMBER(F12),F12&gt;=TODAY(),H12&lt;&gt;"",ISNUMBER(H12),H12&gt;=DATE(YEAR(TODAY()),MONTH(TODAY())-1,1),I12&lt;&gt;"",ISNUMBER(I12),I12&gt;=TODAY(),K12="APTO"),"✔ ACCESO PERMITIDO","✘ SIN ACCESO")</f>
+        <f>IF(AND(G12="✔ Vigente",H12&lt;&gt;"",ISNUMBER(H12),H12&gt;=DATE(YEAR(TODAY()),MONTH(TODAY())-1,1),J12="✔ Vigente",UPPER(K12)="APTO"),"✔ ACCESO PERMITIDO","✘ SIN ACCESO")</f>
         <v/>
       </c>
       <c r="M12" s="12" t="n"/>
@@ -1302,7 +1302,7 @@
       </c>
       <c r="K13" s="13" t="n"/>
       <c r="L13" s="16">
-        <f>IF(AND(F13&lt;&gt;"",ISNUMBER(F13),F13&gt;=TODAY(),H13&lt;&gt;"",ISNUMBER(H13),H13&gt;=DATE(YEAR(TODAY()),MONTH(TODAY())-1,1),I13&lt;&gt;"",ISNUMBER(I13),I13&gt;=TODAY(),K13="APTO"),"✔ ACCESO PERMITIDO","✘ SIN ACCESO")</f>
+        <f>IF(AND(G13="✔ Vigente",H13&lt;&gt;"",ISNUMBER(H13),H13&gt;=DATE(YEAR(TODAY()),MONTH(TODAY())-1,1),J13="✔ Vigente",UPPER(K13)="APTO"),"✔ ACCESO PERMITIDO","✘ SIN ACCESO")</f>
         <v/>
       </c>
       <c r="M13" s="12" t="n"/>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="K14" s="13" t="n"/>
       <c r="L14" s="14">
-        <f>IF(AND(F14&lt;&gt;"",ISNUMBER(F14),F14&gt;=TODAY(),H14&lt;&gt;"",ISNUMBER(H14),H14&gt;=DATE(YEAR(TODAY()),MONTH(TODAY())-1,1),I14&lt;&gt;"",ISNUMBER(I14),I14&gt;=TODAY(),K14="APTO"),"✔ ACCESO PERMITIDO","✘ SIN ACCESO")</f>
+        <f>IF(AND(G14="✔ Vigente",H14&lt;&gt;"",ISNUMBER(H14),H14&gt;=DATE(YEAR(TODAY()),MONTH(TODAY())-1,1),J14="✔ Vigente",UPPER(K14)="APTO"),"✔ ACCESO PERMITIDO","✘ SIN ACCESO")</f>
         <v/>
       </c>
       <c r="M14" s="12" t="n"/>
@@ -1366,7 +1366,7 @@
       </c>
       <c r="K15" s="13" t="n"/>
       <c r="L15" s="16">
-        <f>IF(AND(F15&lt;&gt;"",ISNUMBER(F15),F15&gt;=TODAY(),H15&lt;&gt;"",ISNUMBER(H15),H15&gt;=DATE(YEAR(TODAY()),MONTH(TODAY())-1,1),I15&lt;&gt;"",ISNUMBER(I15),I15&gt;=TODAY(),K15="APTO"),"✔ ACCESO PERMITIDO","✘ SIN ACCESO")</f>
+        <f>IF(AND(G15="✔ Vigente",H15&lt;&gt;"",ISNUMBER(H15),H15&gt;=DATE(YEAR(TODAY()),MONTH(TODAY())-1,1),J15="✔ Vigente",UPPER(K15)="APTO"),"✔ ACCESO PERMITIDO","✘ SIN ACCESO")</f>
         <v/>
       </c>
       <c r="M15" s="12" t="n"/>
@@ -1398,7 +1398,7 @@
       </c>
       <c r="K16" s="13" t="n"/>
       <c r="L16" s="14">
-        <f>IF(AND(F16&lt;&gt;"",ISNUMBER(F16),F16&gt;=TODAY(),H16&lt;&gt;"",ISNUMBER(H16),H16&gt;=DATE(YEAR(TODAY()),MONTH(TODAY())-1,1),I16&lt;&gt;"",ISNUMBER(I16),I16&gt;=TODAY(),K16="APTO"),"✔ ACCESO PERMITIDO","✘ SIN ACCESO")</f>
+        <f>IF(AND(G16="✔ Vigente",H16&lt;&gt;"",ISNUMBER(H16),H16&gt;=DATE(YEAR(TODAY()),MONTH(TODAY())-1,1),J16="✔ Vigente",UPPER(K16)="APTO"),"✔ ACCESO PERMITIDO","✘ SIN ACCESO")</f>
         <v/>
       </c>
       <c r="M16" s="12" t="n"/>
@@ -1430,7 +1430,7 @@
       </c>
       <c r="K17" s="13" t="n"/>
       <c r="L17" s="16">
-        <f>IF(AND(F17&lt;&gt;"",ISNUMBER(F17),F17&gt;=TODAY(),H17&lt;&gt;"",ISNUMBER(H17),H17&gt;=DATE(YEAR(TODAY()),MONTH(TODAY())-1,1),I17&lt;&gt;"",ISNUMBER(I17),I17&gt;=TODAY(),K17="APTO"),"✔ ACCESO PERMITIDO","✘ SIN ACCESO")</f>
+        <f>IF(AND(G17="✔ Vigente",H17&lt;&gt;"",ISNUMBER(H17),H17&gt;=DATE(YEAR(TODAY()),MONTH(TODAY())-1,1),J17="✔ Vigente",UPPER(K17)="APTO"),"✔ ACCESO PERMITIDO","✘ SIN ACCESO")</f>
         <v/>
       </c>
       <c r="M17" s="12" t="n"/>
@@ -1462,7 +1462,7 @@
       </c>
       <c r="K18" s="13" t="n"/>
       <c r="L18" s="14">
-        <f>IF(AND(F18&lt;&gt;"",ISNUMBER(F18),F18&gt;=TODAY(),H18&lt;&gt;"",ISNUMBER(H18),H18&gt;=DATE(YEAR(TODAY()),MONTH(TODAY())-1,1),I18&lt;&gt;"",ISNUMBER(I18),I18&gt;=TODAY(),K18="APTO"),"✔ ACCESO PERMITIDO","✘ SIN ACCESO")</f>
+        <f>IF(AND(G18="✔ Vigente",H18&lt;&gt;"",ISNUMBER(H18),H18&gt;=DATE(YEAR(TODAY()),MONTH(TODAY())-1,1),J18="✔ Vigente",UPPER(K18)="APTO"),"✔ ACCESO PERMITIDO","✘ SIN ACCESO")</f>
         <v/>
       </c>
       <c r="M18" s="12" t="n"/>
@@ -1494,7 +1494,7 @@
       </c>
       <c r="K19" s="13" t="n"/>
       <c r="L19" s="16">
-        <f>IF(AND(F19&lt;&gt;"",ISNUMBER(F19),F19&gt;=TODAY(),H19&lt;&gt;"",ISNUMBER(H19),H19&gt;=DATE(YEAR(TODAY()),MONTH(TODAY())-1,1),I19&lt;&gt;"",ISNUMBER(I19),I19&gt;=TODAY(),K19="APTO"),"✔ ACCESO PERMITIDO","✘ SIN ACCESO")</f>
+        <f>IF(AND(G19="✔ Vigente",H19&lt;&gt;"",ISNUMBER(H19),H19&gt;=DATE(YEAR(TODAY()),MONTH(TODAY())-1,1),J19="✔ Vigente",UPPER(K19)="APTO"),"✔ ACCESO PERMITIDO","✘ SIN ACCESO")</f>
         <v/>
       </c>
       <c r="M19" s="12" t="n"/>
@@ -1526,7 +1526,7 @@
       </c>
       <c r="K20" s="13" t="n"/>
       <c r="L20" s="14">
-        <f>IF(AND(F20&lt;&gt;"",ISNUMBER(F20),F20&gt;=TODAY(),H20&lt;&gt;"",ISNUMBER(H20),H20&gt;=DATE(YEAR(TODAY()),MONTH(TODAY())-1,1),I20&lt;&gt;"",ISNUMBER(I20),I20&gt;=TODAY(),K20="APTO"),"✔ ACCESO PERMITIDO","✘ SIN ACCESO")</f>
+        <f>IF(AND(G20="✔ Vigente",H20&lt;&gt;"",ISNUMBER(H20),H20&gt;=DATE(YEAR(TODAY()),MONTH(TODAY())-1,1),J20="✔ Vigente",UPPER(K20)="APTO"),"✔ ACCESO PERMITIDO","✘ SIN ACCESO")</f>
         <v/>
       </c>
       <c r="M20" s="12" t="n"/>
@@ -1558,7 +1558,7 @@
       </c>
       <c r="K21" s="13" t="n"/>
       <c r="L21" s="16">
-        <f>IF(AND(F21&lt;&gt;"",ISNUMBER(F21),F21&gt;=TODAY(),H21&lt;&gt;"",ISNUMBER(H21),H21&gt;=DATE(YEAR(TODAY()),MONTH(TODAY())-1,1),I21&lt;&gt;"",ISNUMBER(I21),I21&gt;=TODAY(),K21="APTO"),"✔ ACCESO PERMITIDO","✘ SIN ACCESO")</f>
+        <f>IF(AND(G21="✔ Vigente",H21&lt;&gt;"",ISNUMBER(H21),H21&gt;=DATE(YEAR(TODAY()),MONTH(TODAY())-1,1),J21="✔ Vigente",UPPER(K21)="APTO"),"✔ ACCESO PERMITIDO","✘ SIN ACCESO")</f>
         <v/>
       </c>
       <c r="M21" s="12" t="n"/>
@@ -1590,7 +1590,7 @@
       </c>
       <c r="K22" s="13" t="n"/>
       <c r="L22" s="14">
-        <f>IF(AND(F22&lt;&gt;"",ISNUMBER(F22),F22&gt;=TODAY(),H22&lt;&gt;"",ISNUMBER(H22),H22&gt;=DATE(YEAR(TODAY()),MONTH(TODAY())-1,1),I22&lt;&gt;"",ISNUMBER(I22),I22&gt;=TODAY(),K22="APTO"),"✔ ACCESO PERMITIDO","✘ SIN ACCESO")</f>
+        <f>IF(AND(G22="✔ Vigente",H22&lt;&gt;"",ISNUMBER(H22),H22&gt;=DATE(YEAR(TODAY()),MONTH(TODAY())-1,1),J22="✔ Vigente",UPPER(K22)="APTO"),"✔ ACCESO PERMITIDO","✘ SIN ACCESO")</f>
         <v/>
       </c>
       <c r="M22" s="12" t="n"/>
@@ -1622,7 +1622,7 @@
       </c>
       <c r="K23" s="13" t="n"/>
       <c r="L23" s="16">
-        <f>IF(AND(F23&lt;&gt;"",ISNUMBER(F23),F23&gt;=TODAY(),H23&lt;&gt;"",ISNUMBER(H23),H23&gt;=DATE(YEAR(TODAY()),MONTH(TODAY())-1,1),I23&lt;&gt;"",ISNUMBER(I23),I23&gt;=TODAY(),K23="APTO"),"✔ ACCESO PERMITIDO","✘ SIN ACCESO")</f>
+        <f>IF(AND(G23="✔ Vigente",H23&lt;&gt;"",ISNUMBER(H23),H23&gt;=DATE(YEAR(TODAY()),MONTH(TODAY())-1,1),J23="✔ Vigente",UPPER(K23)="APTO"),"✔ ACCESO PERMITIDO","✘ SIN ACCESO")</f>
         <v/>
       </c>
       <c r="M23" s="12" t="n"/>
@@ -1654,7 +1654,7 @@
       </c>
       <c r="K24" s="13" t="n"/>
       <c r="L24" s="14">
-        <f>IF(AND(F24&lt;&gt;"",ISNUMBER(F24),F24&gt;=TODAY(),H24&lt;&gt;"",ISNUMBER(H24),H24&gt;=DATE(YEAR(TODAY()),MONTH(TODAY())-1,1),I24&lt;&gt;"",ISNUMBER(I24),I24&gt;=TODAY(),K24="APTO"),"✔ ACCESO PERMITIDO","✘ SIN ACCESO")</f>
+        <f>IF(AND(G24="✔ Vigente",H24&lt;&gt;"",ISNUMBER(H24),H24&gt;=DATE(YEAR(TODAY()),MONTH(TODAY())-1,1),J24="✔ Vigente",UPPER(K24)="APTO"),"✔ ACCESO PERMITIDO","✘ SIN ACCESO")</f>
         <v/>
       </c>
       <c r="M24" s="12" t="n"/>
@@ -1686,7 +1686,7 @@
       </c>
       <c r="K25" s="13" t="n"/>
       <c r="L25" s="16">
-        <f>IF(AND(F25&lt;&gt;"",ISNUMBER(F25),F25&gt;=TODAY(),H25&lt;&gt;"",ISNUMBER(H25),H25&gt;=DATE(YEAR(TODAY()),MONTH(TODAY())-1,1),I25&lt;&gt;"",ISNUMBER(I25),I25&gt;=TODAY(),K25="APTO"),"✔ ACCESO PERMITIDO","✘ SIN ACCESO")</f>
+        <f>IF(AND(G25="✔ Vigente",H25&lt;&gt;"",ISNUMBER(H25),H25&gt;=DATE(YEAR(TODAY()),MONTH(TODAY())-1,1),J25="✔ Vigente",UPPER(K25)="APTO"),"✔ ACCESO PERMITIDO","✘ SIN ACCESO")</f>
         <v/>
       </c>
       <c r="M25" s="12" t="n"/>
@@ -1718,7 +1718,7 @@
       </c>
       <c r="K26" s="13" t="n"/>
       <c r="L26" s="14">
-        <f>IF(AND(F26&lt;&gt;"",ISNUMBER(F26),F26&gt;=TODAY(),H26&lt;&gt;"",ISNUMBER(H26),H26&gt;=DATE(YEAR(TODAY()),MONTH(TODAY())-1,1),I26&lt;&gt;"",ISNUMBER(I26),I26&gt;=TODAY(),K26="APTO"),"✔ ACCESO PERMITIDO","✘ SIN ACCESO")</f>
+        <f>IF(AND(G26="✔ Vigente",H26&lt;&gt;"",ISNUMBER(H26),H26&gt;=DATE(YEAR(TODAY()),MONTH(TODAY())-1,1),J26="✔ Vigente",UPPER(K26)="APTO"),"✔ ACCESO PERMITIDO","✘ SIN ACCESO")</f>
         <v/>
       </c>
       <c r="M26" s="12" t="n"/>
@@ -1750,7 +1750,7 @@
       </c>
       <c r="K27" s="13" t="n"/>
       <c r="L27" s="16">
-        <f>IF(AND(F27&lt;&gt;"",ISNUMBER(F27),F27&gt;=TODAY(),H27&lt;&gt;"",ISNUMBER(H27),H27&gt;=DATE(YEAR(TODAY()),MONTH(TODAY())-1,1),I27&lt;&gt;"",ISNUMBER(I27),I27&gt;=TODAY(),K27="APTO"),"✔ ACCESO PERMITIDO","✘ SIN ACCESO")</f>
+        <f>IF(AND(G27="✔ Vigente",H27&lt;&gt;"",ISNUMBER(H27),H27&gt;=DATE(YEAR(TODAY()),MONTH(TODAY())-1,1),J27="✔ Vigente",UPPER(K27)="APTO"),"✔ ACCESO PERMITIDO","✘ SIN ACCESO")</f>
         <v/>
       </c>
       <c r="M27" s="12" t="n"/>
@@ -1782,7 +1782,7 @@
       </c>
       <c r="K28" s="13" t="n"/>
       <c r="L28" s="14">
-        <f>IF(AND(F28&lt;&gt;"",ISNUMBER(F28),F28&gt;=TODAY(),H28&lt;&gt;"",ISNUMBER(H28),H28&gt;=DATE(YEAR(TODAY()),MONTH(TODAY())-1,1),I28&lt;&gt;"",ISNUMBER(I28),I28&gt;=TODAY(),K28="APTO"),"✔ ACCESO PERMITIDO","✘ SIN ACCESO")</f>
+        <f>IF(AND(G28="✔ Vigente",H28&lt;&gt;"",ISNUMBER(H28),H28&gt;=DATE(YEAR(TODAY()),MONTH(TODAY())-1,1),J28="✔ Vigente",UPPER(K28)="APTO"),"✔ ACCESO PERMITIDO","✘ SIN ACCESO")</f>
         <v/>
       </c>
       <c r="M28" s="12" t="n"/>
@@ -1814,7 +1814,7 @@
       </c>
       <c r="K29" s="13" t="n"/>
       <c r="L29" s="16">
-        <f>IF(AND(F29&lt;&gt;"",ISNUMBER(F29),F29&gt;=TODAY(),H29&lt;&gt;"",ISNUMBER(H29),H29&gt;=DATE(YEAR(TODAY()),MONTH(TODAY())-1,1),I29&lt;&gt;"",ISNUMBER(I29),I29&gt;=TODAY(),K29="APTO"),"✔ ACCESO PERMITIDO","✘ SIN ACCESO")</f>
+        <f>IF(AND(G29="✔ Vigente",H29&lt;&gt;"",ISNUMBER(H29),H29&gt;=DATE(YEAR(TODAY()),MONTH(TODAY())-1,1),J29="✔ Vigente",UPPER(K29)="APTO"),"✔ ACCESO PERMITIDO","✘ SIN ACCESO")</f>
         <v/>
       </c>
       <c r="M29" s="12" t="n"/>
@@ -1846,7 +1846,7 @@
       </c>
       <c r="K30" s="13" t="n"/>
       <c r="L30" s="14">
-        <f>IF(AND(F30&lt;&gt;"",ISNUMBER(F30),F30&gt;=TODAY(),H30&lt;&gt;"",ISNUMBER(H30),H30&gt;=DATE(YEAR(TODAY()),MONTH(TODAY())-1,1),I30&lt;&gt;"",ISNUMBER(I30),I30&gt;=TODAY(),K30="APTO"),"✔ ACCESO PERMITIDO","✘ SIN ACCESO")</f>
+        <f>IF(AND(G30="✔ Vigente",H30&lt;&gt;"",ISNUMBER(H30),H30&gt;=DATE(YEAR(TODAY()),MONTH(TODAY())-1,1),J30="✔ Vigente",UPPER(K30)="APTO"),"✔ ACCESO PERMITIDO","✘ SIN ACCESO")</f>
         <v/>
       </c>
       <c r="M30" s="12" t="n"/>
@@ -1878,7 +1878,7 @@
       </c>
       <c r="K31" s="13" t="n"/>
       <c r="L31" s="16">
-        <f>IF(AND(F31&lt;&gt;"",ISNUMBER(F31),F31&gt;=TODAY(),H31&lt;&gt;"",ISNUMBER(H31),H31&gt;=DATE(YEAR(TODAY()),MONTH(TODAY())-1,1),I31&lt;&gt;"",ISNUMBER(I31),I31&gt;=TODAY(),K31="APTO"),"✔ ACCESO PERMITIDO","✘ SIN ACCESO")</f>
+        <f>IF(AND(G31="✔ Vigente",H31&lt;&gt;"",ISNUMBER(H31),H31&gt;=DATE(YEAR(TODAY()),MONTH(TODAY())-1,1),J31="✔ Vigente",UPPER(K31)="APTO"),"✔ ACCESO PERMITIDO","✘ SIN ACCESO")</f>
         <v/>
       </c>
       <c r="M31" s="12" t="n"/>
@@ -1910,7 +1910,7 @@
       </c>
       <c r="K32" s="13" t="n"/>
       <c r="L32" s="14">
-        <f>IF(AND(F32&lt;&gt;"",ISNUMBER(F32),F32&gt;=TODAY(),H32&lt;&gt;"",ISNUMBER(H32),H32&gt;=DATE(YEAR(TODAY()),MONTH(TODAY())-1,1),I32&lt;&gt;"",ISNUMBER(I32),I32&gt;=TODAY(),K32="APTO"),"✔ ACCESO PERMITIDO","✘ SIN ACCESO")</f>
+        <f>IF(AND(G32="✔ Vigente",H32&lt;&gt;"",ISNUMBER(H32),H32&gt;=DATE(YEAR(TODAY()),MONTH(TODAY())-1,1),J32="✔ Vigente",UPPER(K32)="APTO"),"✔ ACCESO PERMITIDO","✘ SIN ACCESO")</f>
         <v/>
       </c>
       <c r="M32" s="12" t="n"/>
@@ -1942,7 +1942,7 @@
       </c>
       <c r="K33" s="13" t="n"/>
       <c r="L33" s="16">
-        <f>IF(AND(F33&lt;&gt;"",ISNUMBER(F33),F33&gt;=TODAY(),H33&lt;&gt;"",ISNUMBER(H33),H33&gt;=DATE(YEAR(TODAY()),MONTH(TODAY())-1,1),I33&lt;&gt;"",ISNUMBER(I33),I33&gt;=TODAY(),K33="APTO"),"✔ ACCESO PERMITIDO","✘ SIN ACCESO")</f>
+        <f>IF(AND(G33="✔ Vigente",H33&lt;&gt;"",ISNUMBER(H33),H33&gt;=DATE(YEAR(TODAY()),MONTH(TODAY())-1,1),J33="✔ Vigente",UPPER(K33)="APTO"),"✔ ACCESO PERMITIDO","✘ SIN ACCESO")</f>
         <v/>
       </c>
       <c r="M33" s="12" t="n"/>
@@ -1974,7 +1974,7 @@
       </c>
       <c r="K34" s="13" t="n"/>
       <c r="L34" s="14">
-        <f>IF(AND(F34&lt;&gt;"",ISNUMBER(F34),F34&gt;=TODAY(),H34&lt;&gt;"",ISNUMBER(H34),H34&gt;=DATE(YEAR(TODAY()),MONTH(TODAY())-1,1),I34&lt;&gt;"",ISNUMBER(I34),I34&gt;=TODAY(),K34="APTO"),"✔ ACCESO PERMITIDO","✘ SIN ACCESO")</f>
+        <f>IF(AND(G34="✔ Vigente",H34&lt;&gt;"",ISNUMBER(H34),H34&gt;=DATE(YEAR(TODAY()),MONTH(TODAY())-1,1),J34="✔ Vigente",UPPER(K34)="APTO"),"✔ ACCESO PERMITIDO","✘ SIN ACCESO")</f>
         <v/>
       </c>
       <c r="M34" s="12" t="n"/>
@@ -2006,7 +2006,7 @@
       </c>
       <c r="K35" s="13" t="n"/>
       <c r="L35" s="16">
-        <f>IF(AND(F35&lt;&gt;"",ISNUMBER(F35),F35&gt;=TODAY(),H35&lt;&gt;"",ISNUMBER(H35),H35&gt;=DATE(YEAR(TODAY()),MONTH(TODAY())-1,1),I35&lt;&gt;"",ISNUMBER(I35),I35&gt;=TODAY(),K35="APTO"),"✔ ACCESO PERMITIDO","✘ SIN ACCESO")</f>
+        <f>IF(AND(G35="✔ Vigente",H35&lt;&gt;"",ISNUMBER(H35),H35&gt;=DATE(YEAR(TODAY()),MONTH(TODAY())-1,1),J35="✔ Vigente",UPPER(K35)="APTO"),"✔ ACCESO PERMITIDO","✘ SIN ACCESO")</f>
         <v/>
       </c>
       <c r="M35" s="12" t="n"/>
@@ -2038,7 +2038,7 @@
       </c>
       <c r="K36" s="13" t="n"/>
       <c r="L36" s="14">
-        <f>IF(AND(F36&lt;&gt;"",ISNUMBER(F36),F36&gt;=TODAY(),H36&lt;&gt;"",ISNUMBER(H36),H36&gt;=DATE(YEAR(TODAY()),MONTH(TODAY())-1,1),I36&lt;&gt;"",ISNUMBER(I36),I36&gt;=TODAY(),K36="APTO"),"✔ ACCESO PERMITIDO","✘ SIN ACCESO")</f>
+        <f>IF(AND(G36="✔ Vigente",H36&lt;&gt;"",ISNUMBER(H36),H36&gt;=DATE(YEAR(TODAY()),MONTH(TODAY())-1,1),J36="✔ Vigente",UPPER(K36)="APTO"),"✔ ACCESO PERMITIDO","✘ SIN ACCESO")</f>
         <v/>
       </c>
       <c r="M36" s="12" t="n"/>
@@ -2070,7 +2070,7 @@
       </c>
       <c r="K37" s="13" t="n"/>
       <c r="L37" s="16">
-        <f>IF(AND(F37&lt;&gt;"",ISNUMBER(F37),F37&gt;=TODAY(),H37&lt;&gt;"",ISNUMBER(H37),H37&gt;=DATE(YEAR(TODAY()),MONTH(TODAY())-1,1),I37&lt;&gt;"",ISNUMBER(I37),I37&gt;=TODAY(),K37="APTO"),"✔ ACCESO PERMITIDO","✘ SIN ACCESO")</f>
+        <f>IF(AND(G37="✔ Vigente",H37&lt;&gt;"",ISNUMBER(H37),H37&gt;=DATE(YEAR(TODAY()),MONTH(TODAY())-1,1),J37="✔ Vigente",UPPER(K37)="APTO"),"✔ ACCESO PERMITIDO","✘ SIN ACCESO")</f>
         <v/>
       </c>
       <c r="M37" s="12" t="n"/>
@@ -2102,7 +2102,7 @@
       </c>
       <c r="K38" s="13" t="n"/>
       <c r="L38" s="14">
-        <f>IF(AND(F38&lt;&gt;"",ISNUMBER(F38),F38&gt;=TODAY(),H38&lt;&gt;"",ISNUMBER(H38),H38&gt;=DATE(YEAR(TODAY()),MONTH(TODAY())-1,1),I38&lt;&gt;"",ISNUMBER(I38),I38&gt;=TODAY(),K38="APTO"),"✔ ACCESO PERMITIDO","✘ SIN ACCESO")</f>
+        <f>IF(AND(G38="✔ Vigente",H38&lt;&gt;"",ISNUMBER(H38),H38&gt;=DATE(YEAR(TODAY()),MONTH(TODAY())-1,1),J38="✔ Vigente",UPPER(K38)="APTO"),"✔ ACCESO PERMITIDO","✘ SIN ACCESO")</f>
         <v/>
       </c>
       <c r="M38" s="12" t="n"/>
@@ -2134,7 +2134,7 @@
       </c>
       <c r="K39" s="13" t="n"/>
       <c r="L39" s="16">
-        <f>IF(AND(F39&lt;&gt;"",ISNUMBER(F39),F39&gt;=TODAY(),H39&lt;&gt;"",ISNUMBER(H39),H39&gt;=DATE(YEAR(TODAY()),MONTH(TODAY())-1,1),I39&lt;&gt;"",ISNUMBER(I39),I39&gt;=TODAY(),K39="APTO"),"✔ ACCESO PERMITIDO","✘ SIN ACCESO")</f>
+        <f>IF(AND(G39="✔ Vigente",H39&lt;&gt;"",ISNUMBER(H39),H39&gt;=DATE(YEAR(TODAY()),MONTH(TODAY())-1,1),J39="✔ Vigente",UPPER(K39)="APTO"),"✔ ACCESO PERMITIDO","✘ SIN ACCESO")</f>
         <v/>
       </c>
       <c r="M39" s="12" t="n"/>
@@ -2166,7 +2166,7 @@
       </c>
       <c r="K40" s="13" t="n"/>
       <c r="L40" s="14">
-        <f>IF(AND(F40&lt;&gt;"",ISNUMBER(F40),F40&gt;=TODAY(),H40&lt;&gt;"",ISNUMBER(H40),H40&gt;=DATE(YEAR(TODAY()),MONTH(TODAY())-1,1),I40&lt;&gt;"",ISNUMBER(I40),I40&gt;=TODAY(),K40="APTO"),"✔ ACCESO PERMITIDO","✘ SIN ACCESO")</f>
+        <f>IF(AND(G40="✔ Vigente",H40&lt;&gt;"",ISNUMBER(H40),H40&gt;=DATE(YEAR(TODAY()),MONTH(TODAY())-1,1),J40="✔ Vigente",UPPER(K40)="APTO"),"✔ ACCESO PERMITIDO","✘ SIN ACCESO")</f>
         <v/>
       </c>
       <c r="M40" s="12" t="n"/>
@@ -2198,7 +2198,7 @@
       </c>
       <c r="K41" s="13" t="n"/>
       <c r="L41" s="16">
-        <f>IF(AND(F41&lt;&gt;"",ISNUMBER(F41),F41&gt;=TODAY(),H41&lt;&gt;"",ISNUMBER(H41),H41&gt;=DATE(YEAR(TODAY()),MONTH(TODAY())-1,1),I41&lt;&gt;"",ISNUMBER(I41),I41&gt;=TODAY(),K41="APTO"),"✔ ACCESO PERMITIDO","✘ SIN ACCESO")</f>
+        <f>IF(AND(G41="✔ Vigente",H41&lt;&gt;"",ISNUMBER(H41),H41&gt;=DATE(YEAR(TODAY()),MONTH(TODAY())-1,1),J41="✔ Vigente",UPPER(K41)="APTO"),"✔ ACCESO PERMITIDO","✘ SIN ACCESO")</f>
         <v/>
       </c>
       <c r="M41" s="12" t="n"/>
@@ -2230,7 +2230,7 @@
       </c>
       <c r="K42" s="13" t="n"/>
       <c r="L42" s="14">
-        <f>IF(AND(F42&lt;&gt;"",ISNUMBER(F42),F42&gt;=TODAY(),H42&lt;&gt;"",ISNUMBER(H42),H42&gt;=DATE(YEAR(TODAY()),MONTH(TODAY())-1,1),I42&lt;&gt;"",ISNUMBER(I42),I42&gt;=TODAY(),K42="APTO"),"✔ ACCESO PERMITIDO","✘ SIN ACCESO")</f>
+        <f>IF(AND(G42="✔ Vigente",H42&lt;&gt;"",ISNUMBER(H42),H42&gt;=DATE(YEAR(TODAY()),MONTH(TODAY())-1,1),J42="✔ Vigente",UPPER(K42)="APTO"),"✔ ACCESO PERMITIDO","✘ SIN ACCESO")</f>
         <v/>
       </c>
       <c r="M42" s="12" t="n"/>
@@ -2262,7 +2262,7 @@
       </c>
       <c r="K43" s="13" t="n"/>
       <c r="L43" s="16">
-        <f>IF(AND(F43&lt;&gt;"",ISNUMBER(F43),F43&gt;=TODAY(),H43&lt;&gt;"",ISNUMBER(H43),H43&gt;=DATE(YEAR(TODAY()),MONTH(TODAY())-1,1),I43&lt;&gt;"",ISNUMBER(I43),I43&gt;=TODAY(),K43="APTO"),"✔ ACCESO PERMITIDO","✘ SIN ACCESO")</f>
+        <f>IF(AND(G43="✔ Vigente",H43&lt;&gt;"",ISNUMBER(H43),H43&gt;=DATE(YEAR(TODAY()),MONTH(TODAY())-1,1),J43="✔ Vigente",UPPER(K43)="APTO"),"✔ ACCESO PERMITIDO","✘ SIN ACCESO")</f>
         <v/>
       </c>
       <c r="M43" s="12" t="n"/>
@@ -2294,7 +2294,7 @@
       </c>
       <c r="K44" s="13" t="n"/>
       <c r="L44" s="14">
-        <f>IF(AND(F44&lt;&gt;"",ISNUMBER(F44),F44&gt;=TODAY(),H44&lt;&gt;"",ISNUMBER(H44),H44&gt;=DATE(YEAR(TODAY()),MONTH(TODAY())-1,1),I44&lt;&gt;"",ISNUMBER(I44),I44&gt;=TODAY(),K44="APTO"),"✔ ACCESO PERMITIDO","✘ SIN ACCESO")</f>
+        <f>IF(AND(G44="✔ Vigente",H44&lt;&gt;"",ISNUMBER(H44),H44&gt;=DATE(YEAR(TODAY()),MONTH(TODAY())-1,1),J44="✔ Vigente",UPPER(K44)="APTO"),"✔ ACCESO PERMITIDO","✘ SIN ACCESO")</f>
         <v/>
       </c>
       <c r="M44" s="12" t="n"/>
@@ -2326,7 +2326,7 @@
       </c>
       <c r="K45" s="13" t="n"/>
       <c r="L45" s="16">
-        <f>IF(AND(F45&lt;&gt;"",ISNUMBER(F45),F45&gt;=TODAY(),H45&lt;&gt;"",ISNUMBER(H45),H45&gt;=DATE(YEAR(TODAY()),MONTH(TODAY())-1,1),I45&lt;&gt;"",ISNUMBER(I45),I45&gt;=TODAY(),K45="APTO"),"✔ ACCESO PERMITIDO","✘ SIN ACCESO")</f>
+        <f>IF(AND(G45="✔ Vigente",H45&lt;&gt;"",ISNUMBER(H45),H45&gt;=DATE(YEAR(TODAY()),MONTH(TODAY())-1,1),J45="✔ Vigente",UPPER(K45)="APTO"),"✔ ACCESO PERMITIDO","✘ SIN ACCESO")</f>
         <v/>
       </c>
       <c r="M45" s="12" t="n"/>
@@ -2358,7 +2358,7 @@
       </c>
       <c r="K46" s="13" t="n"/>
       <c r="L46" s="14">
-        <f>IF(AND(F46&lt;&gt;"",ISNUMBER(F46),F46&gt;=TODAY(),H46&lt;&gt;"",ISNUMBER(H46),H46&gt;=DATE(YEAR(TODAY()),MONTH(TODAY())-1,1),I46&lt;&gt;"",ISNUMBER(I46),I46&gt;=TODAY(),K46="APTO"),"✔ ACCESO PERMITIDO","✘ SIN ACCESO")</f>
+        <f>IF(AND(G46="✔ Vigente",H46&lt;&gt;"",ISNUMBER(H46),H46&gt;=DATE(YEAR(TODAY()),MONTH(TODAY())-1,1),J46="✔ Vigente",UPPER(K46)="APTO"),"✔ ACCESO PERMITIDO","✘ SIN ACCESO")</f>
         <v/>
       </c>
       <c r="M46" s="12" t="n"/>
@@ -2390,7 +2390,7 @@
       </c>
       <c r="K47" s="13" t="n"/>
       <c r="L47" s="16">
-        <f>IF(AND(F47&lt;&gt;"",ISNUMBER(F47),F47&gt;=TODAY(),H47&lt;&gt;"",ISNUMBER(H47),H47&gt;=DATE(YEAR(TODAY()),MONTH(TODAY())-1,1),I47&lt;&gt;"",ISNUMBER(I47),I47&gt;=TODAY(),K47="APTO"),"✔ ACCESO PERMITIDO","✘ SIN ACCESO")</f>
+        <f>IF(AND(G47="✔ Vigente",H47&lt;&gt;"",ISNUMBER(H47),H47&gt;=DATE(YEAR(TODAY()),MONTH(TODAY())-1,1),J47="✔ Vigente",UPPER(K47)="APTO"),"✔ ACCESO PERMITIDO","✘ SIN ACCESO")</f>
         <v/>
       </c>
       <c r="M47" s="12" t="n"/>
@@ -2422,7 +2422,7 @@
       </c>
       <c r="K48" s="13" t="n"/>
       <c r="L48" s="14">
-        <f>IF(AND(F48&lt;&gt;"",ISNUMBER(F48),F48&gt;=TODAY(),H48&lt;&gt;"",ISNUMBER(H48),H48&gt;=DATE(YEAR(TODAY()),MONTH(TODAY())-1,1),I48&lt;&gt;"",ISNUMBER(I48),I48&gt;=TODAY(),K48="APTO"),"✔ ACCESO PERMITIDO","✘ SIN ACCESO")</f>
+        <f>IF(AND(G48="✔ Vigente",H48&lt;&gt;"",ISNUMBER(H48),H48&gt;=DATE(YEAR(TODAY()),MONTH(TODAY())-1,1),J48="✔ Vigente",UPPER(K48)="APTO"),"✔ ACCESO PERMITIDO","✘ SIN ACCESO")</f>
         <v/>
       </c>
       <c r="M48" s="12" t="n"/>
@@ -2454,7 +2454,7 @@
       </c>
       <c r="K49" s="13" t="n"/>
       <c r="L49" s="16">
-        <f>IF(AND(F49&lt;&gt;"",ISNUMBER(F49),F49&gt;=TODAY(),H49&lt;&gt;"",ISNUMBER(H49),H49&gt;=DATE(YEAR(TODAY()),MONTH(TODAY())-1,1),I49&lt;&gt;"",ISNUMBER(I49),I49&gt;=TODAY(),K49="APTO"),"✔ ACCESO PERMITIDO","✘ SIN ACCESO")</f>
+        <f>IF(AND(G49="✔ Vigente",H49&lt;&gt;"",ISNUMBER(H49),H49&gt;=DATE(YEAR(TODAY()),MONTH(TODAY())-1,1),J49="✔ Vigente",UPPER(K49)="APTO"),"✔ ACCESO PERMITIDO","✘ SIN ACCESO")</f>
         <v/>
       </c>
       <c r="M49" s="12" t="n"/>
@@ -2486,7 +2486,7 @@
       </c>
       <c r="K50" s="13" t="n"/>
       <c r="L50" s="14">
-        <f>IF(AND(F50&lt;&gt;"",ISNUMBER(F50),F50&gt;=TODAY(),H50&lt;&gt;"",ISNUMBER(H50),H50&gt;=DATE(YEAR(TODAY()),MONTH(TODAY())-1,1),I50&lt;&gt;"",ISNUMBER(I50),I50&gt;=TODAY(),K50="APTO"),"✔ ACCESO PERMITIDO","✘ SIN ACCESO")</f>
+        <f>IF(AND(G50="✔ Vigente",H50&lt;&gt;"",ISNUMBER(H50),H50&gt;=DATE(YEAR(TODAY()),MONTH(TODAY())-1,1),J50="✔ Vigente",UPPER(K50)="APTO"),"✔ ACCESO PERMITIDO","✘ SIN ACCESO")</f>
         <v/>
       </c>
       <c r="M50" s="12" t="n"/>
@@ -2518,7 +2518,7 @@
       </c>
       <c r="K51" s="13" t="n"/>
       <c r="L51" s="16">
-        <f>IF(AND(F51&lt;&gt;"",ISNUMBER(F51),F51&gt;=TODAY(),H51&lt;&gt;"",ISNUMBER(H51),H51&gt;=DATE(YEAR(TODAY()),MONTH(TODAY())-1,1),I51&lt;&gt;"",ISNUMBER(I51),I51&gt;=TODAY(),K51="APTO"),"✔ ACCESO PERMITIDO","✘ SIN ACCESO")</f>
+        <f>IF(AND(G51="✔ Vigente",H51&lt;&gt;"",ISNUMBER(H51),H51&gt;=DATE(YEAR(TODAY()),MONTH(TODAY())-1,1),J51="✔ Vigente",UPPER(K51)="APTO"),"✔ ACCESO PERMITIDO","✘ SIN ACCESO")</f>
         <v/>
       </c>
       <c r="M51" s="12" t="n"/>
@@ -2550,7 +2550,7 @@
       </c>
       <c r="K52" s="13" t="n"/>
       <c r="L52" s="14">
-        <f>IF(AND(F52&lt;&gt;"",ISNUMBER(F52),F52&gt;=TODAY(),H52&lt;&gt;"",ISNUMBER(H52),H52&gt;=DATE(YEAR(TODAY()),MONTH(TODAY())-1,1),I52&lt;&gt;"",ISNUMBER(I52),I52&gt;=TODAY(),K52="APTO"),"✔ ACCESO PERMITIDO","✘ SIN ACCESO")</f>
+        <f>IF(AND(G52="✔ Vigente",H52&lt;&gt;"",ISNUMBER(H52),H52&gt;=DATE(YEAR(TODAY()),MONTH(TODAY())-1,1),J52="✔ Vigente",UPPER(K52)="APTO"),"✔ ACCESO PERMITIDO","✘ SIN ACCESO")</f>
         <v/>
       </c>
       <c r="M52" s="12" t="n"/>
@@ -2582,7 +2582,7 @@
       </c>
       <c r="K53" s="13" t="n"/>
       <c r="L53" s="16">
-        <f>IF(AND(F53&lt;&gt;"",ISNUMBER(F53),F53&gt;=TODAY(),H53&lt;&gt;"",ISNUMBER(H53),H53&gt;=DATE(YEAR(TODAY()),MONTH(TODAY())-1,1),I53&lt;&gt;"",ISNUMBER(I53),I53&gt;=TODAY(),K53="APTO"),"✔ ACCESO PERMITIDO","✘ SIN ACCESO")</f>
+        <f>IF(AND(G53="✔ Vigente",H53&lt;&gt;"",ISNUMBER(H53),H53&gt;=DATE(YEAR(TODAY()),MONTH(TODAY())-1,1),J53="✔ Vigente",UPPER(K53)="APTO"),"✔ ACCESO PERMITIDO","✘ SIN ACCESO")</f>
         <v/>
       </c>
       <c r="M53" s="12" t="n"/>
@@ -2614,7 +2614,7 @@
       </c>
       <c r="K54" s="13" t="n"/>
       <c r="L54" s="14">
-        <f>IF(AND(F54&lt;&gt;"",ISNUMBER(F54),F54&gt;=TODAY(),H54&lt;&gt;"",ISNUMBER(H54),H54&gt;=DATE(YEAR(TODAY()),MONTH(TODAY())-1,1),I54&lt;&gt;"",ISNUMBER(I54),I54&gt;=TODAY(),K54="APTO"),"✔ ACCESO PERMITIDO","✘ SIN ACCESO")</f>
+        <f>IF(AND(G54="✔ Vigente",H54&lt;&gt;"",ISNUMBER(H54),H54&gt;=DATE(YEAR(TODAY()),MONTH(TODAY())-1,1),J54="✔ Vigente",UPPER(K54)="APTO"),"✔ ACCESO PERMITIDO","✘ SIN ACCESO")</f>
         <v/>
       </c>
       <c r="M54" s="12" t="n"/>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="K55" s="13" t="n"/>
       <c r="L55" s="16">
-        <f>IF(AND(F55&lt;&gt;"",ISNUMBER(F55),F55&gt;=TODAY(),H55&lt;&gt;"",ISNUMBER(H55),H55&gt;=DATE(YEAR(TODAY()),MONTH(TODAY())-1,1),I55&lt;&gt;"",ISNUMBER(I55),I55&gt;=TODAY(),K55="APTO"),"✔ ACCESO PERMITIDO","✘ SIN ACCESO")</f>
+        <f>IF(AND(G55="✔ Vigente",H55&lt;&gt;"",ISNUMBER(H55),H55&gt;=DATE(YEAR(TODAY()),MONTH(TODAY())-1,1),J55="✔ Vigente",UPPER(K55)="APTO"),"✔ ACCESO PERMITIDO","✘ SIN ACCESO")</f>
         <v/>
       </c>
       <c r="M55" s="12" t="n"/>

--- a/Consolidado_contratistas_plantabal.xlsx
+++ b/Consolidado_contratistas_plantabal.xlsx
@@ -2714,29 +2714,32 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K6:K55">
-    <cfRule type="expression" priority="13" dxfId="17">
+    <cfRule type="expression" priority="13" dxfId="15">
+      <formula>J6="✘ Vencido"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="14" dxfId="17">
       <formula>UPPER(K6)="APTO"</formula>
     </cfRule>
-    <cfRule type="expression" priority="14" dxfId="15">
+    <cfRule type="expression" priority="15" dxfId="15">
       <formula>UPPER(K6)="NO APTO"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L6:L55">
-    <cfRule type="expression" priority="15" dxfId="17">
+    <cfRule type="expression" priority="16" dxfId="17">
       <formula>L6="✔ ACCESO PERMITIDO"</formula>
     </cfRule>
-    <cfRule type="expression" priority="16" dxfId="15">
+    <cfRule type="expression" priority="17" dxfId="15">
       <formula>L6="✘ SIN ACCESO"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M6:R55">
-    <cfRule type="expression" priority="17" dxfId="15">
+    <cfRule type="expression" priority="18" dxfId="15">
       <formula>AND(M6&lt;&gt;"",ISNUMBER(M6),M6&lt;TODAY())</formula>
     </cfRule>
-    <cfRule type="expression" priority="18" dxfId="16">
+    <cfRule type="expression" priority="19" dxfId="16">
       <formula>AND(M6&lt;&gt;"",ISNUMBER(M6),M6&gt;=TODAY(),M6&lt;=TODAY()+30)</formula>
     </cfRule>
-    <cfRule type="expression" priority="19" dxfId="17">
+    <cfRule type="expression" priority="20" dxfId="17">
       <formula>AND(M6&lt;&gt;"",ISNUMBER(M6),M6&gt;TODAY()+30)</formula>
     </cfRule>
   </conditionalFormatting>

--- a/Consolidado_contratistas_plantabal.xlsx
+++ b/Consolidado_contratistas_plantabal.xlsx
@@ -861,7 +861,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:S55"/>
+  <dimension ref="A1:T55"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6328125" defaultRowHeight="14.5"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -872,7 +872,7 @@
     <col width="15" customWidth="1" min="8" max="8"/>
     <col width="12" customWidth="1" min="9" max="9"/>
     <col width="11" customWidth="1" min="10" max="10"/>
-    <col width="16" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
     <col width="14" customWidth="1" min="12" max="12"/>
     <col width="15" customWidth="1" min="13" max="15"/>
     <col width="14" customWidth="1" min="16" max="16"/>
@@ -901,7 +901,7 @@
           <t>▶  REQUISITOS DE ACCESO A PLANTA</t>
         </is>
       </c>
-      <c r="M3" s="3" t="inlineStr">
+      <c r="N3" s="3" t="inlineStr">
         <is>
           <t>▶  HABILITACIONES POR TIPO DE TRABAJO</t>
         </is>
@@ -975,55 +975,61 @@
           <t>Aptitud de Ingreso</t>
         </is>
       </c>
-      <c r="L5" s="8" t="inlineStr">
+      <c r="L5" s="22" t="inlineStr">
+        <is>
+          <t>Aptitud
+(Ingreso manual)</t>
+        </is>
+      </c>
+      <c r="M5" s="8" t="inlineStr">
         <is>
           <t>¿ACCESO
 A PLANTA?</t>
         </is>
       </c>
-      <c r="M5" s="9" t="inlineStr">
+      <c r="N5" s="9" t="inlineStr">
         <is>
           <t>Cert. Prevención
 Riesgos Eléctricos
 (Caducidad)</t>
         </is>
       </c>
-      <c r="N5" s="9" t="inlineStr">
+      <c r="O5" s="9" t="inlineStr">
         <is>
           <t>Cert. Trabajos
 en Altura
 (Caducidad)</t>
         </is>
       </c>
-      <c r="O5" s="9" t="inlineStr">
+      <c r="P5" s="9" t="inlineStr">
         <is>
           <t>Cert. Espacios
 Confinados
 (Caducidad)</t>
         </is>
       </c>
-      <c r="P5" s="9" t="inlineStr">
+      <c r="Q5" s="9" t="inlineStr">
         <is>
           <t>Cert. Trabajos
 en Caliente
 (Caducidad)</t>
         </is>
       </c>
-      <c r="Q5" s="9" t="inlineStr">
+      <c r="R5" s="9" t="inlineStr">
         <is>
           <t>Cert. Prevención
 de Riesgos
 (Caducidad)</t>
         </is>
       </c>
-      <c r="R5" s="9" t="inlineStr">
+      <c r="S5" s="9" t="inlineStr">
         <is>
           <t>Curso Primeros
 Auxilios
 (Fecha emisión)</t>
         </is>
       </c>
-      <c r="S5" s="9" t="inlineStr">
+      <c r="T5" s="9" t="inlineStr">
         <is>
           <t>Observaciones</t>
         </is>
@@ -1068,26 +1074,26 @@
         <f>IF(I6="","",IF(I6&gt;=TODAY(),"✔ Vigente","✘ Vencido"))</f>
         <v/>
       </c>
-      <c r="K6" s="13" t="inlineStr">
-        <is>
-          <t>Apto</t>
-        </is>
-      </c>
-      <c r="L6" s="14">
-        <f>IF(AND(G6="✔ Vigente",H6&lt;&gt;"",ISNUMBER(H6),H6&gt;=DATE(YEAR(TODAY()),MONTH(TODAY())-1,1),J6="✔ Vigente",UPPER(K6)="APTO"),"✔ ACCESO PERMITIDO","✘ SIN ACCESO")</f>
-        <v/>
-      </c>
-      <c r="M6" s="12" t="n">
+      <c r="K6" s="13">
+        <f>IF(J6="✘ Vencido","NO APTO",IF(L6="","",UPPER(L6)))</f>
+        <v/>
+      </c>
+      <c r="L6" s="13" t="n"/>
+      <c r="M6" s="14">
+        <f>IF(AND(G6="✔ Vigente",H6&lt;&gt;"",ISNUMBER(H6),H6&gt;=DATE(YEAR(TODAY()),MONTH(TODAY())-1,1),J6="✔ Vigente",K6="APTO"),"✔ ACCESO PERMITIDO","✘ SIN ACCESO")</f>
+        <v/>
+      </c>
+      <c r="N6" s="12" t="n">
         <v>47481</v>
       </c>
-      <c r="N6" s="12" t="n"/>
       <c r="O6" s="12" t="n"/>
       <c r="P6" s="12" t="n"/>
-      <c r="Q6" s="12" t="n">
+      <c r="Q6" s="12" t="n"/>
+      <c r="R6" s="12" t="n">
         <v>47392</v>
       </c>
-      <c r="R6" s="12" t="n"/>
-      <c r="S6" s="11" t="n"/>
+      <c r="S6" s="12" t="n"/>
+      <c r="T6" s="11" t="n"/>
     </row>
     <row r="7" ht="19.5" customHeight="1">
       <c r="A7" s="15" t="n">
@@ -1108,18 +1114,22 @@
         <f>IF(I7="","",IF(I7&gt;=TODAY(),"✔ Vigente","✘ Vencido"))</f>
         <v/>
       </c>
-      <c r="K7" s="13" t="n"/>
-      <c r="L7" s="16">
-        <f>IF(AND(G7="✔ Vigente",H7&lt;&gt;"",ISNUMBER(H7),H7&gt;=DATE(YEAR(TODAY()),MONTH(TODAY())-1,1),J7="✔ Vigente",UPPER(K7)="APTO"),"✔ ACCESO PERMITIDO","✘ SIN ACCESO")</f>
-        <v/>
-      </c>
-      <c r="M7" s="12" t="n"/>
+      <c r="K7" s="13">
+        <f>IF(J7="✘ Vencido","NO APTO",IF(L7="","",UPPER(L7)))</f>
+        <v/>
+      </c>
+      <c r="L7" s="13" t="n"/>
+      <c r="M7" s="16">
+        <f>IF(AND(G7="✔ Vigente",H7&lt;&gt;"",ISNUMBER(H7),H7&gt;=DATE(YEAR(TODAY()),MONTH(TODAY())-1,1),J7="✔ Vigente",K7="APTO"),"✔ ACCESO PERMITIDO","✘ SIN ACCESO")</f>
+        <v/>
+      </c>
       <c r="N7" s="12" t="n"/>
       <c r="O7" s="12" t="n"/>
       <c r="P7" s="12" t="n"/>
       <c r="Q7" s="12" t="n"/>
       <c r="R7" s="12" t="n"/>
-      <c r="S7" s="11" t="n"/>
+      <c r="S7" s="12" t="n"/>
+      <c r="T7" s="11" t="n"/>
     </row>
     <row r="8" ht="19.5" customHeight="1">
       <c r="A8" s="10" t="n">
@@ -1140,18 +1150,22 @@
         <f>IF(I8="","",IF(I8&gt;=TODAY(),"✔ Vigente","✘ Vencido"))</f>
         <v/>
       </c>
-      <c r="K8" s="13" t="n"/>
-      <c r="L8" s="14">
-        <f>IF(AND(G8="✔ Vigente",H8&lt;&gt;"",ISNUMBER(H8),H8&gt;=DATE(YEAR(TODAY()),MONTH(TODAY())-1,1),J8="✔ Vigente",UPPER(K8)="APTO"),"✔ ACCESO PERMITIDO","✘ SIN ACCESO")</f>
-        <v/>
-      </c>
-      <c r="M8" s="12" t="n"/>
+      <c r="K8" s="13">
+        <f>IF(J8="✘ Vencido","NO APTO",IF(L8="","",UPPER(L8)))</f>
+        <v/>
+      </c>
+      <c r="L8" s="13" t="n"/>
+      <c r="M8" s="14">
+        <f>IF(AND(G8="✔ Vigente",H8&lt;&gt;"",ISNUMBER(H8),H8&gt;=DATE(YEAR(TODAY()),MONTH(TODAY())-1,1),J8="✔ Vigente",K8="APTO"),"✔ ACCESO PERMITIDO","✘ SIN ACCESO")</f>
+        <v/>
+      </c>
       <c r="N8" s="12" t="n"/>
       <c r="O8" s="12" t="n"/>
       <c r="P8" s="12" t="n"/>
       <c r="Q8" s="12" t="n"/>
       <c r="R8" s="12" t="n"/>
-      <c r="S8" s="11" t="n"/>
+      <c r="S8" s="12" t="n"/>
+      <c r="T8" s="11" t="n"/>
     </row>
     <row r="9" ht="19.5" customHeight="1">
       <c r="A9" s="15" t="n">
@@ -1172,18 +1186,22 @@
         <f>IF(I9="","",IF(I9&gt;=TODAY(),"✔ Vigente","✘ Vencido"))</f>
         <v/>
       </c>
-      <c r="K9" s="13" t="n"/>
-      <c r="L9" s="16">
-        <f>IF(AND(G9="✔ Vigente",H9&lt;&gt;"",ISNUMBER(H9),H9&gt;=DATE(YEAR(TODAY()),MONTH(TODAY())-1,1),J9="✔ Vigente",UPPER(K9)="APTO"),"✔ ACCESO PERMITIDO","✘ SIN ACCESO")</f>
-        <v/>
-      </c>
-      <c r="M9" s="12" t="n"/>
+      <c r="K9" s="13">
+        <f>IF(J9="✘ Vencido","NO APTO",IF(L9="","",UPPER(L9)))</f>
+        <v/>
+      </c>
+      <c r="L9" s="13" t="n"/>
+      <c r="M9" s="16">
+        <f>IF(AND(G9="✔ Vigente",H9&lt;&gt;"",ISNUMBER(H9),H9&gt;=DATE(YEAR(TODAY()),MONTH(TODAY())-1,1),J9="✔ Vigente",K9="APTO"),"✔ ACCESO PERMITIDO","✘ SIN ACCESO")</f>
+        <v/>
+      </c>
       <c r="N9" s="12" t="n"/>
       <c r="O9" s="12" t="n"/>
       <c r="P9" s="12" t="n"/>
       <c r="Q9" s="12" t="n"/>
       <c r="R9" s="12" t="n"/>
-      <c r="S9" s="11" t="n"/>
+      <c r="S9" s="12" t="n"/>
+      <c r="T9" s="11" t="n"/>
     </row>
     <row r="10" ht="19.5" customHeight="1">
       <c r="A10" s="10" t="n">
@@ -1204,18 +1222,22 @@
         <f>IF(I10="","",IF(I10&gt;=TODAY(),"✔ Vigente","✘ Vencido"))</f>
         <v/>
       </c>
-      <c r="K10" s="13" t="n"/>
-      <c r="L10" s="14">
-        <f>IF(AND(G10="✔ Vigente",H10&lt;&gt;"",ISNUMBER(H10),H10&gt;=DATE(YEAR(TODAY()),MONTH(TODAY())-1,1),J10="✔ Vigente",UPPER(K10)="APTO"),"✔ ACCESO PERMITIDO","✘ SIN ACCESO")</f>
-        <v/>
-      </c>
-      <c r="M10" s="12" t="n"/>
+      <c r="K10" s="13">
+        <f>IF(J10="✘ Vencido","NO APTO",IF(L10="","",UPPER(L10)))</f>
+        <v/>
+      </c>
+      <c r="L10" s="13" t="n"/>
+      <c r="M10" s="14">
+        <f>IF(AND(G10="✔ Vigente",H10&lt;&gt;"",ISNUMBER(H10),H10&gt;=DATE(YEAR(TODAY()),MONTH(TODAY())-1,1),J10="✔ Vigente",K10="APTO"),"✔ ACCESO PERMITIDO","✘ SIN ACCESO")</f>
+        <v/>
+      </c>
       <c r="N10" s="12" t="n"/>
       <c r="O10" s="12" t="n"/>
       <c r="P10" s="12" t="n"/>
       <c r="Q10" s="12" t="n"/>
       <c r="R10" s="12" t="n"/>
-      <c r="S10" s="11" t="n"/>
+      <c r="S10" s="12" t="n"/>
+      <c r="T10" s="11" t="n"/>
     </row>
     <row r="11" ht="19.5" customHeight="1">
       <c r="A11" s="15" t="n">
@@ -1236,18 +1258,22 @@
         <f>IF(I11="","",IF(I11&gt;=TODAY(),"✔ Vigente","✘ Vencido"))</f>
         <v/>
       </c>
-      <c r="K11" s="13" t="n"/>
-      <c r="L11" s="16">
-        <f>IF(AND(G11="✔ Vigente",H11&lt;&gt;"",ISNUMBER(H11),H11&gt;=DATE(YEAR(TODAY()),MONTH(TODAY())-1,1),J11="✔ Vigente",UPPER(K11)="APTO"),"✔ ACCESO PERMITIDO","✘ SIN ACCESO")</f>
-        <v/>
-      </c>
-      <c r="M11" s="12" t="n"/>
+      <c r="K11" s="13">
+        <f>IF(J11="✘ Vencido","NO APTO",IF(L11="","",UPPER(L11)))</f>
+        <v/>
+      </c>
+      <c r="L11" s="13" t="n"/>
+      <c r="M11" s="16">
+        <f>IF(AND(G11="✔ Vigente",H11&lt;&gt;"",ISNUMBER(H11),H11&gt;=DATE(YEAR(TODAY()),MONTH(TODAY())-1,1),J11="✔ Vigente",K11="APTO"),"✔ ACCESO PERMITIDO","✘ SIN ACCESO")</f>
+        <v/>
+      </c>
       <c r="N11" s="12" t="n"/>
       <c r="O11" s="12" t="n"/>
       <c r="P11" s="12" t="n"/>
       <c r="Q11" s="12" t="n"/>
       <c r="R11" s="12" t="n"/>
-      <c r="S11" s="11" t="n"/>
+      <c r="S11" s="12" t="n"/>
+      <c r="T11" s="11" t="n"/>
     </row>
     <row r="12" ht="19.5" customHeight="1">
       <c r="A12" s="10" t="n">
@@ -1268,18 +1294,22 @@
         <f>IF(I12="","",IF(I12&gt;=TODAY(),"✔ Vigente","✘ Vencido"))</f>
         <v/>
       </c>
-      <c r="K12" s="13" t="n"/>
-      <c r="L12" s="14">
-        <f>IF(AND(G12="✔ Vigente",H12&lt;&gt;"",ISNUMBER(H12),H12&gt;=DATE(YEAR(TODAY()),MONTH(TODAY())-1,1),J12="✔ Vigente",UPPER(K12)="APTO"),"✔ ACCESO PERMITIDO","✘ SIN ACCESO")</f>
-        <v/>
-      </c>
-      <c r="M12" s="12" t="n"/>
+      <c r="K12" s="13">
+        <f>IF(J12="✘ Vencido","NO APTO",IF(L12="","",UPPER(L12)))</f>
+        <v/>
+      </c>
+      <c r="L12" s="13" t="n"/>
+      <c r="M12" s="14">
+        <f>IF(AND(G12="✔ Vigente",H12&lt;&gt;"",ISNUMBER(H12),H12&gt;=DATE(YEAR(TODAY()),MONTH(TODAY())-1,1),J12="✔ Vigente",K12="APTO"),"✔ ACCESO PERMITIDO","✘ SIN ACCESO")</f>
+        <v/>
+      </c>
       <c r="N12" s="12" t="n"/>
       <c r="O12" s="12" t="n"/>
       <c r="P12" s="12" t="n"/>
       <c r="Q12" s="12" t="n"/>
       <c r="R12" s="12" t="n"/>
-      <c r="S12" s="11" t="n"/>
+      <c r="S12" s="12" t="n"/>
+      <c r="T12" s="11" t="n"/>
     </row>
     <row r="13" ht="19.5" customHeight="1">
       <c r="A13" s="15" t="n">
@@ -1300,18 +1330,22 @@
         <f>IF(I13="","",IF(I13&gt;=TODAY(),"✔ Vigente","✘ Vencido"))</f>
         <v/>
       </c>
-      <c r="K13" s="13" t="n"/>
-      <c r="L13" s="16">
-        <f>IF(AND(G13="✔ Vigente",H13&lt;&gt;"",ISNUMBER(H13),H13&gt;=DATE(YEAR(TODAY()),MONTH(TODAY())-1,1),J13="✔ Vigente",UPPER(K13)="APTO"),"✔ ACCESO PERMITIDO","✘ SIN ACCESO")</f>
-        <v/>
-      </c>
-      <c r="M13" s="12" t="n"/>
+      <c r="K13" s="13">
+        <f>IF(J13="✘ Vencido","NO APTO",IF(L13="","",UPPER(L13)))</f>
+        <v/>
+      </c>
+      <c r="L13" s="13" t="n"/>
+      <c r="M13" s="16">
+        <f>IF(AND(G13="✔ Vigente",H13&lt;&gt;"",ISNUMBER(H13),H13&gt;=DATE(YEAR(TODAY()),MONTH(TODAY())-1,1),J13="✔ Vigente",K13="APTO"),"✔ ACCESO PERMITIDO","✘ SIN ACCESO")</f>
+        <v/>
+      </c>
       <c r="N13" s="12" t="n"/>
       <c r="O13" s="12" t="n"/>
       <c r="P13" s="12" t="n"/>
       <c r="Q13" s="12" t="n"/>
       <c r="R13" s="12" t="n"/>
-      <c r="S13" s="11" t="n"/>
+      <c r="S13" s="12" t="n"/>
+      <c r="T13" s="11" t="n"/>
     </row>
     <row r="14" ht="19.5" customHeight="1">
       <c r="A14" s="10" t="n">
@@ -1332,18 +1366,22 @@
         <f>IF(I14="","",IF(I14&gt;=TODAY(),"✔ Vigente","✘ Vencido"))</f>
         <v/>
       </c>
-      <c r="K14" s="13" t="n"/>
-      <c r="L14" s="14">
-        <f>IF(AND(G14="✔ Vigente",H14&lt;&gt;"",ISNUMBER(H14),H14&gt;=DATE(YEAR(TODAY()),MONTH(TODAY())-1,1),J14="✔ Vigente",UPPER(K14)="APTO"),"✔ ACCESO PERMITIDO","✘ SIN ACCESO")</f>
-        <v/>
-      </c>
-      <c r="M14" s="12" t="n"/>
+      <c r="K14" s="13">
+        <f>IF(J14="✘ Vencido","NO APTO",IF(L14="","",UPPER(L14)))</f>
+        <v/>
+      </c>
+      <c r="L14" s="13" t="n"/>
+      <c r="M14" s="14">
+        <f>IF(AND(G14="✔ Vigente",H14&lt;&gt;"",ISNUMBER(H14),H14&gt;=DATE(YEAR(TODAY()),MONTH(TODAY())-1,1),J14="✔ Vigente",K14="APTO"),"✔ ACCESO PERMITIDO","✘ SIN ACCESO")</f>
+        <v/>
+      </c>
       <c r="N14" s="12" t="n"/>
       <c r="O14" s="12" t="n"/>
       <c r="P14" s="12" t="n"/>
       <c r="Q14" s="12" t="n"/>
       <c r="R14" s="12" t="n"/>
-      <c r="S14" s="11" t="n"/>
+      <c r="S14" s="12" t="n"/>
+      <c r="T14" s="11" t="n"/>
     </row>
     <row r="15" ht="19.5" customHeight="1">
       <c r="A15" s="15" t="n">
@@ -1364,18 +1402,22 @@
         <f>IF(I15="","",IF(I15&gt;=TODAY(),"✔ Vigente","✘ Vencido"))</f>
         <v/>
       </c>
-      <c r="K15" s="13" t="n"/>
-      <c r="L15" s="16">
-        <f>IF(AND(G15="✔ Vigente",H15&lt;&gt;"",ISNUMBER(H15),H15&gt;=DATE(YEAR(TODAY()),MONTH(TODAY())-1,1),J15="✔ Vigente",UPPER(K15)="APTO"),"✔ ACCESO PERMITIDO","✘ SIN ACCESO")</f>
-        <v/>
-      </c>
-      <c r="M15" s="12" t="n"/>
+      <c r="K15" s="13">
+        <f>IF(J15="✘ Vencido","NO APTO",IF(L15="","",UPPER(L15)))</f>
+        <v/>
+      </c>
+      <c r="L15" s="13" t="n"/>
+      <c r="M15" s="16">
+        <f>IF(AND(G15="✔ Vigente",H15&lt;&gt;"",ISNUMBER(H15),H15&gt;=DATE(YEAR(TODAY()),MONTH(TODAY())-1,1),J15="✔ Vigente",K15="APTO"),"✔ ACCESO PERMITIDO","✘ SIN ACCESO")</f>
+        <v/>
+      </c>
       <c r="N15" s="12" t="n"/>
       <c r="O15" s="12" t="n"/>
       <c r="P15" s="12" t="n"/>
       <c r="Q15" s="12" t="n"/>
       <c r="R15" s="12" t="n"/>
-      <c r="S15" s="11" t="n"/>
+      <c r="S15" s="12" t="n"/>
+      <c r="T15" s="11" t="n"/>
     </row>
     <row r="16" ht="19.5" customHeight="1">
       <c r="A16" s="10" t="n">
@@ -1396,18 +1438,22 @@
         <f>IF(I16="","",IF(I16&gt;=TODAY(),"✔ Vigente","✘ Vencido"))</f>
         <v/>
       </c>
-      <c r="K16" s="13" t="n"/>
-      <c r="L16" s="14">
-        <f>IF(AND(G16="✔ Vigente",H16&lt;&gt;"",ISNUMBER(H16),H16&gt;=DATE(YEAR(TODAY()),MONTH(TODAY())-1,1),J16="✔ Vigente",UPPER(K16)="APTO"),"✔ ACCESO PERMITIDO","✘ SIN ACCESO")</f>
-        <v/>
-      </c>
-      <c r="M16" s="12" t="n"/>
+      <c r="K16" s="13">
+        <f>IF(J16="✘ Vencido","NO APTO",IF(L16="","",UPPER(L16)))</f>
+        <v/>
+      </c>
+      <c r="L16" s="13" t="n"/>
+      <c r="M16" s="14">
+        <f>IF(AND(G16="✔ Vigente",H16&lt;&gt;"",ISNUMBER(H16),H16&gt;=DATE(YEAR(TODAY()),MONTH(TODAY())-1,1),J16="✔ Vigente",K16="APTO"),"✔ ACCESO PERMITIDO","✘ SIN ACCESO")</f>
+        <v/>
+      </c>
       <c r="N16" s="12" t="n"/>
       <c r="O16" s="12" t="n"/>
       <c r="P16" s="12" t="n"/>
       <c r="Q16" s="12" t="n"/>
       <c r="R16" s="12" t="n"/>
-      <c r="S16" s="11" t="n"/>
+      <c r="S16" s="12" t="n"/>
+      <c r="T16" s="11" t="n"/>
     </row>
     <row r="17" ht="19.5" customHeight="1">
       <c r="A17" s="15" t="n">
@@ -1428,18 +1474,22 @@
         <f>IF(I17="","",IF(I17&gt;=TODAY(),"✔ Vigente","✘ Vencido"))</f>
         <v/>
       </c>
-      <c r="K17" s="13" t="n"/>
-      <c r="L17" s="16">
-        <f>IF(AND(G17="✔ Vigente",H17&lt;&gt;"",ISNUMBER(H17),H17&gt;=DATE(YEAR(TODAY()),MONTH(TODAY())-1,1),J17="✔ Vigente",UPPER(K17)="APTO"),"✔ ACCESO PERMITIDO","✘ SIN ACCESO")</f>
-        <v/>
-      </c>
-      <c r="M17" s="12" t="n"/>
+      <c r="K17" s="13">
+        <f>IF(J17="✘ Vencido","NO APTO",IF(L17="","",UPPER(L17)))</f>
+        <v/>
+      </c>
+      <c r="L17" s="13" t="n"/>
+      <c r="M17" s="16">
+        <f>IF(AND(G17="✔ Vigente",H17&lt;&gt;"",ISNUMBER(H17),H17&gt;=DATE(YEAR(TODAY()),MONTH(TODAY())-1,1),J17="✔ Vigente",K17="APTO"),"✔ ACCESO PERMITIDO","✘ SIN ACCESO")</f>
+        <v/>
+      </c>
       <c r="N17" s="12" t="n"/>
       <c r="O17" s="12" t="n"/>
       <c r="P17" s="12" t="n"/>
       <c r="Q17" s="12" t="n"/>
       <c r="R17" s="12" t="n"/>
-      <c r="S17" s="11" t="n"/>
+      <c r="S17" s="12" t="n"/>
+      <c r="T17" s="11" t="n"/>
     </row>
     <row r="18" ht="19.5" customHeight="1">
       <c r="A18" s="10" t="n">
@@ -1460,18 +1510,22 @@
         <f>IF(I18="","",IF(I18&gt;=TODAY(),"✔ Vigente","✘ Vencido"))</f>
         <v/>
       </c>
-      <c r="K18" s="13" t="n"/>
-      <c r="L18" s="14">
-        <f>IF(AND(G18="✔ Vigente",H18&lt;&gt;"",ISNUMBER(H18),H18&gt;=DATE(YEAR(TODAY()),MONTH(TODAY())-1,1),J18="✔ Vigente",UPPER(K18)="APTO"),"✔ ACCESO PERMITIDO","✘ SIN ACCESO")</f>
-        <v/>
-      </c>
-      <c r="M18" s="12" t="n"/>
+      <c r="K18" s="13">
+        <f>IF(J18="✘ Vencido","NO APTO",IF(L18="","",UPPER(L18)))</f>
+        <v/>
+      </c>
+      <c r="L18" s="13" t="n"/>
+      <c r="M18" s="14">
+        <f>IF(AND(G18="✔ Vigente",H18&lt;&gt;"",ISNUMBER(H18),H18&gt;=DATE(YEAR(TODAY()),MONTH(TODAY())-1,1),J18="✔ Vigente",K18="APTO"),"✔ ACCESO PERMITIDO","✘ SIN ACCESO")</f>
+        <v/>
+      </c>
       <c r="N18" s="12" t="n"/>
       <c r="O18" s="12" t="n"/>
       <c r="P18" s="12" t="n"/>
       <c r="Q18" s="12" t="n"/>
       <c r="R18" s="12" t="n"/>
-      <c r="S18" s="11" t="n"/>
+      <c r="S18" s="12" t="n"/>
+      <c r="T18" s="11" t="n"/>
     </row>
     <row r="19" ht="19.5" customHeight="1">
       <c r="A19" s="15" t="n">
@@ -1492,18 +1546,22 @@
         <f>IF(I19="","",IF(I19&gt;=TODAY(),"✔ Vigente","✘ Vencido"))</f>
         <v/>
       </c>
-      <c r="K19" s="13" t="n"/>
-      <c r="L19" s="16">
-        <f>IF(AND(G19="✔ Vigente",H19&lt;&gt;"",ISNUMBER(H19),H19&gt;=DATE(YEAR(TODAY()),MONTH(TODAY())-1,1),J19="✔ Vigente",UPPER(K19)="APTO"),"✔ ACCESO PERMITIDO","✘ SIN ACCESO")</f>
-        <v/>
-      </c>
-      <c r="M19" s="12" t="n"/>
+      <c r="K19" s="13">
+        <f>IF(J19="✘ Vencido","NO APTO",IF(L19="","",UPPER(L19)))</f>
+        <v/>
+      </c>
+      <c r="L19" s="13" t="n"/>
+      <c r="M19" s="16">
+        <f>IF(AND(G19="✔ Vigente",H19&lt;&gt;"",ISNUMBER(H19),H19&gt;=DATE(YEAR(TODAY()),MONTH(TODAY())-1,1),J19="✔ Vigente",K19="APTO"),"✔ ACCESO PERMITIDO","✘ SIN ACCESO")</f>
+        <v/>
+      </c>
       <c r="N19" s="12" t="n"/>
       <c r="O19" s="12" t="n"/>
       <c r="P19" s="12" t="n"/>
       <c r="Q19" s="12" t="n"/>
       <c r="R19" s="12" t="n"/>
-      <c r="S19" s="11" t="n"/>
+      <c r="S19" s="12" t="n"/>
+      <c r="T19" s="11" t="n"/>
     </row>
     <row r="20" ht="19.5" customHeight="1">
       <c r="A20" s="10" t="n">
@@ -1524,18 +1582,22 @@
         <f>IF(I20="","",IF(I20&gt;=TODAY(),"✔ Vigente","✘ Vencido"))</f>
         <v/>
       </c>
-      <c r="K20" s="13" t="n"/>
-      <c r="L20" s="14">
-        <f>IF(AND(G20="✔ Vigente",H20&lt;&gt;"",ISNUMBER(H20),H20&gt;=DATE(YEAR(TODAY()),MONTH(TODAY())-1,1),J20="✔ Vigente",UPPER(K20)="APTO"),"✔ ACCESO PERMITIDO","✘ SIN ACCESO")</f>
-        <v/>
-      </c>
-      <c r="M20" s="12" t="n"/>
+      <c r="K20" s="13">
+        <f>IF(J20="✘ Vencido","NO APTO",IF(L20="","",UPPER(L20)))</f>
+        <v/>
+      </c>
+      <c r="L20" s="13" t="n"/>
+      <c r="M20" s="14">
+        <f>IF(AND(G20="✔ Vigente",H20&lt;&gt;"",ISNUMBER(H20),H20&gt;=DATE(YEAR(TODAY()),MONTH(TODAY())-1,1),J20="✔ Vigente",K20="APTO"),"✔ ACCESO PERMITIDO","✘ SIN ACCESO")</f>
+        <v/>
+      </c>
       <c r="N20" s="12" t="n"/>
       <c r="O20" s="12" t="n"/>
       <c r="P20" s="12" t="n"/>
       <c r="Q20" s="12" t="n"/>
       <c r="R20" s="12" t="n"/>
-      <c r="S20" s="11" t="n"/>
+      <c r="S20" s="12" t="n"/>
+      <c r="T20" s="11" t="n"/>
     </row>
     <row r="21" ht="19.5" customHeight="1">
       <c r="A21" s="15" t="n">
@@ -1556,18 +1618,22 @@
         <f>IF(I21="","",IF(I21&gt;=TODAY(),"✔ Vigente","✘ Vencido"))</f>
         <v/>
       </c>
-      <c r="K21" s="13" t="n"/>
-      <c r="L21" s="16">
-        <f>IF(AND(G21="✔ Vigente",H21&lt;&gt;"",ISNUMBER(H21),H21&gt;=DATE(YEAR(TODAY()),MONTH(TODAY())-1,1),J21="✔ Vigente",UPPER(K21)="APTO"),"✔ ACCESO PERMITIDO","✘ SIN ACCESO")</f>
-        <v/>
-      </c>
-      <c r="M21" s="12" t="n"/>
+      <c r="K21" s="13">
+        <f>IF(J21="✘ Vencido","NO APTO",IF(L21="","",UPPER(L21)))</f>
+        <v/>
+      </c>
+      <c r="L21" s="13" t="n"/>
+      <c r="M21" s="16">
+        <f>IF(AND(G21="✔ Vigente",H21&lt;&gt;"",ISNUMBER(H21),H21&gt;=DATE(YEAR(TODAY()),MONTH(TODAY())-1,1),J21="✔ Vigente",K21="APTO"),"✔ ACCESO PERMITIDO","✘ SIN ACCESO")</f>
+        <v/>
+      </c>
       <c r="N21" s="12" t="n"/>
       <c r="O21" s="12" t="n"/>
       <c r="P21" s="12" t="n"/>
       <c r="Q21" s="12" t="n"/>
       <c r="R21" s="12" t="n"/>
-      <c r="S21" s="11" t="n"/>
+      <c r="S21" s="12" t="n"/>
+      <c r="T21" s="11" t="n"/>
     </row>
     <row r="22" ht="19.5" customHeight="1">
       <c r="A22" s="10" t="n">
@@ -1588,18 +1654,22 @@
         <f>IF(I22="","",IF(I22&gt;=TODAY(),"✔ Vigente","✘ Vencido"))</f>
         <v/>
       </c>
-      <c r="K22" s="13" t="n"/>
-      <c r="L22" s="14">
-        <f>IF(AND(G22="✔ Vigente",H22&lt;&gt;"",ISNUMBER(H22),H22&gt;=DATE(YEAR(TODAY()),MONTH(TODAY())-1,1),J22="✔ Vigente",UPPER(K22)="APTO"),"✔ ACCESO PERMITIDO","✘ SIN ACCESO")</f>
-        <v/>
-      </c>
-      <c r="M22" s="12" t="n"/>
+      <c r="K22" s="13">
+        <f>IF(J22="✘ Vencido","NO APTO",IF(L22="","",UPPER(L22)))</f>
+        <v/>
+      </c>
+      <c r="L22" s="13" t="n"/>
+      <c r="M22" s="14">
+        <f>IF(AND(G22="✔ Vigente",H22&lt;&gt;"",ISNUMBER(H22),H22&gt;=DATE(YEAR(TODAY()),MONTH(TODAY())-1,1),J22="✔ Vigente",K22="APTO"),"✔ ACCESO PERMITIDO","✘ SIN ACCESO")</f>
+        <v/>
+      </c>
       <c r="N22" s="12" t="n"/>
       <c r="O22" s="12" t="n"/>
       <c r="P22" s="12" t="n"/>
       <c r="Q22" s="12" t="n"/>
       <c r="R22" s="12" t="n"/>
-      <c r="S22" s="11" t="n"/>
+      <c r="S22" s="12" t="n"/>
+      <c r="T22" s="11" t="n"/>
     </row>
     <row r="23" ht="19.5" customHeight="1">
       <c r="A23" s="15" t="n">
@@ -1620,18 +1690,22 @@
         <f>IF(I23="","",IF(I23&gt;=TODAY(),"✔ Vigente","✘ Vencido"))</f>
         <v/>
       </c>
-      <c r="K23" s="13" t="n"/>
-      <c r="L23" s="16">
-        <f>IF(AND(G23="✔ Vigente",H23&lt;&gt;"",ISNUMBER(H23),H23&gt;=DATE(YEAR(TODAY()),MONTH(TODAY())-1,1),J23="✔ Vigente",UPPER(K23)="APTO"),"✔ ACCESO PERMITIDO","✘ SIN ACCESO")</f>
-        <v/>
-      </c>
-      <c r="M23" s="12" t="n"/>
+      <c r="K23" s="13">
+        <f>IF(J23="✘ Vencido","NO APTO",IF(L23="","",UPPER(L23)))</f>
+        <v/>
+      </c>
+      <c r="L23" s="13" t="n"/>
+      <c r="M23" s="16">
+        <f>IF(AND(G23="✔ Vigente",H23&lt;&gt;"",ISNUMBER(H23),H23&gt;=DATE(YEAR(TODAY()),MONTH(TODAY())-1,1),J23="✔ Vigente",K23="APTO"),"✔ ACCESO PERMITIDO","✘ SIN ACCESO")</f>
+        <v/>
+      </c>
       <c r="N23" s="12" t="n"/>
       <c r="O23" s="12" t="n"/>
       <c r="P23" s="12" t="n"/>
       <c r="Q23" s="12" t="n"/>
       <c r="R23" s="12" t="n"/>
-      <c r="S23" s="11" t="n"/>
+      <c r="S23" s="12" t="n"/>
+      <c r="T23" s="11" t="n"/>
     </row>
     <row r="24" ht="19.5" customHeight="1">
       <c r="A24" s="10" t="n">
@@ -1652,18 +1726,22 @@
         <f>IF(I24="","",IF(I24&gt;=TODAY(),"✔ Vigente","✘ Vencido"))</f>
         <v/>
       </c>
-      <c r="K24" s="13" t="n"/>
-      <c r="L24" s="14">
-        <f>IF(AND(G24="✔ Vigente",H24&lt;&gt;"",ISNUMBER(H24),H24&gt;=DATE(YEAR(TODAY()),MONTH(TODAY())-1,1),J24="✔ Vigente",UPPER(K24)="APTO"),"✔ ACCESO PERMITIDO","✘ SIN ACCESO")</f>
-        <v/>
-      </c>
-      <c r="M24" s="12" t="n"/>
+      <c r="K24" s="13">
+        <f>IF(J24="✘ Vencido","NO APTO",IF(L24="","",UPPER(L24)))</f>
+        <v/>
+      </c>
+      <c r="L24" s="13" t="n"/>
+      <c r="M24" s="14">
+        <f>IF(AND(G24="✔ Vigente",H24&lt;&gt;"",ISNUMBER(H24),H24&gt;=DATE(YEAR(TODAY()),MONTH(TODAY())-1,1),J24="✔ Vigente",K24="APTO"),"✔ ACCESO PERMITIDO","✘ SIN ACCESO")</f>
+        <v/>
+      </c>
       <c r="N24" s="12" t="n"/>
       <c r="O24" s="12" t="n"/>
       <c r="P24" s="12" t="n"/>
       <c r="Q24" s="12" t="n"/>
       <c r="R24" s="12" t="n"/>
-      <c r="S24" s="11" t="n"/>
+      <c r="S24" s="12" t="n"/>
+      <c r="T24" s="11" t="n"/>
     </row>
     <row r="25" ht="19.5" customHeight="1">
       <c r="A25" s="15" t="n">
@@ -1684,18 +1762,22 @@
         <f>IF(I25="","",IF(I25&gt;=TODAY(),"✔ Vigente","✘ Vencido"))</f>
         <v/>
       </c>
-      <c r="K25" s="13" t="n"/>
-      <c r="L25" s="16">
-        <f>IF(AND(G25="✔ Vigente",H25&lt;&gt;"",ISNUMBER(H25),H25&gt;=DATE(YEAR(TODAY()),MONTH(TODAY())-1,1),J25="✔ Vigente",UPPER(K25)="APTO"),"✔ ACCESO PERMITIDO","✘ SIN ACCESO")</f>
-        <v/>
-      </c>
-      <c r="M25" s="12" t="n"/>
+      <c r="K25" s="13">
+        <f>IF(J25="✘ Vencido","NO APTO",IF(L25="","",UPPER(L25)))</f>
+        <v/>
+      </c>
+      <c r="L25" s="13" t="n"/>
+      <c r="M25" s="16">
+        <f>IF(AND(G25="✔ Vigente",H25&lt;&gt;"",ISNUMBER(H25),H25&gt;=DATE(YEAR(TODAY()),MONTH(TODAY())-1,1),J25="✔ Vigente",K25="APTO"),"✔ ACCESO PERMITIDO","✘ SIN ACCESO")</f>
+        <v/>
+      </c>
       <c r="N25" s="12" t="n"/>
       <c r="O25" s="12" t="n"/>
       <c r="P25" s="12" t="n"/>
       <c r="Q25" s="12" t="n"/>
       <c r="R25" s="12" t="n"/>
-      <c r="S25" s="11" t="n"/>
+      <c r="S25" s="12" t="n"/>
+      <c r="T25" s="11" t="n"/>
     </row>
     <row r="26" ht="19.5" customHeight="1">
       <c r="A26" s="10" t="n">
@@ -1716,18 +1798,22 @@
         <f>IF(I26="","",IF(I26&gt;=TODAY(),"✔ Vigente","✘ Vencido"))</f>
         <v/>
       </c>
-      <c r="K26" s="13" t="n"/>
-      <c r="L26" s="14">
-        <f>IF(AND(G26="✔ Vigente",H26&lt;&gt;"",ISNUMBER(H26),H26&gt;=DATE(YEAR(TODAY()),MONTH(TODAY())-1,1),J26="✔ Vigente",UPPER(K26)="APTO"),"✔ ACCESO PERMITIDO","✘ SIN ACCESO")</f>
-        <v/>
-      </c>
-      <c r="M26" s="12" t="n"/>
+      <c r="K26" s="13">
+        <f>IF(J26="✘ Vencido","NO APTO",IF(L26="","",UPPER(L26)))</f>
+        <v/>
+      </c>
+      <c r="L26" s="13" t="n"/>
+      <c r="M26" s="14">
+        <f>IF(AND(G26="✔ Vigente",H26&lt;&gt;"",ISNUMBER(H26),H26&gt;=DATE(YEAR(TODAY()),MONTH(TODAY())-1,1),J26="✔ Vigente",K26="APTO"),"✔ ACCESO PERMITIDO","✘ SIN ACCESO")</f>
+        <v/>
+      </c>
       <c r="N26" s="12" t="n"/>
       <c r="O26" s="12" t="n"/>
       <c r="P26" s="12" t="n"/>
       <c r="Q26" s="12" t="n"/>
       <c r="R26" s="12" t="n"/>
-      <c r="S26" s="11" t="n"/>
+      <c r="S26" s="12" t="n"/>
+      <c r="T26" s="11" t="n"/>
     </row>
     <row r="27" ht="19.5" customHeight="1">
       <c r="A27" s="15" t="n">
@@ -1748,18 +1834,22 @@
         <f>IF(I27="","",IF(I27&gt;=TODAY(),"✔ Vigente","✘ Vencido"))</f>
         <v/>
       </c>
-      <c r="K27" s="13" t="n"/>
-      <c r="L27" s="16">
-        <f>IF(AND(G27="✔ Vigente",H27&lt;&gt;"",ISNUMBER(H27),H27&gt;=DATE(YEAR(TODAY()),MONTH(TODAY())-1,1),J27="✔ Vigente",UPPER(K27)="APTO"),"✔ ACCESO PERMITIDO","✘ SIN ACCESO")</f>
-        <v/>
-      </c>
-      <c r="M27" s="12" t="n"/>
+      <c r="K27" s="13">
+        <f>IF(J27="✘ Vencido","NO APTO",IF(L27="","",UPPER(L27)))</f>
+        <v/>
+      </c>
+      <c r="L27" s="13" t="n"/>
+      <c r="M27" s="16">
+        <f>IF(AND(G27="✔ Vigente",H27&lt;&gt;"",ISNUMBER(H27),H27&gt;=DATE(YEAR(TODAY()),MONTH(TODAY())-1,1),J27="✔ Vigente",K27="APTO"),"✔ ACCESO PERMITIDO","✘ SIN ACCESO")</f>
+        <v/>
+      </c>
       <c r="N27" s="12" t="n"/>
       <c r="O27" s="12" t="n"/>
       <c r="P27" s="12" t="n"/>
       <c r="Q27" s="12" t="n"/>
       <c r="R27" s="12" t="n"/>
-      <c r="S27" s="11" t="n"/>
+      <c r="S27" s="12" t="n"/>
+      <c r="T27" s="11" t="n"/>
     </row>
     <row r="28" ht="19.5" customHeight="1">
       <c r="A28" s="10" t="n">
@@ -1780,18 +1870,22 @@
         <f>IF(I28="","",IF(I28&gt;=TODAY(),"✔ Vigente","✘ Vencido"))</f>
         <v/>
       </c>
-      <c r="K28" s="13" t="n"/>
-      <c r="L28" s="14">
-        <f>IF(AND(G28="✔ Vigente",H28&lt;&gt;"",ISNUMBER(H28),H28&gt;=DATE(YEAR(TODAY()),MONTH(TODAY())-1,1),J28="✔ Vigente",UPPER(K28)="APTO"),"✔ ACCESO PERMITIDO","✘ SIN ACCESO")</f>
-        <v/>
-      </c>
-      <c r="M28" s="12" t="n"/>
+      <c r="K28" s="13">
+        <f>IF(J28="✘ Vencido","NO APTO",IF(L28="","",UPPER(L28)))</f>
+        <v/>
+      </c>
+      <c r="L28" s="13" t="n"/>
+      <c r="M28" s="14">
+        <f>IF(AND(G28="✔ Vigente",H28&lt;&gt;"",ISNUMBER(H28),H28&gt;=DATE(YEAR(TODAY()),MONTH(TODAY())-1,1),J28="✔ Vigente",K28="APTO"),"✔ ACCESO PERMITIDO","✘ SIN ACCESO")</f>
+        <v/>
+      </c>
       <c r="N28" s="12" t="n"/>
       <c r="O28" s="12" t="n"/>
       <c r="P28" s="12" t="n"/>
       <c r="Q28" s="12" t="n"/>
       <c r="R28" s="12" t="n"/>
-      <c r="S28" s="11" t="n"/>
+      <c r="S28" s="12" t="n"/>
+      <c r="T28" s="11" t="n"/>
     </row>
     <row r="29" ht="19.5" customHeight="1">
       <c r="A29" s="15" t="n">
@@ -1812,18 +1906,22 @@
         <f>IF(I29="","",IF(I29&gt;=TODAY(),"✔ Vigente","✘ Vencido"))</f>
         <v/>
       </c>
-      <c r="K29" s="13" t="n"/>
-      <c r="L29" s="16">
-        <f>IF(AND(G29="✔ Vigente",H29&lt;&gt;"",ISNUMBER(H29),H29&gt;=DATE(YEAR(TODAY()),MONTH(TODAY())-1,1),J29="✔ Vigente",UPPER(K29)="APTO"),"✔ ACCESO PERMITIDO","✘ SIN ACCESO")</f>
-        <v/>
-      </c>
-      <c r="M29" s="12" t="n"/>
+      <c r="K29" s="13">
+        <f>IF(J29="✘ Vencido","NO APTO",IF(L29="","",UPPER(L29)))</f>
+        <v/>
+      </c>
+      <c r="L29" s="13" t="n"/>
+      <c r="M29" s="16">
+        <f>IF(AND(G29="✔ Vigente",H29&lt;&gt;"",ISNUMBER(H29),H29&gt;=DATE(YEAR(TODAY()),MONTH(TODAY())-1,1),J29="✔ Vigente",K29="APTO"),"✔ ACCESO PERMITIDO","✘ SIN ACCESO")</f>
+        <v/>
+      </c>
       <c r="N29" s="12" t="n"/>
       <c r="O29" s="12" t="n"/>
       <c r="P29" s="12" t="n"/>
       <c r="Q29" s="12" t="n"/>
       <c r="R29" s="12" t="n"/>
-      <c r="S29" s="11" t="n"/>
+      <c r="S29" s="12" t="n"/>
+      <c r="T29" s="11" t="n"/>
     </row>
     <row r="30" ht="19.5" customHeight="1">
       <c r="A30" s="10" t="n">
@@ -1844,18 +1942,22 @@
         <f>IF(I30="","",IF(I30&gt;=TODAY(),"✔ Vigente","✘ Vencido"))</f>
         <v/>
       </c>
-      <c r="K30" s="13" t="n"/>
-      <c r="L30" s="14">
-        <f>IF(AND(G30="✔ Vigente",H30&lt;&gt;"",ISNUMBER(H30),H30&gt;=DATE(YEAR(TODAY()),MONTH(TODAY())-1,1),J30="✔ Vigente",UPPER(K30)="APTO"),"✔ ACCESO PERMITIDO","✘ SIN ACCESO")</f>
-        <v/>
-      </c>
-      <c r="M30" s="12" t="n"/>
+      <c r="K30" s="13">
+        <f>IF(J30="✘ Vencido","NO APTO",IF(L30="","",UPPER(L30)))</f>
+        <v/>
+      </c>
+      <c r="L30" s="13" t="n"/>
+      <c r="M30" s="14">
+        <f>IF(AND(G30="✔ Vigente",H30&lt;&gt;"",ISNUMBER(H30),H30&gt;=DATE(YEAR(TODAY()),MONTH(TODAY())-1,1),J30="✔ Vigente",K30="APTO"),"✔ ACCESO PERMITIDO","✘ SIN ACCESO")</f>
+        <v/>
+      </c>
       <c r="N30" s="12" t="n"/>
       <c r="O30" s="12" t="n"/>
       <c r="P30" s="12" t="n"/>
       <c r="Q30" s="12" t="n"/>
       <c r="R30" s="12" t="n"/>
-      <c r="S30" s="11" t="n"/>
+      <c r="S30" s="12" t="n"/>
+      <c r="T30" s="11" t="n"/>
     </row>
     <row r="31" ht="19.5" customHeight="1">
       <c r="A31" s="15" t="n">
@@ -1876,18 +1978,22 @@
         <f>IF(I31="","",IF(I31&gt;=TODAY(),"✔ Vigente","✘ Vencido"))</f>
         <v/>
       </c>
-      <c r="K31" s="13" t="n"/>
-      <c r="L31" s="16">
-        <f>IF(AND(G31="✔ Vigente",H31&lt;&gt;"",ISNUMBER(H31),H31&gt;=DATE(YEAR(TODAY()),MONTH(TODAY())-1,1),J31="✔ Vigente",UPPER(K31)="APTO"),"✔ ACCESO PERMITIDO","✘ SIN ACCESO")</f>
-        <v/>
-      </c>
-      <c r="M31" s="12" t="n"/>
+      <c r="K31" s="13">
+        <f>IF(J31="✘ Vencido","NO APTO",IF(L31="","",UPPER(L31)))</f>
+        <v/>
+      </c>
+      <c r="L31" s="13" t="n"/>
+      <c r="M31" s="16">
+        <f>IF(AND(G31="✔ Vigente",H31&lt;&gt;"",ISNUMBER(H31),H31&gt;=DATE(YEAR(TODAY()),MONTH(TODAY())-1,1),J31="✔ Vigente",K31="APTO"),"✔ ACCESO PERMITIDO","✘ SIN ACCESO")</f>
+        <v/>
+      </c>
       <c r="N31" s="12" t="n"/>
       <c r="O31" s="12" t="n"/>
       <c r="P31" s="12" t="n"/>
       <c r="Q31" s="12" t="n"/>
       <c r="R31" s="12" t="n"/>
-      <c r="S31" s="11" t="n"/>
+      <c r="S31" s="12" t="n"/>
+      <c r="T31" s="11" t="n"/>
     </row>
     <row r="32" ht="19.5" customHeight="1">
       <c r="A32" s="10" t="n">
@@ -1908,18 +2014,22 @@
         <f>IF(I32="","",IF(I32&gt;=TODAY(),"✔ Vigente","✘ Vencido"))</f>
         <v/>
       </c>
-      <c r="K32" s="13" t="n"/>
-      <c r="L32" s="14">
-        <f>IF(AND(G32="✔ Vigente",H32&lt;&gt;"",ISNUMBER(H32),H32&gt;=DATE(YEAR(TODAY()),MONTH(TODAY())-1,1),J32="✔ Vigente",UPPER(K32)="APTO"),"✔ ACCESO PERMITIDO","✘ SIN ACCESO")</f>
-        <v/>
-      </c>
-      <c r="M32" s="12" t="n"/>
+      <c r="K32" s="13">
+        <f>IF(J32="✘ Vencido","NO APTO",IF(L32="","",UPPER(L32)))</f>
+        <v/>
+      </c>
+      <c r="L32" s="13" t="n"/>
+      <c r="M32" s="14">
+        <f>IF(AND(G32="✔ Vigente",H32&lt;&gt;"",ISNUMBER(H32),H32&gt;=DATE(YEAR(TODAY()),MONTH(TODAY())-1,1),J32="✔ Vigente",K32="APTO"),"✔ ACCESO PERMITIDO","✘ SIN ACCESO")</f>
+        <v/>
+      </c>
       <c r="N32" s="12" t="n"/>
       <c r="O32" s="12" t="n"/>
       <c r="P32" s="12" t="n"/>
       <c r="Q32" s="12" t="n"/>
       <c r="R32" s="12" t="n"/>
-      <c r="S32" s="11" t="n"/>
+      <c r="S32" s="12" t="n"/>
+      <c r="T32" s="11" t="n"/>
     </row>
     <row r="33" ht="19.5" customHeight="1">
       <c r="A33" s="15" t="n">
@@ -1940,18 +2050,22 @@
         <f>IF(I33="","",IF(I33&gt;=TODAY(),"✔ Vigente","✘ Vencido"))</f>
         <v/>
       </c>
-      <c r="K33" s="13" t="n"/>
-      <c r="L33" s="16">
-        <f>IF(AND(G33="✔ Vigente",H33&lt;&gt;"",ISNUMBER(H33),H33&gt;=DATE(YEAR(TODAY()),MONTH(TODAY())-1,1),J33="✔ Vigente",UPPER(K33)="APTO"),"✔ ACCESO PERMITIDO","✘ SIN ACCESO")</f>
-        <v/>
-      </c>
-      <c r="M33" s="12" t="n"/>
+      <c r="K33" s="13">
+        <f>IF(J33="✘ Vencido","NO APTO",IF(L33="","",UPPER(L33)))</f>
+        <v/>
+      </c>
+      <c r="L33" s="13" t="n"/>
+      <c r="M33" s="16">
+        <f>IF(AND(G33="✔ Vigente",H33&lt;&gt;"",ISNUMBER(H33),H33&gt;=DATE(YEAR(TODAY()),MONTH(TODAY())-1,1),J33="✔ Vigente",K33="APTO"),"✔ ACCESO PERMITIDO","✘ SIN ACCESO")</f>
+        <v/>
+      </c>
       <c r="N33" s="12" t="n"/>
       <c r="O33" s="12" t="n"/>
       <c r="P33" s="12" t="n"/>
       <c r="Q33" s="12" t="n"/>
       <c r="R33" s="12" t="n"/>
-      <c r="S33" s="11" t="n"/>
+      <c r="S33" s="12" t="n"/>
+      <c r="T33" s="11" t="n"/>
     </row>
     <row r="34" ht="19.5" customHeight="1">
       <c r="A34" s="10" t="n">
@@ -1972,18 +2086,22 @@
         <f>IF(I34="","",IF(I34&gt;=TODAY(),"✔ Vigente","✘ Vencido"))</f>
         <v/>
       </c>
-      <c r="K34" s="13" t="n"/>
-      <c r="L34" s="14">
-        <f>IF(AND(G34="✔ Vigente",H34&lt;&gt;"",ISNUMBER(H34),H34&gt;=DATE(YEAR(TODAY()),MONTH(TODAY())-1,1),J34="✔ Vigente",UPPER(K34)="APTO"),"✔ ACCESO PERMITIDO","✘ SIN ACCESO")</f>
-        <v/>
-      </c>
-      <c r="M34" s="12" t="n"/>
+      <c r="K34" s="13">
+        <f>IF(J34="✘ Vencido","NO APTO",IF(L34="","",UPPER(L34)))</f>
+        <v/>
+      </c>
+      <c r="L34" s="13" t="n"/>
+      <c r="M34" s="14">
+        <f>IF(AND(G34="✔ Vigente",H34&lt;&gt;"",ISNUMBER(H34),H34&gt;=DATE(YEAR(TODAY()),MONTH(TODAY())-1,1),J34="✔ Vigente",K34="APTO"),"✔ ACCESO PERMITIDO","✘ SIN ACCESO")</f>
+        <v/>
+      </c>
       <c r="N34" s="12" t="n"/>
       <c r="O34" s="12" t="n"/>
       <c r="P34" s="12" t="n"/>
       <c r="Q34" s="12" t="n"/>
       <c r="R34" s="12" t="n"/>
-      <c r="S34" s="11" t="n"/>
+      <c r="S34" s="12" t="n"/>
+      <c r="T34" s="11" t="n"/>
     </row>
     <row r="35" ht="19.5" customHeight="1">
       <c r="A35" s="15" t="n">
@@ -2004,18 +2122,22 @@
         <f>IF(I35="","",IF(I35&gt;=TODAY(),"✔ Vigente","✘ Vencido"))</f>
         <v/>
       </c>
-      <c r="K35" s="13" t="n"/>
-      <c r="L35" s="16">
-        <f>IF(AND(G35="✔ Vigente",H35&lt;&gt;"",ISNUMBER(H35),H35&gt;=DATE(YEAR(TODAY()),MONTH(TODAY())-1,1),J35="✔ Vigente",UPPER(K35)="APTO"),"✔ ACCESO PERMITIDO","✘ SIN ACCESO")</f>
-        <v/>
-      </c>
-      <c r="M35" s="12" t="n"/>
+      <c r="K35" s="13">
+        <f>IF(J35="✘ Vencido","NO APTO",IF(L35="","",UPPER(L35)))</f>
+        <v/>
+      </c>
+      <c r="L35" s="13" t="n"/>
+      <c r="M35" s="16">
+        <f>IF(AND(G35="✔ Vigente",H35&lt;&gt;"",ISNUMBER(H35),H35&gt;=DATE(YEAR(TODAY()),MONTH(TODAY())-1,1),J35="✔ Vigente",K35="APTO"),"✔ ACCESO PERMITIDO","✘ SIN ACCESO")</f>
+        <v/>
+      </c>
       <c r="N35" s="12" t="n"/>
       <c r="O35" s="12" t="n"/>
       <c r="P35" s="12" t="n"/>
       <c r="Q35" s="12" t="n"/>
       <c r="R35" s="12" t="n"/>
-      <c r="S35" s="11" t="n"/>
+      <c r="S35" s="12" t="n"/>
+      <c r="T35" s="11" t="n"/>
     </row>
     <row r="36" ht="19.5" customHeight="1">
       <c r="A36" s="10" t="n">
@@ -2036,18 +2158,22 @@
         <f>IF(I36="","",IF(I36&gt;=TODAY(),"✔ Vigente","✘ Vencido"))</f>
         <v/>
       </c>
-      <c r="K36" s="13" t="n"/>
-      <c r="L36" s="14">
-        <f>IF(AND(G36="✔ Vigente",H36&lt;&gt;"",ISNUMBER(H36),H36&gt;=DATE(YEAR(TODAY()),MONTH(TODAY())-1,1),J36="✔ Vigente",UPPER(K36)="APTO"),"✔ ACCESO PERMITIDO","✘ SIN ACCESO")</f>
-        <v/>
-      </c>
-      <c r="M36" s="12" t="n"/>
+      <c r="K36" s="13">
+        <f>IF(J36="✘ Vencido","NO APTO",IF(L36="","",UPPER(L36)))</f>
+        <v/>
+      </c>
+      <c r="L36" s="13" t="n"/>
+      <c r="M36" s="14">
+        <f>IF(AND(G36="✔ Vigente",H36&lt;&gt;"",ISNUMBER(H36),H36&gt;=DATE(YEAR(TODAY()),MONTH(TODAY())-1,1),J36="✔ Vigente",K36="APTO"),"✔ ACCESO PERMITIDO","✘ SIN ACCESO")</f>
+        <v/>
+      </c>
       <c r="N36" s="12" t="n"/>
       <c r="O36" s="12" t="n"/>
       <c r="P36" s="12" t="n"/>
       <c r="Q36" s="12" t="n"/>
       <c r="R36" s="12" t="n"/>
-      <c r="S36" s="11" t="n"/>
+      <c r="S36" s="12" t="n"/>
+      <c r="T36" s="11" t="n"/>
     </row>
     <row r="37" ht="19.5" customHeight="1">
       <c r="A37" s="15" t="n">
@@ -2068,18 +2194,22 @@
         <f>IF(I37="","",IF(I37&gt;=TODAY(),"✔ Vigente","✘ Vencido"))</f>
         <v/>
       </c>
-      <c r="K37" s="13" t="n"/>
-      <c r="L37" s="16">
-        <f>IF(AND(G37="✔ Vigente",H37&lt;&gt;"",ISNUMBER(H37),H37&gt;=DATE(YEAR(TODAY()),MONTH(TODAY())-1,1),J37="✔ Vigente",UPPER(K37)="APTO"),"✔ ACCESO PERMITIDO","✘ SIN ACCESO")</f>
-        <v/>
-      </c>
-      <c r="M37" s="12" t="n"/>
+      <c r="K37" s="13">
+        <f>IF(J37="✘ Vencido","NO APTO",IF(L37="","",UPPER(L37)))</f>
+        <v/>
+      </c>
+      <c r="L37" s="13" t="n"/>
+      <c r="M37" s="16">
+        <f>IF(AND(G37="✔ Vigente",H37&lt;&gt;"",ISNUMBER(H37),H37&gt;=DATE(YEAR(TODAY()),MONTH(TODAY())-1,1),J37="✔ Vigente",K37="APTO"),"✔ ACCESO PERMITIDO","✘ SIN ACCESO")</f>
+        <v/>
+      </c>
       <c r="N37" s="12" t="n"/>
       <c r="O37" s="12" t="n"/>
       <c r="P37" s="12" t="n"/>
       <c r="Q37" s="12" t="n"/>
       <c r="R37" s="12" t="n"/>
-      <c r="S37" s="11" t="n"/>
+      <c r="S37" s="12" t="n"/>
+      <c r="T37" s="11" t="n"/>
     </row>
     <row r="38" ht="19.5" customHeight="1">
       <c r="A38" s="10" t="n">
@@ -2100,18 +2230,22 @@
         <f>IF(I38="","",IF(I38&gt;=TODAY(),"✔ Vigente","✘ Vencido"))</f>
         <v/>
       </c>
-      <c r="K38" s="13" t="n"/>
-      <c r="L38" s="14">
-        <f>IF(AND(G38="✔ Vigente",H38&lt;&gt;"",ISNUMBER(H38),H38&gt;=DATE(YEAR(TODAY()),MONTH(TODAY())-1,1),J38="✔ Vigente",UPPER(K38)="APTO"),"✔ ACCESO PERMITIDO","✘ SIN ACCESO")</f>
-        <v/>
-      </c>
-      <c r="M38" s="12" t="n"/>
+      <c r="K38" s="13">
+        <f>IF(J38="✘ Vencido","NO APTO",IF(L38="","",UPPER(L38)))</f>
+        <v/>
+      </c>
+      <c r="L38" s="13" t="n"/>
+      <c r="M38" s="14">
+        <f>IF(AND(G38="✔ Vigente",H38&lt;&gt;"",ISNUMBER(H38),H38&gt;=DATE(YEAR(TODAY()),MONTH(TODAY())-1,1),J38="✔ Vigente",K38="APTO"),"✔ ACCESO PERMITIDO","✘ SIN ACCESO")</f>
+        <v/>
+      </c>
       <c r="N38" s="12" t="n"/>
       <c r="O38" s="12" t="n"/>
       <c r="P38" s="12" t="n"/>
       <c r="Q38" s="12" t="n"/>
       <c r="R38" s="12" t="n"/>
-      <c r="S38" s="11" t="n"/>
+      <c r="S38" s="12" t="n"/>
+      <c r="T38" s="11" t="n"/>
     </row>
     <row r="39" ht="19.5" customHeight="1">
       <c r="A39" s="15" t="n">
@@ -2132,18 +2266,22 @@
         <f>IF(I39="","",IF(I39&gt;=TODAY(),"✔ Vigente","✘ Vencido"))</f>
         <v/>
       </c>
-      <c r="K39" s="13" t="n"/>
-      <c r="L39" s="16">
-        <f>IF(AND(G39="✔ Vigente",H39&lt;&gt;"",ISNUMBER(H39),H39&gt;=DATE(YEAR(TODAY()),MONTH(TODAY())-1,1),J39="✔ Vigente",UPPER(K39)="APTO"),"✔ ACCESO PERMITIDO","✘ SIN ACCESO")</f>
-        <v/>
-      </c>
-      <c r="M39" s="12" t="n"/>
+      <c r="K39" s="13">
+        <f>IF(J39="✘ Vencido","NO APTO",IF(L39="","",UPPER(L39)))</f>
+        <v/>
+      </c>
+      <c r="L39" s="13" t="n"/>
+      <c r="M39" s="16">
+        <f>IF(AND(G39="✔ Vigente",H39&lt;&gt;"",ISNUMBER(H39),H39&gt;=DATE(YEAR(TODAY()),MONTH(TODAY())-1,1),J39="✔ Vigente",K39="APTO"),"✔ ACCESO PERMITIDO","✘ SIN ACCESO")</f>
+        <v/>
+      </c>
       <c r="N39" s="12" t="n"/>
       <c r="O39" s="12" t="n"/>
       <c r="P39" s="12" t="n"/>
       <c r="Q39" s="12" t="n"/>
       <c r="R39" s="12" t="n"/>
-      <c r="S39" s="11" t="n"/>
+      <c r="S39" s="12" t="n"/>
+      <c r="T39" s="11" t="n"/>
     </row>
     <row r="40" ht="19.5" customHeight="1">
       <c r="A40" s="10" t="n">
@@ -2164,18 +2302,22 @@
         <f>IF(I40="","",IF(I40&gt;=TODAY(),"✔ Vigente","✘ Vencido"))</f>
         <v/>
       </c>
-      <c r="K40" s="13" t="n"/>
-      <c r="L40" s="14">
-        <f>IF(AND(G40="✔ Vigente",H40&lt;&gt;"",ISNUMBER(H40),H40&gt;=DATE(YEAR(TODAY()),MONTH(TODAY())-1,1),J40="✔ Vigente",UPPER(K40)="APTO"),"✔ ACCESO PERMITIDO","✘ SIN ACCESO")</f>
-        <v/>
-      </c>
-      <c r="M40" s="12" t="n"/>
+      <c r="K40" s="13">
+        <f>IF(J40="✘ Vencido","NO APTO",IF(L40="","",UPPER(L40)))</f>
+        <v/>
+      </c>
+      <c r="L40" s="13" t="n"/>
+      <c r="M40" s="14">
+        <f>IF(AND(G40="✔ Vigente",H40&lt;&gt;"",ISNUMBER(H40),H40&gt;=DATE(YEAR(TODAY()),MONTH(TODAY())-1,1),J40="✔ Vigente",K40="APTO"),"✔ ACCESO PERMITIDO","✘ SIN ACCESO")</f>
+        <v/>
+      </c>
       <c r="N40" s="12" t="n"/>
       <c r="O40" s="12" t="n"/>
       <c r="P40" s="12" t="n"/>
       <c r="Q40" s="12" t="n"/>
       <c r="R40" s="12" t="n"/>
-      <c r="S40" s="11" t="n"/>
+      <c r="S40" s="12" t="n"/>
+      <c r="T40" s="11" t="n"/>
     </row>
     <row r="41" ht="19.5" customHeight="1">
       <c r="A41" s="15" t="n">
@@ -2196,18 +2338,22 @@
         <f>IF(I41="","",IF(I41&gt;=TODAY(),"✔ Vigente","✘ Vencido"))</f>
         <v/>
       </c>
-      <c r="K41" s="13" t="n"/>
-      <c r="L41" s="16">
-        <f>IF(AND(G41="✔ Vigente",H41&lt;&gt;"",ISNUMBER(H41),H41&gt;=DATE(YEAR(TODAY()),MONTH(TODAY())-1,1),J41="✔ Vigente",UPPER(K41)="APTO"),"✔ ACCESO PERMITIDO","✘ SIN ACCESO")</f>
-        <v/>
-      </c>
-      <c r="M41" s="12" t="n"/>
+      <c r="K41" s="13">
+        <f>IF(J41="✘ Vencido","NO APTO",IF(L41="","",UPPER(L41)))</f>
+        <v/>
+      </c>
+      <c r="L41" s="13" t="n"/>
+      <c r="M41" s="16">
+        <f>IF(AND(G41="✔ Vigente",H41&lt;&gt;"",ISNUMBER(H41),H41&gt;=DATE(YEAR(TODAY()),MONTH(TODAY())-1,1),J41="✔ Vigente",K41="APTO"),"✔ ACCESO PERMITIDO","✘ SIN ACCESO")</f>
+        <v/>
+      </c>
       <c r="N41" s="12" t="n"/>
       <c r="O41" s="12" t="n"/>
       <c r="P41" s="12" t="n"/>
       <c r="Q41" s="12" t="n"/>
       <c r="R41" s="12" t="n"/>
-      <c r="S41" s="11" t="n"/>
+      <c r="S41" s="12" t="n"/>
+      <c r="T41" s="11" t="n"/>
     </row>
     <row r="42" ht="19.5" customHeight="1">
       <c r="A42" s="10" t="n">
@@ -2228,18 +2374,22 @@
         <f>IF(I42="","",IF(I42&gt;=TODAY(),"✔ Vigente","✘ Vencido"))</f>
         <v/>
       </c>
-      <c r="K42" s="13" t="n"/>
-      <c r="L42" s="14">
-        <f>IF(AND(G42="✔ Vigente",H42&lt;&gt;"",ISNUMBER(H42),H42&gt;=DATE(YEAR(TODAY()),MONTH(TODAY())-1,1),J42="✔ Vigente",UPPER(K42)="APTO"),"✔ ACCESO PERMITIDO","✘ SIN ACCESO")</f>
-        <v/>
-      </c>
-      <c r="M42" s="12" t="n"/>
+      <c r="K42" s="13">
+        <f>IF(J42="✘ Vencido","NO APTO",IF(L42="","",UPPER(L42)))</f>
+        <v/>
+      </c>
+      <c r="L42" s="13" t="n"/>
+      <c r="M42" s="14">
+        <f>IF(AND(G42="✔ Vigente",H42&lt;&gt;"",ISNUMBER(H42),H42&gt;=DATE(YEAR(TODAY()),MONTH(TODAY())-1,1),J42="✔ Vigente",K42="APTO"),"✔ ACCESO PERMITIDO","✘ SIN ACCESO")</f>
+        <v/>
+      </c>
       <c r="N42" s="12" t="n"/>
       <c r="O42" s="12" t="n"/>
       <c r="P42" s="12" t="n"/>
       <c r="Q42" s="12" t="n"/>
       <c r="R42" s="12" t="n"/>
-      <c r="S42" s="11" t="n"/>
+      <c r="S42" s="12" t="n"/>
+      <c r="T42" s="11" t="n"/>
     </row>
     <row r="43" ht="19.5" customHeight="1">
       <c r="A43" s="15" t="n">
@@ -2260,18 +2410,22 @@
         <f>IF(I43="","",IF(I43&gt;=TODAY(),"✔ Vigente","✘ Vencido"))</f>
         <v/>
       </c>
-      <c r="K43" s="13" t="n"/>
-      <c r="L43" s="16">
-        <f>IF(AND(G43="✔ Vigente",H43&lt;&gt;"",ISNUMBER(H43),H43&gt;=DATE(YEAR(TODAY()),MONTH(TODAY())-1,1),J43="✔ Vigente",UPPER(K43)="APTO"),"✔ ACCESO PERMITIDO","✘ SIN ACCESO")</f>
-        <v/>
-      </c>
-      <c r="M43" s="12" t="n"/>
+      <c r="K43" s="13">
+        <f>IF(J43="✘ Vencido","NO APTO",IF(L43="","",UPPER(L43)))</f>
+        <v/>
+      </c>
+      <c r="L43" s="13" t="n"/>
+      <c r="M43" s="16">
+        <f>IF(AND(G43="✔ Vigente",H43&lt;&gt;"",ISNUMBER(H43),H43&gt;=DATE(YEAR(TODAY()),MONTH(TODAY())-1,1),J43="✔ Vigente",K43="APTO"),"✔ ACCESO PERMITIDO","✘ SIN ACCESO")</f>
+        <v/>
+      </c>
       <c r="N43" s="12" t="n"/>
       <c r="O43" s="12" t="n"/>
       <c r="P43" s="12" t="n"/>
       <c r="Q43" s="12" t="n"/>
       <c r="R43" s="12" t="n"/>
-      <c r="S43" s="11" t="n"/>
+      <c r="S43" s="12" t="n"/>
+      <c r="T43" s="11" t="n"/>
     </row>
     <row r="44" ht="19.5" customHeight="1">
       <c r="A44" s="10" t="n">
@@ -2292,18 +2446,22 @@
         <f>IF(I44="","",IF(I44&gt;=TODAY(),"✔ Vigente","✘ Vencido"))</f>
         <v/>
       </c>
-      <c r="K44" s="13" t="n"/>
-      <c r="L44" s="14">
-        <f>IF(AND(G44="✔ Vigente",H44&lt;&gt;"",ISNUMBER(H44),H44&gt;=DATE(YEAR(TODAY()),MONTH(TODAY())-1,1),J44="✔ Vigente",UPPER(K44)="APTO"),"✔ ACCESO PERMITIDO","✘ SIN ACCESO")</f>
-        <v/>
-      </c>
-      <c r="M44" s="12" t="n"/>
+      <c r="K44" s="13">
+        <f>IF(J44="✘ Vencido","NO APTO",IF(L44="","",UPPER(L44)))</f>
+        <v/>
+      </c>
+      <c r="L44" s="13" t="n"/>
+      <c r="M44" s="14">
+        <f>IF(AND(G44="✔ Vigente",H44&lt;&gt;"",ISNUMBER(H44),H44&gt;=DATE(YEAR(TODAY()),MONTH(TODAY())-1,1),J44="✔ Vigente",K44="APTO"),"✔ ACCESO PERMITIDO","✘ SIN ACCESO")</f>
+        <v/>
+      </c>
       <c r="N44" s="12" t="n"/>
       <c r="O44" s="12" t="n"/>
       <c r="P44" s="12" t="n"/>
       <c r="Q44" s="12" t="n"/>
       <c r="R44" s="12" t="n"/>
-      <c r="S44" s="11" t="n"/>
+      <c r="S44" s="12" t="n"/>
+      <c r="T44" s="11" t="n"/>
     </row>
     <row r="45" ht="19.5" customHeight="1">
       <c r="A45" s="15" t="n">
@@ -2324,18 +2482,22 @@
         <f>IF(I45="","",IF(I45&gt;=TODAY(),"✔ Vigente","✘ Vencido"))</f>
         <v/>
       </c>
-      <c r="K45" s="13" t="n"/>
-      <c r="L45" s="16">
-        <f>IF(AND(G45="✔ Vigente",H45&lt;&gt;"",ISNUMBER(H45),H45&gt;=DATE(YEAR(TODAY()),MONTH(TODAY())-1,1),J45="✔ Vigente",UPPER(K45)="APTO"),"✔ ACCESO PERMITIDO","✘ SIN ACCESO")</f>
-        <v/>
-      </c>
-      <c r="M45" s="12" t="n"/>
+      <c r="K45" s="13">
+        <f>IF(J45="✘ Vencido","NO APTO",IF(L45="","",UPPER(L45)))</f>
+        <v/>
+      </c>
+      <c r="L45" s="13" t="n"/>
+      <c r="M45" s="16">
+        <f>IF(AND(G45="✔ Vigente",H45&lt;&gt;"",ISNUMBER(H45),H45&gt;=DATE(YEAR(TODAY()),MONTH(TODAY())-1,1),J45="✔ Vigente",K45="APTO"),"✔ ACCESO PERMITIDO","✘ SIN ACCESO")</f>
+        <v/>
+      </c>
       <c r="N45" s="12" t="n"/>
       <c r="O45" s="12" t="n"/>
       <c r="P45" s="12" t="n"/>
       <c r="Q45" s="12" t="n"/>
       <c r="R45" s="12" t="n"/>
-      <c r="S45" s="11" t="n"/>
+      <c r="S45" s="12" t="n"/>
+      <c r="T45" s="11" t="n"/>
     </row>
     <row r="46" ht="19.5" customHeight="1">
       <c r="A46" s="10" t="n">
@@ -2356,18 +2518,22 @@
         <f>IF(I46="","",IF(I46&gt;=TODAY(),"✔ Vigente","✘ Vencido"))</f>
         <v/>
       </c>
-      <c r="K46" s="13" t="n"/>
-      <c r="L46" s="14">
-        <f>IF(AND(G46="✔ Vigente",H46&lt;&gt;"",ISNUMBER(H46),H46&gt;=DATE(YEAR(TODAY()),MONTH(TODAY())-1,1),J46="✔ Vigente",UPPER(K46)="APTO"),"✔ ACCESO PERMITIDO","✘ SIN ACCESO")</f>
-        <v/>
-      </c>
-      <c r="M46" s="12" t="n"/>
+      <c r="K46" s="13">
+        <f>IF(J46="✘ Vencido","NO APTO",IF(L46="","",UPPER(L46)))</f>
+        <v/>
+      </c>
+      <c r="L46" s="13" t="n"/>
+      <c r="M46" s="14">
+        <f>IF(AND(G46="✔ Vigente",H46&lt;&gt;"",ISNUMBER(H46),H46&gt;=DATE(YEAR(TODAY()),MONTH(TODAY())-1,1),J46="✔ Vigente",K46="APTO"),"✔ ACCESO PERMITIDO","✘ SIN ACCESO")</f>
+        <v/>
+      </c>
       <c r="N46" s="12" t="n"/>
       <c r="O46" s="12" t="n"/>
       <c r="P46" s="12" t="n"/>
       <c r="Q46" s="12" t="n"/>
       <c r="R46" s="12" t="n"/>
-      <c r="S46" s="11" t="n"/>
+      <c r="S46" s="12" t="n"/>
+      <c r="T46" s="11" t="n"/>
     </row>
     <row r="47" ht="19.5" customHeight="1">
       <c r="A47" s="15" t="n">
@@ -2388,18 +2554,22 @@
         <f>IF(I47="","",IF(I47&gt;=TODAY(),"✔ Vigente","✘ Vencido"))</f>
         <v/>
       </c>
-      <c r="K47" s="13" t="n"/>
-      <c r="L47" s="16">
-        <f>IF(AND(G47="✔ Vigente",H47&lt;&gt;"",ISNUMBER(H47),H47&gt;=DATE(YEAR(TODAY()),MONTH(TODAY())-1,1),J47="✔ Vigente",UPPER(K47)="APTO"),"✔ ACCESO PERMITIDO","✘ SIN ACCESO")</f>
-        <v/>
-      </c>
-      <c r="M47" s="12" t="n"/>
+      <c r="K47" s="13">
+        <f>IF(J47="✘ Vencido","NO APTO",IF(L47="","",UPPER(L47)))</f>
+        <v/>
+      </c>
+      <c r="L47" s="13" t="n"/>
+      <c r="M47" s="16">
+        <f>IF(AND(G47="✔ Vigente",H47&lt;&gt;"",ISNUMBER(H47),H47&gt;=DATE(YEAR(TODAY()),MONTH(TODAY())-1,1),J47="✔ Vigente",K47="APTO"),"✔ ACCESO PERMITIDO","✘ SIN ACCESO")</f>
+        <v/>
+      </c>
       <c r="N47" s="12" t="n"/>
       <c r="O47" s="12" t="n"/>
       <c r="P47" s="12" t="n"/>
       <c r="Q47" s="12" t="n"/>
       <c r="R47" s="12" t="n"/>
-      <c r="S47" s="11" t="n"/>
+      <c r="S47" s="12" t="n"/>
+      <c r="T47" s="11" t="n"/>
     </row>
     <row r="48" ht="19.5" customHeight="1">
       <c r="A48" s="10" t="n">
@@ -2420,18 +2590,22 @@
         <f>IF(I48="","",IF(I48&gt;=TODAY(),"✔ Vigente","✘ Vencido"))</f>
         <v/>
       </c>
-      <c r="K48" s="13" t="n"/>
-      <c r="L48" s="14">
-        <f>IF(AND(G48="✔ Vigente",H48&lt;&gt;"",ISNUMBER(H48),H48&gt;=DATE(YEAR(TODAY()),MONTH(TODAY())-1,1),J48="✔ Vigente",UPPER(K48)="APTO"),"✔ ACCESO PERMITIDO","✘ SIN ACCESO")</f>
-        <v/>
-      </c>
-      <c r="M48" s="12" t="n"/>
+      <c r="K48" s="13">
+        <f>IF(J48="✘ Vencido","NO APTO",IF(L48="","",UPPER(L48)))</f>
+        <v/>
+      </c>
+      <c r="L48" s="13" t="n"/>
+      <c r="M48" s="14">
+        <f>IF(AND(G48="✔ Vigente",H48&lt;&gt;"",ISNUMBER(H48),H48&gt;=DATE(YEAR(TODAY()),MONTH(TODAY())-1,1),J48="✔ Vigente",K48="APTO"),"✔ ACCESO PERMITIDO","✘ SIN ACCESO")</f>
+        <v/>
+      </c>
       <c r="N48" s="12" t="n"/>
       <c r="O48" s="12" t="n"/>
       <c r="P48" s="12" t="n"/>
       <c r="Q48" s="12" t="n"/>
       <c r="R48" s="12" t="n"/>
-      <c r="S48" s="11" t="n"/>
+      <c r="S48" s="12" t="n"/>
+      <c r="T48" s="11" t="n"/>
     </row>
     <row r="49" ht="19.5" customHeight="1">
       <c r="A49" s="15" t="n">
@@ -2452,18 +2626,22 @@
         <f>IF(I49="","",IF(I49&gt;=TODAY(),"✔ Vigente","✘ Vencido"))</f>
         <v/>
       </c>
-      <c r="K49" s="13" t="n"/>
-      <c r="L49" s="16">
-        <f>IF(AND(G49="✔ Vigente",H49&lt;&gt;"",ISNUMBER(H49),H49&gt;=DATE(YEAR(TODAY()),MONTH(TODAY())-1,1),J49="✔ Vigente",UPPER(K49)="APTO"),"✔ ACCESO PERMITIDO","✘ SIN ACCESO")</f>
-        <v/>
-      </c>
-      <c r="M49" s="12" t="n"/>
+      <c r="K49" s="13">
+        <f>IF(J49="✘ Vencido","NO APTO",IF(L49="","",UPPER(L49)))</f>
+        <v/>
+      </c>
+      <c r="L49" s="13" t="n"/>
+      <c r="M49" s="16">
+        <f>IF(AND(G49="✔ Vigente",H49&lt;&gt;"",ISNUMBER(H49),H49&gt;=DATE(YEAR(TODAY()),MONTH(TODAY())-1,1),J49="✔ Vigente",K49="APTO"),"✔ ACCESO PERMITIDO","✘ SIN ACCESO")</f>
+        <v/>
+      </c>
       <c r="N49" s="12" t="n"/>
       <c r="O49" s="12" t="n"/>
       <c r="P49" s="12" t="n"/>
       <c r="Q49" s="12" t="n"/>
       <c r="R49" s="12" t="n"/>
-      <c r="S49" s="11" t="n"/>
+      <c r="S49" s="12" t="n"/>
+      <c r="T49" s="11" t="n"/>
     </row>
     <row r="50" ht="19.5" customHeight="1">
       <c r="A50" s="10" t="n">
@@ -2484,18 +2662,22 @@
         <f>IF(I50="","",IF(I50&gt;=TODAY(),"✔ Vigente","✘ Vencido"))</f>
         <v/>
       </c>
-      <c r="K50" s="13" t="n"/>
-      <c r="L50" s="14">
-        <f>IF(AND(G50="✔ Vigente",H50&lt;&gt;"",ISNUMBER(H50),H50&gt;=DATE(YEAR(TODAY()),MONTH(TODAY())-1,1),J50="✔ Vigente",UPPER(K50)="APTO"),"✔ ACCESO PERMITIDO","✘ SIN ACCESO")</f>
-        <v/>
-      </c>
-      <c r="M50" s="12" t="n"/>
+      <c r="K50" s="13">
+        <f>IF(J50="✘ Vencido","NO APTO",IF(L50="","",UPPER(L50)))</f>
+        <v/>
+      </c>
+      <c r="L50" s="13" t="n"/>
+      <c r="M50" s="14">
+        <f>IF(AND(G50="✔ Vigente",H50&lt;&gt;"",ISNUMBER(H50),H50&gt;=DATE(YEAR(TODAY()),MONTH(TODAY())-1,1),J50="✔ Vigente",K50="APTO"),"✔ ACCESO PERMITIDO","✘ SIN ACCESO")</f>
+        <v/>
+      </c>
       <c r="N50" s="12" t="n"/>
       <c r="O50" s="12" t="n"/>
       <c r="P50" s="12" t="n"/>
       <c r="Q50" s="12" t="n"/>
       <c r="R50" s="12" t="n"/>
-      <c r="S50" s="11" t="n"/>
+      <c r="S50" s="12" t="n"/>
+      <c r="T50" s="11" t="n"/>
     </row>
     <row r="51" ht="19.5" customHeight="1">
       <c r="A51" s="15" t="n">
@@ -2516,18 +2698,22 @@
         <f>IF(I51="","",IF(I51&gt;=TODAY(),"✔ Vigente","✘ Vencido"))</f>
         <v/>
       </c>
-      <c r="K51" s="13" t="n"/>
-      <c r="L51" s="16">
-        <f>IF(AND(G51="✔ Vigente",H51&lt;&gt;"",ISNUMBER(H51),H51&gt;=DATE(YEAR(TODAY()),MONTH(TODAY())-1,1),J51="✔ Vigente",UPPER(K51)="APTO"),"✔ ACCESO PERMITIDO","✘ SIN ACCESO")</f>
-        <v/>
-      </c>
-      <c r="M51" s="12" t="n"/>
+      <c r="K51" s="13">
+        <f>IF(J51="✘ Vencido","NO APTO",IF(L51="","",UPPER(L51)))</f>
+        <v/>
+      </c>
+      <c r="L51" s="13" t="n"/>
+      <c r="M51" s="16">
+        <f>IF(AND(G51="✔ Vigente",H51&lt;&gt;"",ISNUMBER(H51),H51&gt;=DATE(YEAR(TODAY()),MONTH(TODAY())-1,1),J51="✔ Vigente",K51="APTO"),"✔ ACCESO PERMITIDO","✘ SIN ACCESO")</f>
+        <v/>
+      </c>
       <c r="N51" s="12" t="n"/>
       <c r="O51" s="12" t="n"/>
       <c r="P51" s="12" t="n"/>
       <c r="Q51" s="12" t="n"/>
       <c r="R51" s="12" t="n"/>
-      <c r="S51" s="11" t="n"/>
+      <c r="S51" s="12" t="n"/>
+      <c r="T51" s="11" t="n"/>
     </row>
     <row r="52" ht="19.5" customHeight="1">
       <c r="A52" s="10" t="n">
@@ -2548,18 +2734,22 @@
         <f>IF(I52="","",IF(I52&gt;=TODAY(),"✔ Vigente","✘ Vencido"))</f>
         <v/>
       </c>
-      <c r="K52" s="13" t="n"/>
-      <c r="L52" s="14">
-        <f>IF(AND(G52="✔ Vigente",H52&lt;&gt;"",ISNUMBER(H52),H52&gt;=DATE(YEAR(TODAY()),MONTH(TODAY())-1,1),J52="✔ Vigente",UPPER(K52)="APTO"),"✔ ACCESO PERMITIDO","✘ SIN ACCESO")</f>
-        <v/>
-      </c>
-      <c r="M52" s="12" t="n"/>
+      <c r="K52" s="13">
+        <f>IF(J52="✘ Vencido","NO APTO",IF(L52="","",UPPER(L52)))</f>
+        <v/>
+      </c>
+      <c r="L52" s="13" t="n"/>
+      <c r="M52" s="14">
+        <f>IF(AND(G52="✔ Vigente",H52&lt;&gt;"",ISNUMBER(H52),H52&gt;=DATE(YEAR(TODAY()),MONTH(TODAY())-1,1),J52="✔ Vigente",K52="APTO"),"✔ ACCESO PERMITIDO","✘ SIN ACCESO")</f>
+        <v/>
+      </c>
       <c r="N52" s="12" t="n"/>
       <c r="O52" s="12" t="n"/>
       <c r="P52" s="12" t="n"/>
       <c r="Q52" s="12" t="n"/>
       <c r="R52" s="12" t="n"/>
-      <c r="S52" s="11" t="n"/>
+      <c r="S52" s="12" t="n"/>
+      <c r="T52" s="11" t="n"/>
     </row>
     <row r="53" ht="19.5" customHeight="1">
       <c r="A53" s="15" t="n">
@@ -2580,18 +2770,22 @@
         <f>IF(I53="","",IF(I53&gt;=TODAY(),"✔ Vigente","✘ Vencido"))</f>
         <v/>
       </c>
-      <c r="K53" s="13" t="n"/>
-      <c r="L53" s="16">
-        <f>IF(AND(G53="✔ Vigente",H53&lt;&gt;"",ISNUMBER(H53),H53&gt;=DATE(YEAR(TODAY()),MONTH(TODAY())-1,1),J53="✔ Vigente",UPPER(K53)="APTO"),"✔ ACCESO PERMITIDO","✘ SIN ACCESO")</f>
-        <v/>
-      </c>
-      <c r="M53" s="12" t="n"/>
+      <c r="K53" s="13">
+        <f>IF(J53="✘ Vencido","NO APTO",IF(L53="","",UPPER(L53)))</f>
+        <v/>
+      </c>
+      <c r="L53" s="13" t="n"/>
+      <c r="M53" s="16">
+        <f>IF(AND(G53="✔ Vigente",H53&lt;&gt;"",ISNUMBER(H53),H53&gt;=DATE(YEAR(TODAY()),MONTH(TODAY())-1,1),J53="✔ Vigente",K53="APTO"),"✔ ACCESO PERMITIDO","✘ SIN ACCESO")</f>
+        <v/>
+      </c>
       <c r="N53" s="12" t="n"/>
       <c r="O53" s="12" t="n"/>
       <c r="P53" s="12" t="n"/>
       <c r="Q53" s="12" t="n"/>
       <c r="R53" s="12" t="n"/>
-      <c r="S53" s="11" t="n"/>
+      <c r="S53" s="12" t="n"/>
+      <c r="T53" s="11" t="n"/>
     </row>
     <row r="54" ht="19.5" customHeight="1">
       <c r="A54" s="10" t="n">
@@ -2612,18 +2806,22 @@
         <f>IF(I54="","",IF(I54&gt;=TODAY(),"✔ Vigente","✘ Vencido"))</f>
         <v/>
       </c>
-      <c r="K54" s="13" t="n"/>
-      <c r="L54" s="14">
-        <f>IF(AND(G54="✔ Vigente",H54&lt;&gt;"",ISNUMBER(H54),H54&gt;=DATE(YEAR(TODAY()),MONTH(TODAY())-1,1),J54="✔ Vigente",UPPER(K54)="APTO"),"✔ ACCESO PERMITIDO","✘ SIN ACCESO")</f>
-        <v/>
-      </c>
-      <c r="M54" s="12" t="n"/>
+      <c r="K54" s="13">
+        <f>IF(J54="✘ Vencido","NO APTO",IF(L54="","",UPPER(L54)))</f>
+        <v/>
+      </c>
+      <c r="L54" s="13" t="n"/>
+      <c r="M54" s="14">
+        <f>IF(AND(G54="✔ Vigente",H54&lt;&gt;"",ISNUMBER(H54),H54&gt;=DATE(YEAR(TODAY()),MONTH(TODAY())-1,1),J54="✔ Vigente",K54="APTO"),"✔ ACCESO PERMITIDO","✘ SIN ACCESO")</f>
+        <v/>
+      </c>
       <c r="N54" s="12" t="n"/>
       <c r="O54" s="12" t="n"/>
       <c r="P54" s="12" t="n"/>
       <c r="Q54" s="12" t="n"/>
       <c r="R54" s="12" t="n"/>
-      <c r="S54" s="11" t="n"/>
+      <c r="S54" s="12" t="n"/>
+      <c r="T54" s="11" t="n"/>
     </row>
     <row r="55" ht="19.5" customHeight="1">
       <c r="A55" s="15" t="n">
@@ -2644,18 +2842,22 @@
         <f>IF(I55="","",IF(I55&gt;=TODAY(),"✔ Vigente","✘ Vencido"))</f>
         <v/>
       </c>
-      <c r="K55" s="13" t="n"/>
-      <c r="L55" s="16">
-        <f>IF(AND(G55="✔ Vigente",H55&lt;&gt;"",ISNUMBER(H55),H55&gt;=DATE(YEAR(TODAY()),MONTH(TODAY())-1,1),J55="✔ Vigente",UPPER(K55)="APTO"),"✔ ACCESO PERMITIDO","✘ SIN ACCESO")</f>
-        <v/>
-      </c>
-      <c r="M55" s="12" t="n"/>
+      <c r="K55" s="13">
+        <f>IF(J55="✘ Vencido","NO APTO",IF(L55="","",UPPER(L55)))</f>
+        <v/>
+      </c>
+      <c r="L55" s="13" t="n"/>
+      <c r="M55" s="16">
+        <f>IF(AND(G55="✔ Vigente",H55&lt;&gt;"",ISNUMBER(H55),H55&gt;=DATE(YEAR(TODAY()),MONTH(TODAY())-1,1),J55="✔ Vigente",K55="APTO"),"✔ ACCESO PERMITIDO","✘ SIN ACCESO")</f>
+        <v/>
+      </c>
       <c r="N55" s="12" t="n"/>
       <c r="O55" s="12" t="n"/>
       <c r="P55" s="12" t="n"/>
       <c r="Q55" s="12" t="n"/>
       <c r="R55" s="12" t="n"/>
-      <c r="S55" s="11" t="n"/>
+      <c r="S55" s="12" t="n"/>
+      <c r="T55" s="11" t="n"/>
     </row>
   </sheetData>
   <autoFilter ref="A5:Q5"/>
@@ -2714,33 +2916,30 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K6:K55">
-    <cfRule type="expression" priority="13" dxfId="15">
-      <formula>J6="✘ Vencido"</formula>
+    <cfRule type="expression" priority="13" dxfId="17">
+      <formula>K6="APTO"</formula>
     </cfRule>
-    <cfRule type="expression" priority="14" dxfId="17">
-      <formula>UPPER(K6)="APTO"</formula>
-    </cfRule>
-    <cfRule type="expression" priority="15" dxfId="15">
-      <formula>UPPER(K6)="NO APTO"</formula>
+    <cfRule type="expression" priority="14" dxfId="15">
+      <formula>K6="NO APTO"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L6:L55">
-    <cfRule type="expression" priority="16" dxfId="17">
-      <formula>L6="✔ ACCESO PERMITIDO"</formula>
+  <conditionalFormatting sqref="M6:M55">
+    <cfRule type="expression" priority="15" dxfId="17">
+      <formula>M6="✔ ACCESO PERMITIDO"</formula>
     </cfRule>
-    <cfRule type="expression" priority="17" dxfId="15">
-      <formula>L6="✘ SIN ACCESO"</formula>
+    <cfRule type="expression" priority="16" dxfId="15">
+      <formula>M6="✘ SIN ACCESO"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M6:R55">
-    <cfRule type="expression" priority="18" dxfId="15">
-      <formula>AND(M6&lt;&gt;"",ISNUMBER(M6),M6&lt;TODAY())</formula>
+  <conditionalFormatting sqref="N6:S55">
+    <cfRule type="expression" priority="17" dxfId="15">
+      <formula>AND(N6&lt;&gt;"",ISNUMBER(N6),N6&lt;TODAY())</formula>
     </cfRule>
-    <cfRule type="expression" priority="19" dxfId="16">
-      <formula>AND(M6&lt;&gt;"",ISNUMBER(M6),M6&gt;=TODAY(),M6&lt;=TODAY()+30)</formula>
+    <cfRule type="expression" priority="18" dxfId="16">
+      <formula>AND(N6&lt;&gt;"",ISNUMBER(N6),N6&gt;=TODAY(),N6&lt;=TODAY()+30)</formula>
     </cfRule>
-    <cfRule type="expression" priority="20" dxfId="17">
-      <formula>AND(M6&lt;&gt;"",ISNUMBER(M6),M6&gt;TODAY()+30)</formula>
+    <cfRule type="expression" priority="19" dxfId="17">
+      <formula>AND(N6&lt;&gt;"",ISNUMBER(N6),N6&gt;TODAY()+30)</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">

--- a/Consolidado_contratistas_plantabal.xlsx
+++ b/Consolidado_contratistas_plantabal.xlsx
@@ -861,7 +861,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:T55"/>
+  <dimension ref="A1:S55"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6328125" defaultRowHeight="14.5"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -872,7 +872,7 @@
     <col width="15" customWidth="1" min="8" max="8"/>
     <col width="12" customWidth="1" min="9" max="9"/>
     <col width="11" customWidth="1" min="10" max="10"/>
-    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="11" customWidth="1" min="11" max="11"/>
     <col width="14" customWidth="1" min="12" max="12"/>
     <col width="15" customWidth="1" min="13" max="15"/>
     <col width="14" customWidth="1" min="16" max="16"/>
@@ -901,7 +901,7 @@
           <t>▶  REQUISITOS DE ACCESO A PLANTA</t>
         </is>
       </c>
-      <c r="N3" s="3" t="inlineStr">
+      <c r="M3" s="3" t="inlineStr">
         <is>
           <t>▶  HABILITACIONES POR TIPO DE TRABAJO</t>
         </is>
@@ -975,61 +975,55 @@
           <t>Aptitud de Ingreso</t>
         </is>
       </c>
-      <c r="L5" s="22" t="inlineStr">
-        <is>
-          <t>Aptitud
-(Ingreso manual)</t>
-        </is>
-      </c>
-      <c r="M5" s="8" t="inlineStr">
+      <c r="L5" s="8" t="inlineStr">
         <is>
           <t>¿ACCESO
 A PLANTA?</t>
         </is>
       </c>
-      <c r="N5" s="9" t="inlineStr">
+      <c r="M5" s="9" t="inlineStr">
         <is>
           <t>Cert. Prevención
 Riesgos Eléctricos
 (Caducidad)</t>
         </is>
       </c>
-      <c r="O5" s="9" t="inlineStr">
+      <c r="N5" s="9" t="inlineStr">
         <is>
           <t>Cert. Trabajos
 en Altura
 (Caducidad)</t>
         </is>
       </c>
-      <c r="P5" s="9" t="inlineStr">
+      <c r="O5" s="9" t="inlineStr">
         <is>
           <t>Cert. Espacios
 Confinados
 (Caducidad)</t>
         </is>
       </c>
-      <c r="Q5" s="9" t="inlineStr">
+      <c r="P5" s="9" t="inlineStr">
         <is>
           <t>Cert. Trabajos
 en Caliente
 (Caducidad)</t>
         </is>
       </c>
-      <c r="R5" s="9" t="inlineStr">
+      <c r="Q5" s="9" t="inlineStr">
         <is>
           <t>Cert. Prevención
 de Riesgos
 (Caducidad)</t>
         </is>
       </c>
-      <c r="S5" s="9" t="inlineStr">
+      <c r="R5" s="9" t="inlineStr">
         <is>
           <t>Curso Primeros
 Auxilios
 (Fecha emisión)</t>
         </is>
       </c>
-      <c r="T5" s="9" t="inlineStr">
+      <c r="S5" s="9" t="inlineStr">
         <is>
           <t>Observaciones</t>
         </is>
@@ -1075,25 +1069,24 @@
         <v/>
       </c>
       <c r="K6" s="13">
-        <f>IF(J6="✘ Vencido","NO APTO",IF(L6="","",UPPER(L6)))</f>
-        <v/>
-      </c>
-      <c r="L6" s="13" t="n"/>
-      <c r="M6" s="14">
+        <f>IF(I6="","",IF(I6&gt;=TODAY(),"APTO","NO APTO"))</f>
+        <v/>
+      </c>
+      <c r="L6" s="14">
         <f>IF(AND(G6="✔ Vigente",H6&lt;&gt;"",ISNUMBER(H6),H6&gt;=DATE(YEAR(TODAY()),MONTH(TODAY())-1,1),J6="✔ Vigente",K6="APTO"),"✔ ACCESO PERMITIDO","✘ SIN ACCESO")</f>
         <v/>
       </c>
-      <c r="N6" s="12" t="n">
+      <c r="M6" s="12" t="n">
         <v>47481</v>
       </c>
+      <c r="N6" s="12" t="n"/>
       <c r="O6" s="12" t="n"/>
       <c r="P6" s="12" t="n"/>
-      <c r="Q6" s="12" t="n"/>
-      <c r="R6" s="12" t="n">
+      <c r="Q6" s="12" t="n">
         <v>47392</v>
       </c>
-      <c r="S6" s="12" t="n"/>
-      <c r="T6" s="11" t="n"/>
+      <c r="R6" s="12" t="n"/>
+      <c r="S6" s="11" t="n"/>
     </row>
     <row r="7" ht="19.5" customHeight="1">
       <c r="A7" s="15" t="n">
@@ -1115,21 +1108,20 @@
         <v/>
       </c>
       <c r="K7" s="13">
-        <f>IF(J7="✘ Vencido","NO APTO",IF(L7="","",UPPER(L7)))</f>
-        <v/>
-      </c>
-      <c r="L7" s="13" t="n"/>
-      <c r="M7" s="16">
+        <f>IF(I7="","",IF(I7&gt;=TODAY(),"APTO","NO APTO"))</f>
+        <v/>
+      </c>
+      <c r="L7" s="16">
         <f>IF(AND(G7="✔ Vigente",H7&lt;&gt;"",ISNUMBER(H7),H7&gt;=DATE(YEAR(TODAY()),MONTH(TODAY())-1,1),J7="✔ Vigente",K7="APTO"),"✔ ACCESO PERMITIDO","✘ SIN ACCESO")</f>
         <v/>
       </c>
+      <c r="M7" s="12" t="n"/>
       <c r="N7" s="12" t="n"/>
       <c r="O7" s="12" t="n"/>
       <c r="P7" s="12" t="n"/>
       <c r="Q7" s="12" t="n"/>
       <c r="R7" s="12" t="n"/>
-      <c r="S7" s="12" t="n"/>
-      <c r="T7" s="11" t="n"/>
+      <c r="S7" s="11" t="n"/>
     </row>
     <row r="8" ht="19.5" customHeight="1">
       <c r="A8" s="10" t="n">
@@ -1151,21 +1143,20 @@
         <v/>
       </c>
       <c r="K8" s="13">
-        <f>IF(J8="✘ Vencido","NO APTO",IF(L8="","",UPPER(L8)))</f>
-        <v/>
-      </c>
-      <c r="L8" s="13" t="n"/>
-      <c r="M8" s="14">
+        <f>IF(I8="","",IF(I8&gt;=TODAY(),"APTO","NO APTO"))</f>
+        <v/>
+      </c>
+      <c r="L8" s="14">
         <f>IF(AND(G8="✔ Vigente",H8&lt;&gt;"",ISNUMBER(H8),H8&gt;=DATE(YEAR(TODAY()),MONTH(TODAY())-1,1),J8="✔ Vigente",K8="APTO"),"✔ ACCESO PERMITIDO","✘ SIN ACCESO")</f>
         <v/>
       </c>
+      <c r="M8" s="12" t="n"/>
       <c r="N8" s="12" t="n"/>
       <c r="O8" s="12" t="n"/>
       <c r="P8" s="12" t="n"/>
       <c r="Q8" s="12" t="n"/>
       <c r="R8" s="12" t="n"/>
-      <c r="S8" s="12" t="n"/>
-      <c r="T8" s="11" t="n"/>
+      <c r="S8" s="11" t="n"/>
     </row>
     <row r="9" ht="19.5" customHeight="1">
       <c r="A9" s="15" t="n">
@@ -1187,21 +1178,20 @@
         <v/>
       </c>
       <c r="K9" s="13">
-        <f>IF(J9="✘ Vencido","NO APTO",IF(L9="","",UPPER(L9)))</f>
-        <v/>
-      </c>
-      <c r="L9" s="13" t="n"/>
-      <c r="M9" s="16">
+        <f>IF(I9="","",IF(I9&gt;=TODAY(),"APTO","NO APTO"))</f>
+        <v/>
+      </c>
+      <c r="L9" s="16">
         <f>IF(AND(G9="✔ Vigente",H9&lt;&gt;"",ISNUMBER(H9),H9&gt;=DATE(YEAR(TODAY()),MONTH(TODAY())-1,1),J9="✔ Vigente",K9="APTO"),"✔ ACCESO PERMITIDO","✘ SIN ACCESO")</f>
         <v/>
       </c>
+      <c r="M9" s="12" t="n"/>
       <c r="N9" s="12" t="n"/>
       <c r="O9" s="12" t="n"/>
       <c r="P9" s="12" t="n"/>
       <c r="Q9" s="12" t="n"/>
       <c r="R9" s="12" t="n"/>
-      <c r="S9" s="12" t="n"/>
-      <c r="T9" s="11" t="n"/>
+      <c r="S9" s="11" t="n"/>
     </row>
     <row r="10" ht="19.5" customHeight="1">
       <c r="A10" s="10" t="n">
@@ -1223,21 +1213,20 @@
         <v/>
       </c>
       <c r="K10" s="13">
-        <f>IF(J10="✘ Vencido","NO APTO",IF(L10="","",UPPER(L10)))</f>
-        <v/>
-      </c>
-      <c r="L10" s="13" t="n"/>
-      <c r="M10" s="14">
+        <f>IF(I10="","",IF(I10&gt;=TODAY(),"APTO","NO APTO"))</f>
+        <v/>
+      </c>
+      <c r="L10" s="14">
         <f>IF(AND(G10="✔ Vigente",H10&lt;&gt;"",ISNUMBER(H10),H10&gt;=DATE(YEAR(TODAY()),MONTH(TODAY())-1,1),J10="✔ Vigente",K10="APTO"),"✔ ACCESO PERMITIDO","✘ SIN ACCESO")</f>
         <v/>
       </c>
+      <c r="M10" s="12" t="n"/>
       <c r="N10" s="12" t="n"/>
       <c r="O10" s="12" t="n"/>
       <c r="P10" s="12" t="n"/>
       <c r="Q10" s="12" t="n"/>
       <c r="R10" s="12" t="n"/>
-      <c r="S10" s="12" t="n"/>
-      <c r="T10" s="11" t="n"/>
+      <c r="S10" s="11" t="n"/>
     </row>
     <row r="11" ht="19.5" customHeight="1">
       <c r="A11" s="15" t="n">
@@ -1259,21 +1248,20 @@
         <v/>
       </c>
       <c r="K11" s="13">
-        <f>IF(J11="✘ Vencido","NO APTO",IF(L11="","",UPPER(L11)))</f>
-        <v/>
-      </c>
-      <c r="L11" s="13" t="n"/>
-      <c r="M11" s="16">
+        <f>IF(I11="","",IF(I11&gt;=TODAY(),"APTO","NO APTO"))</f>
+        <v/>
+      </c>
+      <c r="L11" s="16">
         <f>IF(AND(G11="✔ Vigente",H11&lt;&gt;"",ISNUMBER(H11),H11&gt;=DATE(YEAR(TODAY()),MONTH(TODAY())-1,1),J11="✔ Vigente",K11="APTO"),"✔ ACCESO PERMITIDO","✘ SIN ACCESO")</f>
         <v/>
       </c>
+      <c r="M11" s="12" t="n"/>
       <c r="N11" s="12" t="n"/>
       <c r="O11" s="12" t="n"/>
       <c r="P11" s="12" t="n"/>
       <c r="Q11" s="12" t="n"/>
       <c r="R11" s="12" t="n"/>
-      <c r="S11" s="12" t="n"/>
-      <c r="T11" s="11" t="n"/>
+      <c r="S11" s="11" t="n"/>
     </row>
     <row r="12" ht="19.5" customHeight="1">
       <c r="A12" s="10" t="n">
@@ -1295,21 +1283,20 @@
         <v/>
       </c>
       <c r="K12" s="13">
-        <f>IF(J12="✘ Vencido","NO APTO",IF(L12="","",UPPER(L12)))</f>
-        <v/>
-      </c>
-      <c r="L12" s="13" t="n"/>
-      <c r="M12" s="14">
+        <f>IF(I12="","",IF(I12&gt;=TODAY(),"APTO","NO APTO"))</f>
+        <v/>
+      </c>
+      <c r="L12" s="14">
         <f>IF(AND(G12="✔ Vigente",H12&lt;&gt;"",ISNUMBER(H12),H12&gt;=DATE(YEAR(TODAY()),MONTH(TODAY())-1,1),J12="✔ Vigente",K12="APTO"),"✔ ACCESO PERMITIDO","✘ SIN ACCESO")</f>
         <v/>
       </c>
+      <c r="M12" s="12" t="n"/>
       <c r="N12" s="12" t="n"/>
       <c r="O12" s="12" t="n"/>
       <c r="P12" s="12" t="n"/>
       <c r="Q12" s="12" t="n"/>
       <c r="R12" s="12" t="n"/>
-      <c r="S12" s="12" t="n"/>
-      <c r="T12" s="11" t="n"/>
+      <c r="S12" s="11" t="n"/>
     </row>
     <row r="13" ht="19.5" customHeight="1">
       <c r="A13" s="15" t="n">
@@ -1331,21 +1318,20 @@
         <v/>
       </c>
       <c r="K13" s="13">
-        <f>IF(J13="✘ Vencido","NO APTO",IF(L13="","",UPPER(L13)))</f>
-        <v/>
-      </c>
-      <c r="L13" s="13" t="n"/>
-      <c r="M13" s="16">
+        <f>IF(I13="","",IF(I13&gt;=TODAY(),"APTO","NO APTO"))</f>
+        <v/>
+      </c>
+      <c r="L13" s="16">
         <f>IF(AND(G13="✔ Vigente",H13&lt;&gt;"",ISNUMBER(H13),H13&gt;=DATE(YEAR(TODAY()),MONTH(TODAY())-1,1),J13="✔ Vigente",K13="APTO"),"✔ ACCESO PERMITIDO","✘ SIN ACCESO")</f>
         <v/>
       </c>
+      <c r="M13" s="12" t="n"/>
       <c r="N13" s="12" t="n"/>
       <c r="O13" s="12" t="n"/>
       <c r="P13" s="12" t="n"/>
       <c r="Q13" s="12" t="n"/>
       <c r="R13" s="12" t="n"/>
-      <c r="S13" s="12" t="n"/>
-      <c r="T13" s="11" t="n"/>
+      <c r="S13" s="11" t="n"/>
     </row>
     <row r="14" ht="19.5" customHeight="1">
       <c r="A14" s="10" t="n">
@@ -1367,21 +1353,20 @@
         <v/>
       </c>
       <c r="K14" s="13">
-        <f>IF(J14="✘ Vencido","NO APTO",IF(L14="","",UPPER(L14)))</f>
-        <v/>
-      </c>
-      <c r="L14" s="13" t="n"/>
-      <c r="M14" s="14">
+        <f>IF(I14="","",IF(I14&gt;=TODAY(),"APTO","NO APTO"))</f>
+        <v/>
+      </c>
+      <c r="L14" s="14">
         <f>IF(AND(G14="✔ Vigente",H14&lt;&gt;"",ISNUMBER(H14),H14&gt;=DATE(YEAR(TODAY()),MONTH(TODAY())-1,1),J14="✔ Vigente",K14="APTO"),"✔ ACCESO PERMITIDO","✘ SIN ACCESO")</f>
         <v/>
       </c>
+      <c r="M14" s="12" t="n"/>
       <c r="N14" s="12" t="n"/>
       <c r="O14" s="12" t="n"/>
       <c r="P14" s="12" t="n"/>
       <c r="Q14" s="12" t="n"/>
       <c r="R14" s="12" t="n"/>
-      <c r="S14" s="12" t="n"/>
-      <c r="T14" s="11" t="n"/>
+      <c r="S14" s="11" t="n"/>
     </row>
     <row r="15" ht="19.5" customHeight="1">
       <c r="A15" s="15" t="n">
@@ -1403,21 +1388,20 @@
         <v/>
       </c>
       <c r="K15" s="13">
-        <f>IF(J15="✘ Vencido","NO APTO",IF(L15="","",UPPER(L15)))</f>
-        <v/>
-      </c>
-      <c r="L15" s="13" t="n"/>
-      <c r="M15" s="16">
+        <f>IF(I15="","",IF(I15&gt;=TODAY(),"APTO","NO APTO"))</f>
+        <v/>
+      </c>
+      <c r="L15" s="16">
         <f>IF(AND(G15="✔ Vigente",H15&lt;&gt;"",ISNUMBER(H15),H15&gt;=DATE(YEAR(TODAY()),MONTH(TODAY())-1,1),J15="✔ Vigente",K15="APTO"),"✔ ACCESO PERMITIDO","✘ SIN ACCESO")</f>
         <v/>
       </c>
+      <c r="M15" s="12" t="n"/>
       <c r="N15" s="12" t="n"/>
       <c r="O15" s="12" t="n"/>
       <c r="P15" s="12" t="n"/>
       <c r="Q15" s="12" t="n"/>
       <c r="R15" s="12" t="n"/>
-      <c r="S15" s="12" t="n"/>
-      <c r="T15" s="11" t="n"/>
+      <c r="S15" s="11" t="n"/>
     </row>
     <row r="16" ht="19.5" customHeight="1">
       <c r="A16" s="10" t="n">
@@ -1439,21 +1423,20 @@
         <v/>
       </c>
       <c r="K16" s="13">
-        <f>IF(J16="✘ Vencido","NO APTO",IF(L16="","",UPPER(L16)))</f>
-        <v/>
-      </c>
-      <c r="L16" s="13" t="n"/>
-      <c r="M16" s="14">
+        <f>IF(I16="","",IF(I16&gt;=TODAY(),"APTO","NO APTO"))</f>
+        <v/>
+      </c>
+      <c r="L16" s="14">
         <f>IF(AND(G16="✔ Vigente",H16&lt;&gt;"",ISNUMBER(H16),H16&gt;=DATE(YEAR(TODAY()),MONTH(TODAY())-1,1),J16="✔ Vigente",K16="APTO"),"✔ ACCESO PERMITIDO","✘ SIN ACCESO")</f>
         <v/>
       </c>
+      <c r="M16" s="12" t="n"/>
       <c r="N16" s="12" t="n"/>
       <c r="O16" s="12" t="n"/>
       <c r="P16" s="12" t="n"/>
       <c r="Q16" s="12" t="n"/>
       <c r="R16" s="12" t="n"/>
-      <c r="S16" s="12" t="n"/>
-      <c r="T16" s="11" t="n"/>
+      <c r="S16" s="11" t="n"/>
     </row>
     <row r="17" ht="19.5" customHeight="1">
       <c r="A17" s="15" t="n">
@@ -1475,21 +1458,20 @@
         <v/>
       </c>
       <c r="K17" s="13">
-        <f>IF(J17="✘ Vencido","NO APTO",IF(L17="","",UPPER(L17)))</f>
-        <v/>
-      </c>
-      <c r="L17" s="13" t="n"/>
-      <c r="M17" s="16">
+        <f>IF(I17="","",IF(I17&gt;=TODAY(),"APTO","NO APTO"))</f>
+        <v/>
+      </c>
+      <c r="L17" s="16">
         <f>IF(AND(G17="✔ Vigente",H17&lt;&gt;"",ISNUMBER(H17),H17&gt;=DATE(YEAR(TODAY()),MONTH(TODAY())-1,1),J17="✔ Vigente",K17="APTO"),"✔ ACCESO PERMITIDO","✘ SIN ACCESO")</f>
         <v/>
       </c>
+      <c r="M17" s="12" t="n"/>
       <c r="N17" s="12" t="n"/>
       <c r="O17" s="12" t="n"/>
       <c r="P17" s="12" t="n"/>
       <c r="Q17" s="12" t="n"/>
       <c r="R17" s="12" t="n"/>
-      <c r="S17" s="12" t="n"/>
-      <c r="T17" s="11" t="n"/>
+      <c r="S17" s="11" t="n"/>
     </row>
     <row r="18" ht="19.5" customHeight="1">
       <c r="A18" s="10" t="n">
@@ -1511,21 +1493,20 @@
         <v/>
       </c>
       <c r="K18" s="13">
-        <f>IF(J18="✘ Vencido","NO APTO",IF(L18="","",UPPER(L18)))</f>
-        <v/>
-      </c>
-      <c r="L18" s="13" t="n"/>
-      <c r="M18" s="14">
+        <f>IF(I18="","",IF(I18&gt;=TODAY(),"APTO","NO APTO"))</f>
+        <v/>
+      </c>
+      <c r="L18" s="14">
         <f>IF(AND(G18="✔ Vigente",H18&lt;&gt;"",ISNUMBER(H18),H18&gt;=DATE(YEAR(TODAY()),MONTH(TODAY())-1,1),J18="✔ Vigente",K18="APTO"),"✔ ACCESO PERMITIDO","✘ SIN ACCESO")</f>
         <v/>
       </c>
+      <c r="M18" s="12" t="n"/>
       <c r="N18" s="12" t="n"/>
       <c r="O18" s="12" t="n"/>
       <c r="P18" s="12" t="n"/>
       <c r="Q18" s="12" t="n"/>
       <c r="R18" s="12" t="n"/>
-      <c r="S18" s="12" t="n"/>
-      <c r="T18" s="11" t="n"/>
+      <c r="S18" s="11" t="n"/>
     </row>
     <row r="19" ht="19.5" customHeight="1">
       <c r="A19" s="15" t="n">
@@ -1547,21 +1528,20 @@
         <v/>
       </c>
       <c r="K19" s="13">
-        <f>IF(J19="✘ Vencido","NO APTO",IF(L19="","",UPPER(L19)))</f>
-        <v/>
-      </c>
-      <c r="L19" s="13" t="n"/>
-      <c r="M19" s="16">
+        <f>IF(I19="","",IF(I19&gt;=TODAY(),"APTO","NO APTO"))</f>
+        <v/>
+      </c>
+      <c r="L19" s="16">
         <f>IF(AND(G19="✔ Vigente",H19&lt;&gt;"",ISNUMBER(H19),H19&gt;=DATE(YEAR(TODAY()),MONTH(TODAY())-1,1),J19="✔ Vigente",K19="APTO"),"✔ ACCESO PERMITIDO","✘ SIN ACCESO")</f>
         <v/>
       </c>
+      <c r="M19" s="12" t="n"/>
       <c r="N19" s="12" t="n"/>
       <c r="O19" s="12" t="n"/>
       <c r="P19" s="12" t="n"/>
       <c r="Q19" s="12" t="n"/>
       <c r="R19" s="12" t="n"/>
-      <c r="S19" s="12" t="n"/>
-      <c r="T19" s="11" t="n"/>
+      <c r="S19" s="11" t="n"/>
     </row>
     <row r="20" ht="19.5" customHeight="1">
       <c r="A20" s="10" t="n">
@@ -1583,21 +1563,20 @@
         <v/>
       </c>
       <c r="K20" s="13">
-        <f>IF(J20="✘ Vencido","NO APTO",IF(L20="","",UPPER(L20)))</f>
-        <v/>
-      </c>
-      <c r="L20" s="13" t="n"/>
-      <c r="M20" s="14">
+        <f>IF(I20="","",IF(I20&gt;=TODAY(),"APTO","NO APTO"))</f>
+        <v/>
+      </c>
+      <c r="L20" s="14">
         <f>IF(AND(G20="✔ Vigente",H20&lt;&gt;"",ISNUMBER(H20),H20&gt;=DATE(YEAR(TODAY()),MONTH(TODAY())-1,1),J20="✔ Vigente",K20="APTO"),"✔ ACCESO PERMITIDO","✘ SIN ACCESO")</f>
         <v/>
       </c>
+      <c r="M20" s="12" t="n"/>
       <c r="N20" s="12" t="n"/>
       <c r="O20" s="12" t="n"/>
       <c r="P20" s="12" t="n"/>
       <c r="Q20" s="12" t="n"/>
       <c r="R20" s="12" t="n"/>
-      <c r="S20" s="12" t="n"/>
-      <c r="T20" s="11" t="n"/>
+      <c r="S20" s="11" t="n"/>
     </row>
     <row r="21" ht="19.5" customHeight="1">
       <c r="A21" s="15" t="n">
@@ -1619,21 +1598,20 @@
         <v/>
       </c>
       <c r="K21" s="13">
-        <f>IF(J21="✘ Vencido","NO APTO",IF(L21="","",UPPER(L21)))</f>
-        <v/>
-      </c>
-      <c r="L21" s="13" t="n"/>
-      <c r="M21" s="16">
+        <f>IF(I21="","",IF(I21&gt;=TODAY(),"APTO","NO APTO"))</f>
+        <v/>
+      </c>
+      <c r="L21" s="16">
         <f>IF(AND(G21="✔ Vigente",H21&lt;&gt;"",ISNUMBER(H21),H21&gt;=DATE(YEAR(TODAY()),MONTH(TODAY())-1,1),J21="✔ Vigente",K21="APTO"),"✔ ACCESO PERMITIDO","✘ SIN ACCESO")</f>
         <v/>
       </c>
+      <c r="M21" s="12" t="n"/>
       <c r="N21" s="12" t="n"/>
       <c r="O21" s="12" t="n"/>
       <c r="P21" s="12" t="n"/>
       <c r="Q21" s="12" t="n"/>
       <c r="R21" s="12" t="n"/>
-      <c r="S21" s="12" t="n"/>
-      <c r="T21" s="11" t="n"/>
+      <c r="S21" s="11" t="n"/>
     </row>
     <row r="22" ht="19.5" customHeight="1">
       <c r="A22" s="10" t="n">
@@ -1655,21 +1633,20 @@
         <v/>
       </c>
       <c r="K22" s="13">
-        <f>IF(J22="✘ Vencido","NO APTO",IF(L22="","",UPPER(L22)))</f>
-        <v/>
-      </c>
-      <c r="L22" s="13" t="n"/>
-      <c r="M22" s="14">
+        <f>IF(I22="","",IF(I22&gt;=TODAY(),"APTO","NO APTO"))</f>
+        <v/>
+      </c>
+      <c r="L22" s="14">
         <f>IF(AND(G22="✔ Vigente",H22&lt;&gt;"",ISNUMBER(H22),H22&gt;=DATE(YEAR(TODAY()),MONTH(TODAY())-1,1),J22="✔ Vigente",K22="APTO"),"✔ ACCESO PERMITIDO","✘ SIN ACCESO")</f>
         <v/>
       </c>
+      <c r="M22" s="12" t="n"/>
       <c r="N22" s="12" t="n"/>
       <c r="O22" s="12" t="n"/>
       <c r="P22" s="12" t="n"/>
       <c r="Q22" s="12" t="n"/>
       <c r="R22" s="12" t="n"/>
-      <c r="S22" s="12" t="n"/>
-      <c r="T22" s="11" t="n"/>
+      <c r="S22" s="11" t="n"/>
     </row>
     <row r="23" ht="19.5" customHeight="1">
       <c r="A23" s="15" t="n">
@@ -1691,21 +1668,20 @@
         <v/>
       </c>
       <c r="K23" s="13">
-        <f>IF(J23="✘ Vencido","NO APTO",IF(L23="","",UPPER(L23)))</f>
-        <v/>
-      </c>
-      <c r="L23" s="13" t="n"/>
-      <c r="M23" s="16">
+        <f>IF(I23="","",IF(I23&gt;=TODAY(),"APTO","NO APTO"))</f>
+        <v/>
+      </c>
+      <c r="L23" s="16">
         <f>IF(AND(G23="✔ Vigente",H23&lt;&gt;"",ISNUMBER(H23),H23&gt;=DATE(YEAR(TODAY()),MONTH(TODAY())-1,1),J23="✔ Vigente",K23="APTO"),"✔ ACCESO PERMITIDO","✘ SIN ACCESO")</f>
         <v/>
       </c>
+      <c r="M23" s="12" t="n"/>
       <c r="N23" s="12" t="n"/>
       <c r="O23" s="12" t="n"/>
       <c r="P23" s="12" t="n"/>
       <c r="Q23" s="12" t="n"/>
       <c r="R23" s="12" t="n"/>
-      <c r="S23" s="12" t="n"/>
-      <c r="T23" s="11" t="n"/>
+      <c r="S23" s="11" t="n"/>
     </row>
     <row r="24" ht="19.5" customHeight="1">
       <c r="A24" s="10" t="n">
@@ -1727,21 +1703,20 @@
         <v/>
       </c>
       <c r="K24" s="13">
-        <f>IF(J24="✘ Vencido","NO APTO",IF(L24="","",UPPER(L24)))</f>
-        <v/>
-      </c>
-      <c r="L24" s="13" t="n"/>
-      <c r="M24" s="14">
+        <f>IF(I24="","",IF(I24&gt;=TODAY(),"APTO","NO APTO"))</f>
+        <v/>
+      </c>
+      <c r="L24" s="14">
         <f>IF(AND(G24="✔ Vigente",H24&lt;&gt;"",ISNUMBER(H24),H24&gt;=DATE(YEAR(TODAY()),MONTH(TODAY())-1,1),J24="✔ Vigente",K24="APTO"),"✔ ACCESO PERMITIDO","✘ SIN ACCESO")</f>
         <v/>
       </c>
+      <c r="M24" s="12" t="n"/>
       <c r="N24" s="12" t="n"/>
       <c r="O24" s="12" t="n"/>
       <c r="P24" s="12" t="n"/>
       <c r="Q24" s="12" t="n"/>
       <c r="R24" s="12" t="n"/>
-      <c r="S24" s="12" t="n"/>
-      <c r="T24" s="11" t="n"/>
+      <c r="S24" s="11" t="n"/>
     </row>
     <row r="25" ht="19.5" customHeight="1">
       <c r="A25" s="15" t="n">
@@ -1763,21 +1738,20 @@
         <v/>
       </c>
       <c r="K25" s="13">
-        <f>IF(J25="✘ Vencido","NO APTO",IF(L25="","",UPPER(L25)))</f>
-        <v/>
-      </c>
-      <c r="L25" s="13" t="n"/>
-      <c r="M25" s="16">
+        <f>IF(I25="","",IF(I25&gt;=TODAY(),"APTO","NO APTO"))</f>
+        <v/>
+      </c>
+      <c r="L25" s="16">
         <f>IF(AND(G25="✔ Vigente",H25&lt;&gt;"",ISNUMBER(H25),H25&gt;=DATE(YEAR(TODAY()),MONTH(TODAY())-1,1),J25="✔ Vigente",K25="APTO"),"✔ ACCESO PERMITIDO","✘ SIN ACCESO")</f>
         <v/>
       </c>
+      <c r="M25" s="12" t="n"/>
       <c r="N25" s="12" t="n"/>
       <c r="O25" s="12" t="n"/>
       <c r="P25" s="12" t="n"/>
       <c r="Q25" s="12" t="n"/>
       <c r="R25" s="12" t="n"/>
-      <c r="S25" s="12" t="n"/>
-      <c r="T25" s="11" t="n"/>
+      <c r="S25" s="11" t="n"/>
     </row>
     <row r="26" ht="19.5" customHeight="1">
       <c r="A26" s="10" t="n">
@@ -1799,21 +1773,20 @@
         <v/>
       </c>
       <c r="K26" s="13">
-        <f>IF(J26="✘ Vencido","NO APTO",IF(L26="","",UPPER(L26)))</f>
-        <v/>
-      </c>
-      <c r="L26" s="13" t="n"/>
-      <c r="M26" s="14">
+        <f>IF(I26="","",IF(I26&gt;=TODAY(),"APTO","NO APTO"))</f>
+        <v/>
+      </c>
+      <c r="L26" s="14">
         <f>IF(AND(G26="✔ Vigente",H26&lt;&gt;"",ISNUMBER(H26),H26&gt;=DATE(YEAR(TODAY()),MONTH(TODAY())-1,1),J26="✔ Vigente",K26="APTO"),"✔ ACCESO PERMITIDO","✘ SIN ACCESO")</f>
         <v/>
       </c>
+      <c r="M26" s="12" t="n"/>
       <c r="N26" s="12" t="n"/>
       <c r="O26" s="12" t="n"/>
       <c r="P26" s="12" t="n"/>
       <c r="Q26" s="12" t="n"/>
       <c r="R26" s="12" t="n"/>
-      <c r="S26" s="12" t="n"/>
-      <c r="T26" s="11" t="n"/>
+      <c r="S26" s="11" t="n"/>
     </row>
     <row r="27" ht="19.5" customHeight="1">
       <c r="A27" s="15" t="n">
@@ -1835,21 +1808,20 @@
         <v/>
       </c>
       <c r="K27" s="13">
-        <f>IF(J27="✘ Vencido","NO APTO",IF(L27="","",UPPER(L27)))</f>
-        <v/>
-      </c>
-      <c r="L27" s="13" t="n"/>
-      <c r="M27" s="16">
+        <f>IF(I27="","",IF(I27&gt;=TODAY(),"APTO","NO APTO"))</f>
+        <v/>
+      </c>
+      <c r="L27" s="16">
         <f>IF(AND(G27="✔ Vigente",H27&lt;&gt;"",ISNUMBER(H27),H27&gt;=DATE(YEAR(TODAY()),MONTH(TODAY())-1,1),J27="✔ Vigente",K27="APTO"),"✔ ACCESO PERMITIDO","✘ SIN ACCESO")</f>
         <v/>
       </c>
+      <c r="M27" s="12" t="n"/>
       <c r="N27" s="12" t="n"/>
       <c r="O27" s="12" t="n"/>
       <c r="P27" s="12" t="n"/>
       <c r="Q27" s="12" t="n"/>
       <c r="R27" s="12" t="n"/>
-      <c r="S27" s="12" t="n"/>
-      <c r="T27" s="11" t="n"/>
+      <c r="S27" s="11" t="n"/>
     </row>
     <row r="28" ht="19.5" customHeight="1">
       <c r="A28" s="10" t="n">
@@ -1871,21 +1843,20 @@
         <v/>
       </c>
       <c r="K28" s="13">
-        <f>IF(J28="✘ Vencido","NO APTO",IF(L28="","",UPPER(L28)))</f>
-        <v/>
-      </c>
-      <c r="L28" s="13" t="n"/>
-      <c r="M28" s="14">
+        <f>IF(I28="","",IF(I28&gt;=TODAY(),"APTO","NO APTO"))</f>
+        <v/>
+      </c>
+      <c r="L28" s="14">
         <f>IF(AND(G28="✔ Vigente",H28&lt;&gt;"",ISNUMBER(H28),H28&gt;=DATE(YEAR(TODAY()),MONTH(TODAY())-1,1),J28="✔ Vigente",K28="APTO"),"✔ ACCESO PERMITIDO","✘ SIN ACCESO")</f>
         <v/>
       </c>
+      <c r="M28" s="12" t="n"/>
       <c r="N28" s="12" t="n"/>
       <c r="O28" s="12" t="n"/>
       <c r="P28" s="12" t="n"/>
       <c r="Q28" s="12" t="n"/>
       <c r="R28" s="12" t="n"/>
-      <c r="S28" s="12" t="n"/>
-      <c r="T28" s="11" t="n"/>
+      <c r="S28" s="11" t="n"/>
     </row>
     <row r="29" ht="19.5" customHeight="1">
       <c r="A29" s="15" t="n">
@@ -1907,21 +1878,20 @@
         <v/>
       </c>
       <c r="K29" s="13">
-        <f>IF(J29="✘ Vencido","NO APTO",IF(L29="","",UPPER(L29)))</f>
-        <v/>
-      </c>
-      <c r="L29" s="13" t="n"/>
-      <c r="M29" s="16">
+        <f>IF(I29="","",IF(I29&gt;=TODAY(),"APTO","NO APTO"))</f>
+        <v/>
+      </c>
+      <c r="L29" s="16">
         <f>IF(AND(G29="✔ Vigente",H29&lt;&gt;"",ISNUMBER(H29),H29&gt;=DATE(YEAR(TODAY()),MONTH(TODAY())-1,1),J29="✔ Vigente",K29="APTO"),"✔ ACCESO PERMITIDO","✘ SIN ACCESO")</f>
         <v/>
       </c>
+      <c r="M29" s="12" t="n"/>
       <c r="N29" s="12" t="n"/>
       <c r="O29" s="12" t="n"/>
       <c r="P29" s="12" t="n"/>
       <c r="Q29" s="12" t="n"/>
       <c r="R29" s="12" t="n"/>
-      <c r="S29" s="12" t="n"/>
-      <c r="T29" s="11" t="n"/>
+      <c r="S29" s="11" t="n"/>
     </row>
     <row r="30" ht="19.5" customHeight="1">
       <c r="A30" s="10" t="n">
@@ -1943,21 +1913,20 @@
         <v/>
       </c>
       <c r="K30" s="13">
-        <f>IF(J30="✘ Vencido","NO APTO",IF(L30="","",UPPER(L30)))</f>
-        <v/>
-      </c>
-      <c r="L30" s="13" t="n"/>
-      <c r="M30" s="14">
+        <f>IF(I30="","",IF(I30&gt;=TODAY(),"APTO","NO APTO"))</f>
+        <v/>
+      </c>
+      <c r="L30" s="14">
         <f>IF(AND(G30="✔ Vigente",H30&lt;&gt;"",ISNUMBER(H30),H30&gt;=DATE(YEAR(TODAY()),MONTH(TODAY())-1,1),J30="✔ Vigente",K30="APTO"),"✔ ACCESO PERMITIDO","✘ SIN ACCESO")</f>
         <v/>
       </c>
+      <c r="M30" s="12" t="n"/>
       <c r="N30" s="12" t="n"/>
       <c r="O30" s="12" t="n"/>
       <c r="P30" s="12" t="n"/>
       <c r="Q30" s="12" t="n"/>
       <c r="R30" s="12" t="n"/>
-      <c r="S30" s="12" t="n"/>
-      <c r="T30" s="11" t="n"/>
+      <c r="S30" s="11" t="n"/>
     </row>
     <row r="31" ht="19.5" customHeight="1">
       <c r="A31" s="15" t="n">
@@ -1979,21 +1948,20 @@
         <v/>
       </c>
       <c r="K31" s="13">
-        <f>IF(J31="✘ Vencido","NO APTO",IF(L31="","",UPPER(L31)))</f>
-        <v/>
-      </c>
-      <c r="L31" s="13" t="n"/>
-      <c r="M31" s="16">
+        <f>IF(I31="","",IF(I31&gt;=TODAY(),"APTO","NO APTO"))</f>
+        <v/>
+      </c>
+      <c r="L31" s="16">
         <f>IF(AND(G31="✔ Vigente",H31&lt;&gt;"",ISNUMBER(H31),H31&gt;=DATE(YEAR(TODAY()),MONTH(TODAY())-1,1),J31="✔ Vigente",K31="APTO"),"✔ ACCESO PERMITIDO","✘ SIN ACCESO")</f>
         <v/>
       </c>
+      <c r="M31" s="12" t="n"/>
       <c r="N31" s="12" t="n"/>
       <c r="O31" s="12" t="n"/>
       <c r="P31" s="12" t="n"/>
       <c r="Q31" s="12" t="n"/>
       <c r="R31" s="12" t="n"/>
-      <c r="S31" s="12" t="n"/>
-      <c r="T31" s="11" t="n"/>
+      <c r="S31" s="11" t="n"/>
     </row>
     <row r="32" ht="19.5" customHeight="1">
       <c r="A32" s="10" t="n">
@@ -2015,21 +1983,20 @@
         <v/>
       </c>
       <c r="K32" s="13">
-        <f>IF(J32="✘ Vencido","NO APTO",IF(L32="","",UPPER(L32)))</f>
-        <v/>
-      </c>
-      <c r="L32" s="13" t="n"/>
-      <c r="M32" s="14">
+        <f>IF(I32="","",IF(I32&gt;=TODAY(),"APTO","NO APTO"))</f>
+        <v/>
+      </c>
+      <c r="L32" s="14">
         <f>IF(AND(G32="✔ Vigente",H32&lt;&gt;"",ISNUMBER(H32),H32&gt;=DATE(YEAR(TODAY()),MONTH(TODAY())-1,1),J32="✔ Vigente",K32="APTO"),"✔ ACCESO PERMITIDO","✘ SIN ACCESO")</f>
         <v/>
       </c>
+      <c r="M32" s="12" t="n"/>
       <c r="N32" s="12" t="n"/>
       <c r="O32" s="12" t="n"/>
       <c r="P32" s="12" t="n"/>
       <c r="Q32" s="12" t="n"/>
       <c r="R32" s="12" t="n"/>
-      <c r="S32" s="12" t="n"/>
-      <c r="T32" s="11" t="n"/>
+      <c r="S32" s="11" t="n"/>
     </row>
     <row r="33" ht="19.5" customHeight="1">
       <c r="A33" s="15" t="n">
@@ -2051,21 +2018,20 @@
         <v/>
       </c>
       <c r="K33" s="13">
-        <f>IF(J33="✘ Vencido","NO APTO",IF(L33="","",UPPER(L33)))</f>
-        <v/>
-      </c>
-      <c r="L33" s="13" t="n"/>
-      <c r="M33" s="16">
+        <f>IF(I33="","",IF(I33&gt;=TODAY(),"APTO","NO APTO"))</f>
+        <v/>
+      </c>
+      <c r="L33" s="16">
         <f>IF(AND(G33="✔ Vigente",H33&lt;&gt;"",ISNUMBER(H33),H33&gt;=DATE(YEAR(TODAY()),MONTH(TODAY())-1,1),J33="✔ Vigente",K33="APTO"),"✔ ACCESO PERMITIDO","✘ SIN ACCESO")</f>
         <v/>
       </c>
+      <c r="M33" s="12" t="n"/>
       <c r="N33" s="12" t="n"/>
       <c r="O33" s="12" t="n"/>
       <c r="P33" s="12" t="n"/>
       <c r="Q33" s="12" t="n"/>
       <c r="R33" s="12" t="n"/>
-      <c r="S33" s="12" t="n"/>
-      <c r="T33" s="11" t="n"/>
+      <c r="S33" s="11" t="n"/>
     </row>
     <row r="34" ht="19.5" customHeight="1">
       <c r="A34" s="10" t="n">
@@ -2087,21 +2053,20 @@
         <v/>
       </c>
       <c r="K34" s="13">
-        <f>IF(J34="✘ Vencido","NO APTO",IF(L34="","",UPPER(L34)))</f>
-        <v/>
-      </c>
-      <c r="L34" s="13" t="n"/>
-      <c r="M34" s="14">
+        <f>IF(I34="","",IF(I34&gt;=TODAY(),"APTO","NO APTO"))</f>
+        <v/>
+      </c>
+      <c r="L34" s="14">
         <f>IF(AND(G34="✔ Vigente",H34&lt;&gt;"",ISNUMBER(H34),H34&gt;=DATE(YEAR(TODAY()),MONTH(TODAY())-1,1),J34="✔ Vigente",K34="APTO"),"✔ ACCESO PERMITIDO","✘ SIN ACCESO")</f>
         <v/>
       </c>
+      <c r="M34" s="12" t="n"/>
       <c r="N34" s="12" t="n"/>
       <c r="O34" s="12" t="n"/>
       <c r="P34" s="12" t="n"/>
       <c r="Q34" s="12" t="n"/>
       <c r="R34" s="12" t="n"/>
-      <c r="S34" s="12" t="n"/>
-      <c r="T34" s="11" t="n"/>
+      <c r="S34" s="11" t="n"/>
     </row>
     <row r="35" ht="19.5" customHeight="1">
       <c r="A35" s="15" t="n">
@@ -2123,21 +2088,20 @@
         <v/>
       </c>
       <c r="K35" s="13">
-        <f>IF(J35="✘ Vencido","NO APTO",IF(L35="","",UPPER(L35)))</f>
-        <v/>
-      </c>
-      <c r="L35" s="13" t="n"/>
-      <c r="M35" s="16">
+        <f>IF(I35="","",IF(I35&gt;=TODAY(),"APTO","NO APTO"))</f>
+        <v/>
+      </c>
+      <c r="L35" s="16">
         <f>IF(AND(G35="✔ Vigente",H35&lt;&gt;"",ISNUMBER(H35),H35&gt;=DATE(YEAR(TODAY()),MONTH(TODAY())-1,1),J35="✔ Vigente",K35="APTO"),"✔ ACCESO PERMITIDO","✘ SIN ACCESO")</f>
         <v/>
       </c>
+      <c r="M35" s="12" t="n"/>
       <c r="N35" s="12" t="n"/>
       <c r="O35" s="12" t="n"/>
       <c r="P35" s="12" t="n"/>
       <c r="Q35" s="12" t="n"/>
       <c r="R35" s="12" t="n"/>
-      <c r="S35" s="12" t="n"/>
-      <c r="T35" s="11" t="n"/>
+      <c r="S35" s="11" t="n"/>
     </row>
     <row r="36" ht="19.5" customHeight="1">
       <c r="A36" s="10" t="n">
@@ -2159,21 +2123,20 @@
         <v/>
       </c>
       <c r="K36" s="13">
-        <f>IF(J36="✘ Vencido","NO APTO",IF(L36="","",UPPER(L36)))</f>
-        <v/>
-      </c>
-      <c r="L36" s="13" t="n"/>
-      <c r="M36" s="14">
+        <f>IF(I36="","",IF(I36&gt;=TODAY(),"APTO","NO APTO"))</f>
+        <v/>
+      </c>
+      <c r="L36" s="14">
         <f>IF(AND(G36="✔ Vigente",H36&lt;&gt;"",ISNUMBER(H36),H36&gt;=DATE(YEAR(TODAY()),MONTH(TODAY())-1,1),J36="✔ Vigente",K36="APTO"),"✔ ACCESO PERMITIDO","✘ SIN ACCESO")</f>
         <v/>
       </c>
+      <c r="M36" s="12" t="n"/>
       <c r="N36" s="12" t="n"/>
       <c r="O36" s="12" t="n"/>
       <c r="P36" s="12" t="n"/>
       <c r="Q36" s="12" t="n"/>
       <c r="R36" s="12" t="n"/>
-      <c r="S36" s="12" t="n"/>
-      <c r="T36" s="11" t="n"/>
+      <c r="S36" s="11" t="n"/>
     </row>
     <row r="37" ht="19.5" customHeight="1">
       <c r="A37" s="15" t="n">
@@ -2195,21 +2158,20 @@
         <v/>
       </c>
       <c r="K37" s="13">
-        <f>IF(J37="✘ Vencido","NO APTO",IF(L37="","",UPPER(L37)))</f>
-        <v/>
-      </c>
-      <c r="L37" s="13" t="n"/>
-      <c r="M37" s="16">
+        <f>IF(I37="","",IF(I37&gt;=TODAY(),"APTO","NO APTO"))</f>
+        <v/>
+      </c>
+      <c r="L37" s="16">
         <f>IF(AND(G37="✔ Vigente",H37&lt;&gt;"",ISNUMBER(H37),H37&gt;=DATE(YEAR(TODAY()),MONTH(TODAY())-1,1),J37="✔ Vigente",K37="APTO"),"✔ ACCESO PERMITIDO","✘ SIN ACCESO")</f>
         <v/>
       </c>
+      <c r="M37" s="12" t="n"/>
       <c r="N37" s="12" t="n"/>
       <c r="O37" s="12" t="n"/>
       <c r="P37" s="12" t="n"/>
       <c r="Q37" s="12" t="n"/>
       <c r="R37" s="12" t="n"/>
-      <c r="S37" s="12" t="n"/>
-      <c r="T37" s="11" t="n"/>
+      <c r="S37" s="11" t="n"/>
     </row>
     <row r="38" ht="19.5" customHeight="1">
       <c r="A38" s="10" t="n">
@@ -2231,21 +2193,20 @@
         <v/>
       </c>
       <c r="K38" s="13">
-        <f>IF(J38="✘ Vencido","NO APTO",IF(L38="","",UPPER(L38)))</f>
-        <v/>
-      </c>
-      <c r="L38" s="13" t="n"/>
-      <c r="M38" s="14">
+        <f>IF(I38="","",IF(I38&gt;=TODAY(),"APTO","NO APTO"))</f>
+        <v/>
+      </c>
+      <c r="L38" s="14">
         <f>IF(AND(G38="✔ Vigente",H38&lt;&gt;"",ISNUMBER(H38),H38&gt;=DATE(YEAR(TODAY()),MONTH(TODAY())-1,1),J38="✔ Vigente",K38="APTO"),"✔ ACCESO PERMITIDO","✘ SIN ACCESO")</f>
         <v/>
       </c>
+      <c r="M38" s="12" t="n"/>
       <c r="N38" s="12" t="n"/>
       <c r="O38" s="12" t="n"/>
       <c r="P38" s="12" t="n"/>
       <c r="Q38" s="12" t="n"/>
       <c r="R38" s="12" t="n"/>
-      <c r="S38" s="12" t="n"/>
-      <c r="T38" s="11" t="n"/>
+      <c r="S38" s="11" t="n"/>
     </row>
     <row r="39" ht="19.5" customHeight="1">
       <c r="A39" s="15" t="n">
@@ -2267,21 +2228,20 @@
         <v/>
       </c>
       <c r="K39" s="13">
-        <f>IF(J39="✘ Vencido","NO APTO",IF(L39="","",UPPER(L39)))</f>
-        <v/>
-      </c>
-      <c r="L39" s="13" t="n"/>
-      <c r="M39" s="16">
+        <f>IF(I39="","",IF(I39&gt;=TODAY(),"APTO","NO APTO"))</f>
+        <v/>
+      </c>
+      <c r="L39" s="16">
         <f>IF(AND(G39="✔ Vigente",H39&lt;&gt;"",ISNUMBER(H39),H39&gt;=DATE(YEAR(TODAY()),MONTH(TODAY())-1,1),J39="✔ Vigente",K39="APTO"),"✔ ACCESO PERMITIDO","✘ SIN ACCESO")</f>
         <v/>
       </c>
+      <c r="M39" s="12" t="n"/>
       <c r="N39" s="12" t="n"/>
       <c r="O39" s="12" t="n"/>
       <c r="P39" s="12" t="n"/>
       <c r="Q39" s="12" t="n"/>
       <c r="R39" s="12" t="n"/>
-      <c r="S39" s="12" t="n"/>
-      <c r="T39" s="11" t="n"/>
+      <c r="S39" s="11" t="n"/>
     </row>
     <row r="40" ht="19.5" customHeight="1">
       <c r="A40" s="10" t="n">
@@ -2303,21 +2263,20 @@
         <v/>
       </c>
       <c r="K40" s="13">
-        <f>IF(J40="✘ Vencido","NO APTO",IF(L40="","",UPPER(L40)))</f>
-        <v/>
-      </c>
-      <c r="L40" s="13" t="n"/>
-      <c r="M40" s="14">
+        <f>IF(I40="","",IF(I40&gt;=TODAY(),"APTO","NO APTO"))</f>
+        <v/>
+      </c>
+      <c r="L40" s="14">
         <f>IF(AND(G40="✔ Vigente",H40&lt;&gt;"",ISNUMBER(H40),H40&gt;=DATE(YEAR(TODAY()),MONTH(TODAY())-1,1),J40="✔ Vigente",K40="APTO"),"✔ ACCESO PERMITIDO","✘ SIN ACCESO")</f>
         <v/>
       </c>
+      <c r="M40" s="12" t="n"/>
       <c r="N40" s="12" t="n"/>
       <c r="O40" s="12" t="n"/>
       <c r="P40" s="12" t="n"/>
       <c r="Q40" s="12" t="n"/>
       <c r="R40" s="12" t="n"/>
-      <c r="S40" s="12" t="n"/>
-      <c r="T40" s="11" t="n"/>
+      <c r="S40" s="11" t="n"/>
     </row>
     <row r="41" ht="19.5" customHeight="1">
       <c r="A41" s="15" t="n">
@@ -2339,21 +2298,20 @@
         <v/>
       </c>
       <c r="K41" s="13">
-        <f>IF(J41="✘ Vencido","NO APTO",IF(L41="","",UPPER(L41)))</f>
-        <v/>
-      </c>
-      <c r="L41" s="13" t="n"/>
-      <c r="M41" s="16">
+        <f>IF(I41="","",IF(I41&gt;=TODAY(),"APTO","NO APTO"))</f>
+        <v/>
+      </c>
+      <c r="L41" s="16">
         <f>IF(AND(G41="✔ Vigente",H41&lt;&gt;"",ISNUMBER(H41),H41&gt;=DATE(YEAR(TODAY()),MONTH(TODAY())-1,1),J41="✔ Vigente",K41="APTO"),"✔ ACCESO PERMITIDO","✘ SIN ACCESO")</f>
         <v/>
       </c>
+      <c r="M41" s="12" t="n"/>
       <c r="N41" s="12" t="n"/>
       <c r="O41" s="12" t="n"/>
       <c r="P41" s="12" t="n"/>
       <c r="Q41" s="12" t="n"/>
       <c r="R41" s="12" t="n"/>
-      <c r="S41" s="12" t="n"/>
-      <c r="T41" s="11" t="n"/>
+      <c r="S41" s="11" t="n"/>
     </row>
     <row r="42" ht="19.5" customHeight="1">
       <c r="A42" s="10" t="n">
@@ -2375,21 +2333,20 @@
         <v/>
       </c>
       <c r="K42" s="13">
-        <f>IF(J42="✘ Vencido","NO APTO",IF(L42="","",UPPER(L42)))</f>
-        <v/>
-      </c>
-      <c r="L42" s="13" t="n"/>
-      <c r="M42" s="14">
+        <f>IF(I42="","",IF(I42&gt;=TODAY(),"APTO","NO APTO"))</f>
+        <v/>
+      </c>
+      <c r="L42" s="14">
         <f>IF(AND(G42="✔ Vigente",H42&lt;&gt;"",ISNUMBER(H42),H42&gt;=DATE(YEAR(TODAY()),MONTH(TODAY())-1,1),J42="✔ Vigente",K42="APTO"),"✔ ACCESO PERMITIDO","✘ SIN ACCESO")</f>
         <v/>
       </c>
+      <c r="M42" s="12" t="n"/>
       <c r="N42" s="12" t="n"/>
       <c r="O42" s="12" t="n"/>
       <c r="P42" s="12" t="n"/>
       <c r="Q42" s="12" t="n"/>
       <c r="R42" s="12" t="n"/>
-      <c r="S42" s="12" t="n"/>
-      <c r="T42" s="11" t="n"/>
+      <c r="S42" s="11" t="n"/>
     </row>
     <row r="43" ht="19.5" customHeight="1">
       <c r="A43" s="15" t="n">
@@ -2411,21 +2368,20 @@
         <v/>
       </c>
       <c r="K43" s="13">
-        <f>IF(J43="✘ Vencido","NO APTO",IF(L43="","",UPPER(L43)))</f>
-        <v/>
-      </c>
-      <c r="L43" s="13" t="n"/>
-      <c r="M43" s="16">
+        <f>IF(I43="","",IF(I43&gt;=TODAY(),"APTO","NO APTO"))</f>
+        <v/>
+      </c>
+      <c r="L43" s="16">
         <f>IF(AND(G43="✔ Vigente",H43&lt;&gt;"",ISNUMBER(H43),H43&gt;=DATE(YEAR(TODAY()),MONTH(TODAY())-1,1),J43="✔ Vigente",K43="APTO"),"✔ ACCESO PERMITIDO","✘ SIN ACCESO")</f>
         <v/>
       </c>
+      <c r="M43" s="12" t="n"/>
       <c r="N43" s="12" t="n"/>
       <c r="O43" s="12" t="n"/>
       <c r="P43" s="12" t="n"/>
       <c r="Q43" s="12" t="n"/>
       <c r="R43" s="12" t="n"/>
-      <c r="S43" s="12" t="n"/>
-      <c r="T43" s="11" t="n"/>
+      <c r="S43" s="11" t="n"/>
     </row>
     <row r="44" ht="19.5" customHeight="1">
       <c r="A44" s="10" t="n">
@@ -2447,21 +2403,20 @@
         <v/>
       </c>
       <c r="K44" s="13">
-        <f>IF(J44="✘ Vencido","NO APTO",IF(L44="","",UPPER(L44)))</f>
-        <v/>
-      </c>
-      <c r="L44" s="13" t="n"/>
-      <c r="M44" s="14">
+        <f>IF(I44="","",IF(I44&gt;=TODAY(),"APTO","NO APTO"))</f>
+        <v/>
+      </c>
+      <c r="L44" s="14">
         <f>IF(AND(G44="✔ Vigente",H44&lt;&gt;"",ISNUMBER(H44),H44&gt;=DATE(YEAR(TODAY()),MONTH(TODAY())-1,1),J44="✔ Vigente",K44="APTO"),"✔ ACCESO PERMITIDO","✘ SIN ACCESO")</f>
         <v/>
       </c>
+      <c r="M44" s="12" t="n"/>
       <c r="N44" s="12" t="n"/>
       <c r="O44" s="12" t="n"/>
       <c r="P44" s="12" t="n"/>
       <c r="Q44" s="12" t="n"/>
       <c r="R44" s="12" t="n"/>
-      <c r="S44" s="12" t="n"/>
-      <c r="T44" s="11" t="n"/>
+      <c r="S44" s="11" t="n"/>
     </row>
     <row r="45" ht="19.5" customHeight="1">
       <c r="A45" s="15" t="n">
@@ -2483,21 +2438,20 @@
         <v/>
       </c>
       <c r="K45" s="13">
-        <f>IF(J45="✘ Vencido","NO APTO",IF(L45="","",UPPER(L45)))</f>
-        <v/>
-      </c>
-      <c r="L45" s="13" t="n"/>
-      <c r="M45" s="16">
+        <f>IF(I45="","",IF(I45&gt;=TODAY(),"APTO","NO APTO"))</f>
+        <v/>
+      </c>
+      <c r="L45" s="16">
         <f>IF(AND(G45="✔ Vigente",H45&lt;&gt;"",ISNUMBER(H45),H45&gt;=DATE(YEAR(TODAY()),MONTH(TODAY())-1,1),J45="✔ Vigente",K45="APTO"),"✔ ACCESO PERMITIDO","✘ SIN ACCESO")</f>
         <v/>
       </c>
+      <c r="M45" s="12" t="n"/>
       <c r="N45" s="12" t="n"/>
       <c r="O45" s="12" t="n"/>
       <c r="P45" s="12" t="n"/>
       <c r="Q45" s="12" t="n"/>
       <c r="R45" s="12" t="n"/>
-      <c r="S45" s="12" t="n"/>
-      <c r="T45" s="11" t="n"/>
+      <c r="S45" s="11" t="n"/>
     </row>
     <row r="46" ht="19.5" customHeight="1">
       <c r="A46" s="10" t="n">
@@ -2519,21 +2473,20 @@
         <v/>
       </c>
       <c r="K46" s="13">
-        <f>IF(J46="✘ Vencido","NO APTO",IF(L46="","",UPPER(L46)))</f>
-        <v/>
-      </c>
-      <c r="L46" s="13" t="n"/>
-      <c r="M46" s="14">
+        <f>IF(I46="","",IF(I46&gt;=TODAY(),"APTO","NO APTO"))</f>
+        <v/>
+      </c>
+      <c r="L46" s="14">
         <f>IF(AND(G46="✔ Vigente",H46&lt;&gt;"",ISNUMBER(H46),H46&gt;=DATE(YEAR(TODAY()),MONTH(TODAY())-1,1),J46="✔ Vigente",K46="APTO"),"✔ ACCESO PERMITIDO","✘ SIN ACCESO")</f>
         <v/>
       </c>
+      <c r="M46" s="12" t="n"/>
       <c r="N46" s="12" t="n"/>
       <c r="O46" s="12" t="n"/>
       <c r="P46" s="12" t="n"/>
       <c r="Q46" s="12" t="n"/>
       <c r="R46" s="12" t="n"/>
-      <c r="S46" s="12" t="n"/>
-      <c r="T46" s="11" t="n"/>
+      <c r="S46" s="11" t="n"/>
     </row>
     <row r="47" ht="19.5" customHeight="1">
       <c r="A47" s="15" t="n">
@@ -2555,21 +2508,20 @@
         <v/>
       </c>
       <c r="K47" s="13">
-        <f>IF(J47="✘ Vencido","NO APTO",IF(L47="","",UPPER(L47)))</f>
-        <v/>
-      </c>
-      <c r="L47" s="13" t="n"/>
-      <c r="M47" s="16">
+        <f>IF(I47="","",IF(I47&gt;=TODAY(),"APTO","NO APTO"))</f>
+        <v/>
+      </c>
+      <c r="L47" s="16">
         <f>IF(AND(G47="✔ Vigente",H47&lt;&gt;"",ISNUMBER(H47),H47&gt;=DATE(YEAR(TODAY()),MONTH(TODAY())-1,1),J47="✔ Vigente",K47="APTO"),"✔ ACCESO PERMITIDO","✘ SIN ACCESO")</f>
         <v/>
       </c>
+      <c r="M47" s="12" t="n"/>
       <c r="N47" s="12" t="n"/>
       <c r="O47" s="12" t="n"/>
       <c r="P47" s="12" t="n"/>
       <c r="Q47" s="12" t="n"/>
       <c r="R47" s="12" t="n"/>
-      <c r="S47" s="12" t="n"/>
-      <c r="T47" s="11" t="n"/>
+      <c r="S47" s="11" t="n"/>
     </row>
     <row r="48" ht="19.5" customHeight="1">
       <c r="A48" s="10" t="n">
@@ -2591,21 +2543,20 @@
         <v/>
       </c>
       <c r="K48" s="13">
-        <f>IF(J48="✘ Vencido","NO APTO",IF(L48="","",UPPER(L48)))</f>
-        <v/>
-      </c>
-      <c r="L48" s="13" t="n"/>
-      <c r="M48" s="14">
+        <f>IF(I48="","",IF(I48&gt;=TODAY(),"APTO","NO APTO"))</f>
+        <v/>
+      </c>
+      <c r="L48" s="14">
         <f>IF(AND(G48="✔ Vigente",H48&lt;&gt;"",ISNUMBER(H48),H48&gt;=DATE(YEAR(TODAY()),MONTH(TODAY())-1,1),J48="✔ Vigente",K48="APTO"),"✔ ACCESO PERMITIDO","✘ SIN ACCESO")</f>
         <v/>
       </c>
+      <c r="M48" s="12" t="n"/>
       <c r="N48" s="12" t="n"/>
       <c r="O48" s="12" t="n"/>
       <c r="P48" s="12" t="n"/>
       <c r="Q48" s="12" t="n"/>
       <c r="R48" s="12" t="n"/>
-      <c r="S48" s="12" t="n"/>
-      <c r="T48" s="11" t="n"/>
+      <c r="S48" s="11" t="n"/>
     </row>
     <row r="49" ht="19.5" customHeight="1">
       <c r="A49" s="15" t="n">
@@ -2627,21 +2578,20 @@
         <v/>
       </c>
       <c r="K49" s="13">
-        <f>IF(J49="✘ Vencido","NO APTO",IF(L49="","",UPPER(L49)))</f>
-        <v/>
-      </c>
-      <c r="L49" s="13" t="n"/>
-      <c r="M49" s="16">
+        <f>IF(I49="","",IF(I49&gt;=TODAY(),"APTO","NO APTO"))</f>
+        <v/>
+      </c>
+      <c r="L49" s="16">
         <f>IF(AND(G49="✔ Vigente",H49&lt;&gt;"",ISNUMBER(H49),H49&gt;=DATE(YEAR(TODAY()),MONTH(TODAY())-1,1),J49="✔ Vigente",K49="APTO"),"✔ ACCESO PERMITIDO","✘ SIN ACCESO")</f>
         <v/>
       </c>
+      <c r="M49" s="12" t="n"/>
       <c r="N49" s="12" t="n"/>
       <c r="O49" s="12" t="n"/>
       <c r="P49" s="12" t="n"/>
       <c r="Q49" s="12" t="n"/>
       <c r="R49" s="12" t="n"/>
-      <c r="S49" s="12" t="n"/>
-      <c r="T49" s="11" t="n"/>
+      <c r="S49" s="11" t="n"/>
     </row>
     <row r="50" ht="19.5" customHeight="1">
       <c r="A50" s="10" t="n">
@@ -2663,21 +2613,20 @@
         <v/>
       </c>
       <c r="K50" s="13">
-        <f>IF(J50="✘ Vencido","NO APTO",IF(L50="","",UPPER(L50)))</f>
-        <v/>
-      </c>
-      <c r="L50" s="13" t="n"/>
-      <c r="M50" s="14">
+        <f>IF(I50="","",IF(I50&gt;=TODAY(),"APTO","NO APTO"))</f>
+        <v/>
+      </c>
+      <c r="L50" s="14">
         <f>IF(AND(G50="✔ Vigente",H50&lt;&gt;"",ISNUMBER(H50),H50&gt;=DATE(YEAR(TODAY()),MONTH(TODAY())-1,1),J50="✔ Vigente",K50="APTO"),"✔ ACCESO PERMITIDO","✘ SIN ACCESO")</f>
         <v/>
       </c>
+      <c r="M50" s="12" t="n"/>
       <c r="N50" s="12" t="n"/>
       <c r="O50" s="12" t="n"/>
       <c r="P50" s="12" t="n"/>
       <c r="Q50" s="12" t="n"/>
       <c r="R50" s="12" t="n"/>
-      <c r="S50" s="12" t="n"/>
-      <c r="T50" s="11" t="n"/>
+      <c r="S50" s="11" t="n"/>
     </row>
     <row r="51" ht="19.5" customHeight="1">
       <c r="A51" s="15" t="n">
@@ -2699,21 +2648,20 @@
         <v/>
       </c>
       <c r="K51" s="13">
-        <f>IF(J51="✘ Vencido","NO APTO",IF(L51="","",UPPER(L51)))</f>
-        <v/>
-      </c>
-      <c r="L51" s="13" t="n"/>
-      <c r="M51" s="16">
+        <f>IF(I51="","",IF(I51&gt;=TODAY(),"APTO","NO APTO"))</f>
+        <v/>
+      </c>
+      <c r="L51" s="16">
         <f>IF(AND(G51="✔ Vigente",H51&lt;&gt;"",ISNUMBER(H51),H51&gt;=DATE(YEAR(TODAY()),MONTH(TODAY())-1,1),J51="✔ Vigente",K51="APTO"),"✔ ACCESO PERMITIDO","✘ SIN ACCESO")</f>
         <v/>
       </c>
+      <c r="M51" s="12" t="n"/>
       <c r="N51" s="12" t="n"/>
       <c r="O51" s="12" t="n"/>
       <c r="P51" s="12" t="n"/>
       <c r="Q51" s="12" t="n"/>
       <c r="R51" s="12" t="n"/>
-      <c r="S51" s="12" t="n"/>
-      <c r="T51" s="11" t="n"/>
+      <c r="S51" s="11" t="n"/>
     </row>
     <row r="52" ht="19.5" customHeight="1">
       <c r="A52" s="10" t="n">
@@ -2735,21 +2683,20 @@
         <v/>
       </c>
       <c r="K52" s="13">
-        <f>IF(J52="✘ Vencido","NO APTO",IF(L52="","",UPPER(L52)))</f>
-        <v/>
-      </c>
-      <c r="L52" s="13" t="n"/>
-      <c r="M52" s="14">
+        <f>IF(I52="","",IF(I52&gt;=TODAY(),"APTO","NO APTO"))</f>
+        <v/>
+      </c>
+      <c r="L52" s="14">
         <f>IF(AND(G52="✔ Vigente",H52&lt;&gt;"",ISNUMBER(H52),H52&gt;=DATE(YEAR(TODAY()),MONTH(TODAY())-1,1),J52="✔ Vigente",K52="APTO"),"✔ ACCESO PERMITIDO","✘ SIN ACCESO")</f>
         <v/>
       </c>
+      <c r="M52" s="12" t="n"/>
       <c r="N52" s="12" t="n"/>
       <c r="O52" s="12" t="n"/>
       <c r="P52" s="12" t="n"/>
       <c r="Q52" s="12" t="n"/>
       <c r="R52" s="12" t="n"/>
-      <c r="S52" s="12" t="n"/>
-      <c r="T52" s="11" t="n"/>
+      <c r="S52" s="11" t="n"/>
     </row>
     <row r="53" ht="19.5" customHeight="1">
       <c r="A53" s="15" t="n">
@@ -2771,21 +2718,20 @@
         <v/>
       </c>
       <c r="K53" s="13">
-        <f>IF(J53="✘ Vencido","NO APTO",IF(L53="","",UPPER(L53)))</f>
-        <v/>
-      </c>
-      <c r="L53" s="13" t="n"/>
-      <c r="M53" s="16">
+        <f>IF(I53="","",IF(I53&gt;=TODAY(),"APTO","NO APTO"))</f>
+        <v/>
+      </c>
+      <c r="L53" s="16">
         <f>IF(AND(G53="✔ Vigente",H53&lt;&gt;"",ISNUMBER(H53),H53&gt;=DATE(YEAR(TODAY()),MONTH(TODAY())-1,1),J53="✔ Vigente",K53="APTO"),"✔ ACCESO PERMITIDO","✘ SIN ACCESO")</f>
         <v/>
       </c>
+      <c r="M53" s="12" t="n"/>
       <c r="N53" s="12" t="n"/>
       <c r="O53" s="12" t="n"/>
       <c r="P53" s="12" t="n"/>
       <c r="Q53" s="12" t="n"/>
       <c r="R53" s="12" t="n"/>
-      <c r="S53" s="12" t="n"/>
-      <c r="T53" s="11" t="n"/>
+      <c r="S53" s="11" t="n"/>
     </row>
     <row r="54" ht="19.5" customHeight="1">
       <c r="A54" s="10" t="n">
@@ -2807,21 +2753,20 @@
         <v/>
       </c>
       <c r="K54" s="13">
-        <f>IF(J54="✘ Vencido","NO APTO",IF(L54="","",UPPER(L54)))</f>
-        <v/>
-      </c>
-      <c r="L54" s="13" t="n"/>
-      <c r="M54" s="14">
+        <f>IF(I54="","",IF(I54&gt;=TODAY(),"APTO","NO APTO"))</f>
+        <v/>
+      </c>
+      <c r="L54" s="14">
         <f>IF(AND(G54="✔ Vigente",H54&lt;&gt;"",ISNUMBER(H54),H54&gt;=DATE(YEAR(TODAY()),MONTH(TODAY())-1,1),J54="✔ Vigente",K54="APTO"),"✔ ACCESO PERMITIDO","✘ SIN ACCESO")</f>
         <v/>
       </c>
+      <c r="M54" s="12" t="n"/>
       <c r="N54" s="12" t="n"/>
       <c r="O54" s="12" t="n"/>
       <c r="P54" s="12" t="n"/>
       <c r="Q54" s="12" t="n"/>
       <c r="R54" s="12" t="n"/>
-      <c r="S54" s="12" t="n"/>
-      <c r="T54" s="11" t="n"/>
+      <c r="S54" s="11" t="n"/>
     </row>
     <row r="55" ht="19.5" customHeight="1">
       <c r="A55" s="15" t="n">
@@ -2843,21 +2788,20 @@
         <v/>
       </c>
       <c r="K55" s="13">
-        <f>IF(J55="✘ Vencido","NO APTO",IF(L55="","",UPPER(L55)))</f>
-        <v/>
-      </c>
-      <c r="L55" s="13" t="n"/>
-      <c r="M55" s="16">
+        <f>IF(I55="","",IF(I55&gt;=TODAY(),"APTO","NO APTO"))</f>
+        <v/>
+      </c>
+      <c r="L55" s="16">
         <f>IF(AND(G55="✔ Vigente",H55&lt;&gt;"",ISNUMBER(H55),H55&gt;=DATE(YEAR(TODAY()),MONTH(TODAY())-1,1),J55="✔ Vigente",K55="APTO"),"✔ ACCESO PERMITIDO","✘ SIN ACCESO")</f>
         <v/>
       </c>
+      <c r="M55" s="12" t="n"/>
       <c r="N55" s="12" t="n"/>
       <c r="O55" s="12" t="n"/>
       <c r="P55" s="12" t="n"/>
       <c r="Q55" s="12" t="n"/>
       <c r="R55" s="12" t="n"/>
-      <c r="S55" s="12" t="n"/>
-      <c r="T55" s="11" t="n"/>
+      <c r="S55" s="11" t="n"/>
     </row>
   </sheetData>
   <autoFilter ref="A5:Q5"/>
@@ -2923,23 +2867,23 @@
       <formula>K6="NO APTO"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M6:M55">
+  <conditionalFormatting sqref="L6:L55">
     <cfRule type="expression" priority="15" dxfId="17">
-      <formula>M6="✔ ACCESO PERMITIDO"</formula>
+      <formula>L6="✔ ACCESO PERMITIDO"</formula>
     </cfRule>
     <cfRule type="expression" priority="16" dxfId="15">
-      <formula>M6="✘ SIN ACCESO"</formula>
+      <formula>L6="✘ SIN ACCESO"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N6:S55">
+  <conditionalFormatting sqref="M6:R55">
     <cfRule type="expression" priority="17" dxfId="15">
-      <formula>AND(N6&lt;&gt;"",ISNUMBER(N6),N6&lt;TODAY())</formula>
+      <formula>AND(M6&lt;&gt;"",ISNUMBER(M6),M6&lt;TODAY())</formula>
     </cfRule>
     <cfRule type="expression" priority="18" dxfId="16">
-      <formula>AND(N6&lt;&gt;"",ISNUMBER(N6),N6&gt;=TODAY(),N6&lt;=TODAY()+30)</formula>
+      <formula>AND(M6&lt;&gt;"",ISNUMBER(M6),M6&gt;=TODAY(),M6&lt;=TODAY()+30)</formula>
     </cfRule>
     <cfRule type="expression" priority="19" dxfId="17">
-      <formula>AND(N6&lt;&gt;"",ISNUMBER(N6),N6&gt;TODAY()+30)</formula>
+      <formula>AND(M6&lt;&gt;"",ISNUMBER(M6),M6&gt;TODAY()+30)</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
